--- a/artfynd/A 31590-2025 artfynd.xlsx
+++ b/artfynd/A 31590-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY2"/>
+  <dimension ref="A1:AY35"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -678,7 +678,7 @@
         <v>127264982</v>
       </c>
       <c r="B2" t="n">
-        <v>98361</v>
+        <v>98436</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -787,6 +787,3436 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>127283088</v>
+      </c>
+      <c r="B3" t="n">
+        <v>105471</v>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E3" t="n">
+        <v>221144</v>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>Grönpyrola</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>Pyrola chlorantha</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>Sw.</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="P3" t="inlineStr">
+        <is>
+          <t>Gråtängarna, Gstr</t>
+        </is>
+      </c>
+      <c r="Q3" t="n">
+        <v>603837</v>
+      </c>
+      <c r="R3" t="n">
+        <v>6692637</v>
+      </c>
+      <c r="S3" t="n">
+        <v>10</v>
+      </c>
+      <c r="T3" t="inlineStr">
+        <is>
+          <t>Gävleborg</t>
+        </is>
+      </c>
+      <c r="U3" t="inlineStr">
+        <is>
+          <t>Gävle</t>
+        </is>
+      </c>
+      <c r="V3" t="inlineStr">
+        <is>
+          <t>Gästrikland</t>
+        </is>
+      </c>
+      <c r="W3" t="inlineStr">
+        <is>
+          <t>Hedesunda</t>
+        </is>
+      </c>
+      <c r="Y3" t="inlineStr">
+        <is>
+          <t>2025-08-06</t>
+        </is>
+      </c>
+      <c r="AA3" t="inlineStr">
+        <is>
+          <t>2025-08-06</t>
+        </is>
+      </c>
+      <c r="AD3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT3" t="inlineStr"/>
+      <c r="AW3" t="inlineStr">
+        <is>
+          <t>Beke Regelin</t>
+        </is>
+      </c>
+      <c r="AX3" t="inlineStr">
+        <is>
+          <t>Beke Regelin, Clara Lerbro</t>
+        </is>
+      </c>
+      <c r="AY3" t="inlineStr"/>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>127264978</v>
+      </c>
+      <c r="B4" t="n">
+        <v>97314</v>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E4" t="n">
+        <v>221945</v>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Revlummer</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>Lycopodium annotinum</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr"/>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>Gråtängarna, Gstr</t>
+        </is>
+      </c>
+      <c r="Q4" t="n">
+        <v>603963</v>
+      </c>
+      <c r="R4" t="n">
+        <v>6692670</v>
+      </c>
+      <c r="S4" t="n">
+        <v>10</v>
+      </c>
+      <c r="T4" t="inlineStr">
+        <is>
+          <t>Gävleborg</t>
+        </is>
+      </c>
+      <c r="U4" t="inlineStr">
+        <is>
+          <t>Gävle</t>
+        </is>
+      </c>
+      <c r="V4" t="inlineStr">
+        <is>
+          <t>Gästrikland</t>
+        </is>
+      </c>
+      <c r="W4" t="inlineStr">
+        <is>
+          <t>Hedesunda</t>
+        </is>
+      </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>2025-08-04</t>
+        </is>
+      </c>
+      <c r="AA4" t="inlineStr">
+        <is>
+          <t>2025-08-04</t>
+        </is>
+      </c>
+      <c r="AD4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF4" t="inlineStr"/>
+      <c r="AG4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT4" t="inlineStr"/>
+      <c r="AW4" t="inlineStr">
+        <is>
+          <t>Beke Regelin</t>
+        </is>
+      </c>
+      <c r="AX4" t="inlineStr">
+        <is>
+          <t>Beke Regelin</t>
+        </is>
+      </c>
+      <c r="AY4" t="inlineStr"/>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>127283086</v>
+      </c>
+      <c r="B5" t="n">
+        <v>98436</v>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E5" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>Gråtängarna, Gstr</t>
+        </is>
+      </c>
+      <c r="Q5" t="n">
+        <v>603813</v>
+      </c>
+      <c r="R5" t="n">
+        <v>6692582</v>
+      </c>
+      <c r="S5" t="n">
+        <v>10</v>
+      </c>
+      <c r="T5" t="inlineStr">
+        <is>
+          <t>Gävleborg</t>
+        </is>
+      </c>
+      <c r="U5" t="inlineStr">
+        <is>
+          <t>Gävle</t>
+        </is>
+      </c>
+      <c r="V5" t="inlineStr">
+        <is>
+          <t>Gästrikland</t>
+        </is>
+      </c>
+      <c r="W5" t="inlineStr">
+        <is>
+          <t>Hedesunda</t>
+        </is>
+      </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>2025-08-06</t>
+        </is>
+      </c>
+      <c r="AA5" t="inlineStr">
+        <is>
+          <t>2025-08-06</t>
+        </is>
+      </c>
+      <c r="AD5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT5" t="inlineStr"/>
+      <c r="AW5" t="inlineStr">
+        <is>
+          <t>Beke Regelin</t>
+        </is>
+      </c>
+      <c r="AX5" t="inlineStr">
+        <is>
+          <t>Beke Regelin, Clara Lerbro</t>
+        </is>
+      </c>
+      <c r="AY5" t="inlineStr"/>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>127283078</v>
+      </c>
+      <c r="B6" t="n">
+        <v>91284</v>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E6" t="n">
+        <v>5447</v>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Vedticka</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>Fuscoporia viticola</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>(Schwein.) Murrill</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr"/>
+      <c r="J6" t="inlineStr"/>
+      <c r="K6" t="inlineStr"/>
+      <c r="N6" t="inlineStr"/>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>Gråtängarna, Gstr</t>
+        </is>
+      </c>
+      <c r="Q6" t="n">
+        <v>603985</v>
+      </c>
+      <c r="R6" t="n">
+        <v>6692665</v>
+      </c>
+      <c r="S6" t="n">
+        <v>10</v>
+      </c>
+      <c r="T6" t="inlineStr">
+        <is>
+          <t>Gävleborg</t>
+        </is>
+      </c>
+      <c r="U6" t="inlineStr">
+        <is>
+          <t>Gävle</t>
+        </is>
+      </c>
+      <c r="V6" t="inlineStr">
+        <is>
+          <t>Gästrikland</t>
+        </is>
+      </c>
+      <c r="W6" t="inlineStr">
+        <is>
+          <t>Hedesunda</t>
+        </is>
+      </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>2025-08-06</t>
+        </is>
+      </c>
+      <c r="AA6" t="inlineStr">
+        <is>
+          <t>2025-08-06</t>
+        </is>
+      </c>
+      <c r="AD6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF6" t="inlineStr"/>
+      <c r="AG6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT6" t="inlineStr"/>
+      <c r="AW6" t="inlineStr">
+        <is>
+          <t>Beke Regelin</t>
+        </is>
+      </c>
+      <c r="AX6" t="inlineStr">
+        <is>
+          <t>Beke Regelin, Clara Lerbro</t>
+        </is>
+      </c>
+      <c r="AY6" t="inlineStr"/>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>127264973</v>
+      </c>
+      <c r="B7" t="n">
+        <v>97314</v>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E7" t="n">
+        <v>221945</v>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Revlummer</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>Lycopodium annotinum</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr"/>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>Gråtängarna, Gstr</t>
+        </is>
+      </c>
+      <c r="Q7" t="n">
+        <v>603941</v>
+      </c>
+      <c r="R7" t="n">
+        <v>6692639</v>
+      </c>
+      <c r="S7" t="n">
+        <v>10</v>
+      </c>
+      <c r="T7" t="inlineStr">
+        <is>
+          <t>Gävleborg</t>
+        </is>
+      </c>
+      <c r="U7" t="inlineStr">
+        <is>
+          <t>Gävle</t>
+        </is>
+      </c>
+      <c r="V7" t="inlineStr">
+        <is>
+          <t>Gästrikland</t>
+        </is>
+      </c>
+      <c r="W7" t="inlineStr">
+        <is>
+          <t>Hedesunda</t>
+        </is>
+      </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>2025-08-04</t>
+        </is>
+      </c>
+      <c r="AA7" t="inlineStr">
+        <is>
+          <t>2025-08-04</t>
+        </is>
+      </c>
+      <c r="AD7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT7" t="inlineStr"/>
+      <c r="AW7" t="inlineStr">
+        <is>
+          <t>Beke Regelin</t>
+        </is>
+      </c>
+      <c r="AX7" t="inlineStr">
+        <is>
+          <t>Beke Regelin</t>
+        </is>
+      </c>
+      <c r="AY7" t="inlineStr"/>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>127283087</v>
+      </c>
+      <c r="B8" t="n">
+        <v>105471</v>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E8" t="n">
+        <v>221144</v>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Grönpyrola</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>Pyrola chlorantha</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>Sw.</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="P8" t="inlineStr">
+        <is>
+          <t>Gråtängarna, Gstr</t>
+        </is>
+      </c>
+      <c r="Q8" t="n">
+        <v>603809</v>
+      </c>
+      <c r="R8" t="n">
+        <v>6692598</v>
+      </c>
+      <c r="S8" t="n">
+        <v>10</v>
+      </c>
+      <c r="T8" t="inlineStr">
+        <is>
+          <t>Gävleborg</t>
+        </is>
+      </c>
+      <c r="U8" t="inlineStr">
+        <is>
+          <t>Gävle</t>
+        </is>
+      </c>
+      <c r="V8" t="inlineStr">
+        <is>
+          <t>Gästrikland</t>
+        </is>
+      </c>
+      <c r="W8" t="inlineStr">
+        <is>
+          <t>Hedesunda</t>
+        </is>
+      </c>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>2025-08-06</t>
+        </is>
+      </c>
+      <c r="AA8" t="inlineStr">
+        <is>
+          <t>2025-08-06</t>
+        </is>
+      </c>
+      <c r="AD8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT8" t="inlineStr"/>
+      <c r="AW8" t="inlineStr">
+        <is>
+          <t>Beke Regelin</t>
+        </is>
+      </c>
+      <c r="AX8" t="inlineStr">
+        <is>
+          <t>Beke Regelin, Clara Lerbro</t>
+        </is>
+      </c>
+      <c r="AY8" t="inlineStr"/>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>127283085</v>
+      </c>
+      <c r="B9" t="n">
+        <v>98436</v>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E9" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>17</t>
+        </is>
+      </c>
+      <c r="P9" t="inlineStr">
+        <is>
+          <t>Gråtängarna, Gstr</t>
+        </is>
+      </c>
+      <c r="Q9" t="n">
+        <v>603852</v>
+      </c>
+      <c r="R9" t="n">
+        <v>6692707</v>
+      </c>
+      <c r="S9" t="n">
+        <v>10</v>
+      </c>
+      <c r="T9" t="inlineStr">
+        <is>
+          <t>Gävleborg</t>
+        </is>
+      </c>
+      <c r="U9" t="inlineStr">
+        <is>
+          <t>Gävle</t>
+        </is>
+      </c>
+      <c r="V9" t="inlineStr">
+        <is>
+          <t>Gästrikland</t>
+        </is>
+      </c>
+      <c r="W9" t="inlineStr">
+        <is>
+          <t>Hedesunda</t>
+        </is>
+      </c>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>2025-08-06</t>
+        </is>
+      </c>
+      <c r="AA9" t="inlineStr">
+        <is>
+          <t>2025-08-06</t>
+        </is>
+      </c>
+      <c r="AD9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT9" t="inlineStr"/>
+      <c r="AW9" t="inlineStr">
+        <is>
+          <t>Beke Regelin</t>
+        </is>
+      </c>
+      <c r="AX9" t="inlineStr">
+        <is>
+          <t>Beke Regelin, Clara Lerbro</t>
+        </is>
+      </c>
+      <c r="AY9" t="inlineStr"/>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>127283076</v>
+      </c>
+      <c r="B10" t="n">
+        <v>56849</v>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E10" t="n">
+        <v>100138</v>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>Tjäder</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>Tetrao urogallus</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr"/>
+      <c r="P10" t="inlineStr">
+        <is>
+          <t>Gråtängarna, Gstr</t>
+        </is>
+      </c>
+      <c r="Q10" t="n">
+        <v>603964</v>
+      </c>
+      <c r="R10" t="n">
+        <v>6692543</v>
+      </c>
+      <c r="S10" t="n">
+        <v>10</v>
+      </c>
+      <c r="T10" t="inlineStr">
+        <is>
+          <t>Gävleborg</t>
+        </is>
+      </c>
+      <c r="U10" t="inlineStr">
+        <is>
+          <t>Gävle</t>
+        </is>
+      </c>
+      <c r="V10" t="inlineStr">
+        <is>
+          <t>Gästrikland</t>
+        </is>
+      </c>
+      <c r="W10" t="inlineStr">
+        <is>
+          <t>Hedesunda</t>
+        </is>
+      </c>
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>2025-08-06</t>
+        </is>
+      </c>
+      <c r="AA10" t="inlineStr">
+        <is>
+          <t>2025-08-06</t>
+        </is>
+      </c>
+      <c r="AC10" t="inlineStr">
+        <is>
+          <t>spillning</t>
+        </is>
+      </c>
+      <c r="AD10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT10" t="inlineStr"/>
+      <c r="AW10" t="inlineStr">
+        <is>
+          <t>Beke Regelin</t>
+        </is>
+      </c>
+      <c r="AX10" t="inlineStr">
+        <is>
+          <t>Beke Regelin, Clara Lerbro</t>
+        </is>
+      </c>
+      <c r="AY10" t="inlineStr"/>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>127283083</v>
+      </c>
+      <c r="B11" t="n">
+        <v>92601</v>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E11" t="n">
+        <v>4361</v>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>Orange taggsvamp</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>Hydnellum aurantiacum</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>(Batsch:Fr.) P.Karst.</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr"/>
+      <c r="J11" t="inlineStr"/>
+      <c r="K11" t="inlineStr"/>
+      <c r="N11" t="inlineStr"/>
+      <c r="P11" t="inlineStr">
+        <is>
+          <t>Gråtängarna, Gstr</t>
+        </is>
+      </c>
+      <c r="Q11" t="n">
+        <v>603807</v>
+      </c>
+      <c r="R11" t="n">
+        <v>6692702</v>
+      </c>
+      <c r="S11" t="n">
+        <v>10</v>
+      </c>
+      <c r="T11" t="inlineStr">
+        <is>
+          <t>Gävleborg</t>
+        </is>
+      </c>
+      <c r="U11" t="inlineStr">
+        <is>
+          <t>Gävle</t>
+        </is>
+      </c>
+      <c r="V11" t="inlineStr">
+        <is>
+          <t>Gästrikland</t>
+        </is>
+      </c>
+      <c r="W11" t="inlineStr">
+        <is>
+          <t>Hedesunda</t>
+        </is>
+      </c>
+      <c r="Y11" t="inlineStr">
+        <is>
+          <t>2025-08-06</t>
+        </is>
+      </c>
+      <c r="AA11" t="inlineStr">
+        <is>
+          <t>2025-08-06</t>
+        </is>
+      </c>
+      <c r="AD11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF11" t="inlineStr"/>
+      <c r="AG11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT11" t="inlineStr"/>
+      <c r="AW11" t="inlineStr">
+        <is>
+          <t>Beke Regelin</t>
+        </is>
+      </c>
+      <c r="AX11" t="inlineStr">
+        <is>
+          <t>Beke Regelin, Clara Lerbro</t>
+        </is>
+      </c>
+      <c r="AY11" t="inlineStr"/>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>127283084</v>
+      </c>
+      <c r="B12" t="n">
+        <v>98436</v>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E12" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="J12" t="inlineStr"/>
+      <c r="K12" t="inlineStr"/>
+      <c r="L12" t="inlineStr"/>
+      <c r="N12" t="inlineStr"/>
+      <c r="P12" t="inlineStr">
+        <is>
+          <t>Gråtängarna, Gstr</t>
+        </is>
+      </c>
+      <c r="Q12" t="n">
+        <v>603920</v>
+      </c>
+      <c r="R12" t="n">
+        <v>6692653</v>
+      </c>
+      <c r="S12" t="n">
+        <v>10</v>
+      </c>
+      <c r="T12" t="inlineStr">
+        <is>
+          <t>Gävleborg</t>
+        </is>
+      </c>
+      <c r="U12" t="inlineStr">
+        <is>
+          <t>Gävle</t>
+        </is>
+      </c>
+      <c r="V12" t="inlineStr">
+        <is>
+          <t>Gästrikland</t>
+        </is>
+      </c>
+      <c r="W12" t="inlineStr">
+        <is>
+          <t>Hedesunda</t>
+        </is>
+      </c>
+      <c r="Y12" t="inlineStr">
+        <is>
+          <t>2025-08-06</t>
+        </is>
+      </c>
+      <c r="AA12" t="inlineStr">
+        <is>
+          <t>2025-08-06</t>
+        </is>
+      </c>
+      <c r="AD12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF12" t="inlineStr"/>
+      <c r="AG12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT12" t="inlineStr"/>
+      <c r="AW12" t="inlineStr">
+        <is>
+          <t>Beke Regelin</t>
+        </is>
+      </c>
+      <c r="AX12" t="inlineStr">
+        <is>
+          <t>Beke Regelin, Clara Lerbro</t>
+        </is>
+      </c>
+      <c r="AY12" t="inlineStr"/>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>127290259</v>
+      </c>
+      <c r="B13" t="n">
+        <v>98436</v>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E13" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="J13" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K13" t="inlineStr">
+        <is>
+          <t>överblommad</t>
+        </is>
+      </c>
+      <c r="L13" t="inlineStr"/>
+      <c r="N13" t="inlineStr"/>
+      <c r="P13" t="inlineStr">
+        <is>
+          <t>Österbyggebo, Gstr</t>
+        </is>
+      </c>
+      <c r="Q13" t="n">
+        <v>603970</v>
+      </c>
+      <c r="R13" t="n">
+        <v>6692424</v>
+      </c>
+      <c r="S13" t="n">
+        <v>10</v>
+      </c>
+      <c r="T13" t="inlineStr">
+        <is>
+          <t>Gävleborg</t>
+        </is>
+      </c>
+      <c r="U13" t="inlineStr">
+        <is>
+          <t>Gävle</t>
+        </is>
+      </c>
+      <c r="V13" t="inlineStr">
+        <is>
+          <t>Gästrikland</t>
+        </is>
+      </c>
+      <c r="W13" t="inlineStr">
+        <is>
+          <t>Hedesunda</t>
+        </is>
+      </c>
+      <c r="Y13" t="inlineStr">
+        <is>
+          <t>2025-08-06</t>
+        </is>
+      </c>
+      <c r="AA13" t="inlineStr">
+        <is>
+          <t>2025-08-06</t>
+        </is>
+      </c>
+      <c r="AD13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF13" t="inlineStr"/>
+      <c r="AG13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT13" t="inlineStr"/>
+      <c r="AW13" t="inlineStr">
+        <is>
+          <t>Clara Lerbro</t>
+        </is>
+      </c>
+      <c r="AX13" t="inlineStr">
+        <is>
+          <t>Clara Lerbro, Beke Regelin</t>
+        </is>
+      </c>
+      <c r="AY13" t="inlineStr"/>
+    </row>
+    <row r="14">
+      <c r="A14" t="n">
+        <v>127290258</v>
+      </c>
+      <c r="B14" t="n">
+        <v>98436</v>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E14" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="J14" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K14" t="inlineStr">
+        <is>
+          <t>överblommad</t>
+        </is>
+      </c>
+      <c r="L14" t="inlineStr"/>
+      <c r="N14" t="inlineStr"/>
+      <c r="P14" t="inlineStr">
+        <is>
+          <t>Österbyggebo, Gstr</t>
+        </is>
+      </c>
+      <c r="Q14" t="n">
+        <v>603981</v>
+      </c>
+      <c r="R14" t="n">
+        <v>6692427</v>
+      </c>
+      <c r="S14" t="n">
+        <v>10</v>
+      </c>
+      <c r="T14" t="inlineStr">
+        <is>
+          <t>Gävleborg</t>
+        </is>
+      </c>
+      <c r="U14" t="inlineStr">
+        <is>
+          <t>Gävle</t>
+        </is>
+      </c>
+      <c r="V14" t="inlineStr">
+        <is>
+          <t>Gästrikland</t>
+        </is>
+      </c>
+      <c r="W14" t="inlineStr">
+        <is>
+          <t>Hedesunda</t>
+        </is>
+      </c>
+      <c r="Y14" t="inlineStr">
+        <is>
+          <t>2025-08-06</t>
+        </is>
+      </c>
+      <c r="AA14" t="inlineStr">
+        <is>
+          <t>2025-08-06</t>
+        </is>
+      </c>
+      <c r="AD14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF14" t="inlineStr"/>
+      <c r="AG14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT14" t="inlineStr"/>
+      <c r="AW14" t="inlineStr">
+        <is>
+          <t>Clara Lerbro</t>
+        </is>
+      </c>
+      <c r="AX14" t="inlineStr">
+        <is>
+          <t>Clara Lerbro, Beke Regelin</t>
+        </is>
+      </c>
+      <c r="AY14" t="inlineStr"/>
+    </row>
+    <row r="15">
+      <c r="A15" t="n">
+        <v>127290233</v>
+      </c>
+      <c r="B15" t="n">
+        <v>91319</v>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E15" t="n">
+        <v>1202</v>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>Ullticka</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>Phellinidium ferrugineofuscum</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr"/>
+      <c r="P15" t="inlineStr">
+        <is>
+          <t>Österbyggebo, Gstr</t>
+        </is>
+      </c>
+      <c r="Q15" t="n">
+        <v>603850</v>
+      </c>
+      <c r="R15" t="n">
+        <v>6692680</v>
+      </c>
+      <c r="S15" t="n">
+        <v>10</v>
+      </c>
+      <c r="T15" t="inlineStr">
+        <is>
+          <t>Gävleborg</t>
+        </is>
+      </c>
+      <c r="U15" t="inlineStr">
+        <is>
+          <t>Gävle</t>
+        </is>
+      </c>
+      <c r="V15" t="inlineStr">
+        <is>
+          <t>Gästrikland</t>
+        </is>
+      </c>
+      <c r="W15" t="inlineStr">
+        <is>
+          <t>Hedesunda</t>
+        </is>
+      </c>
+      <c r="Y15" t="inlineStr">
+        <is>
+          <t>2025-08-06</t>
+        </is>
+      </c>
+      <c r="AA15" t="inlineStr">
+        <is>
+          <t>2025-08-06</t>
+        </is>
+      </c>
+      <c r="AD15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT15" t="inlineStr"/>
+      <c r="AW15" t="inlineStr">
+        <is>
+          <t>Clara Lerbro</t>
+        </is>
+      </c>
+      <c r="AX15" t="inlineStr">
+        <is>
+          <t>Clara Lerbro, Beke Regelin</t>
+        </is>
+      </c>
+      <c r="AY15" t="inlineStr"/>
+    </row>
+    <row r="16">
+      <c r="A16" t="n">
+        <v>127290255</v>
+      </c>
+      <c r="B16" t="n">
+        <v>91333</v>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E16" t="n">
+        <v>1204</v>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>Gränsticka</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>Phellopilus nigrolimitatus</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr"/>
+      <c r="P16" t="inlineStr">
+        <is>
+          <t>Österbyggebo, Gstr</t>
+        </is>
+      </c>
+      <c r="Q16" t="n">
+        <v>603980</v>
+      </c>
+      <c r="R16" t="n">
+        <v>6692483</v>
+      </c>
+      <c r="S16" t="n">
+        <v>10</v>
+      </c>
+      <c r="T16" t="inlineStr">
+        <is>
+          <t>Gävleborg</t>
+        </is>
+      </c>
+      <c r="U16" t="inlineStr">
+        <is>
+          <t>Gävle</t>
+        </is>
+      </c>
+      <c r="V16" t="inlineStr">
+        <is>
+          <t>Gästrikland</t>
+        </is>
+      </c>
+      <c r="W16" t="inlineStr">
+        <is>
+          <t>Hedesunda</t>
+        </is>
+      </c>
+      <c r="Y16" t="inlineStr">
+        <is>
+          <t>2025-08-06</t>
+        </is>
+      </c>
+      <c r="AA16" t="inlineStr">
+        <is>
+          <t>2025-08-06</t>
+        </is>
+      </c>
+      <c r="AD16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT16" t="inlineStr"/>
+      <c r="AW16" t="inlineStr">
+        <is>
+          <t>Clara Lerbro</t>
+        </is>
+      </c>
+      <c r="AX16" t="inlineStr">
+        <is>
+          <t>Clara Lerbro, Beke Regelin</t>
+        </is>
+      </c>
+      <c r="AY16" t="inlineStr"/>
+    </row>
+    <row r="17">
+      <c r="A17" t="n">
+        <v>127283080</v>
+      </c>
+      <c r="B17" t="n">
+        <v>56849</v>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E17" t="n">
+        <v>100138</v>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>Tjäder</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>Tetrao urogallus</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr"/>
+      <c r="K17" t="inlineStr"/>
+      <c r="L17" t="inlineStr"/>
+      <c r="M17" t="inlineStr"/>
+      <c r="N17" t="inlineStr"/>
+      <c r="P17" t="inlineStr">
+        <is>
+          <t>Gråtängarna, Gstr</t>
+        </is>
+      </c>
+      <c r="Q17" t="n">
+        <v>603972</v>
+      </c>
+      <c r="R17" t="n">
+        <v>6692667</v>
+      </c>
+      <c r="S17" t="n">
+        <v>10</v>
+      </c>
+      <c r="T17" t="inlineStr">
+        <is>
+          <t>Gävleborg</t>
+        </is>
+      </c>
+      <c r="U17" t="inlineStr">
+        <is>
+          <t>Gävle</t>
+        </is>
+      </c>
+      <c r="V17" t="inlineStr">
+        <is>
+          <t>Gästrikland</t>
+        </is>
+      </c>
+      <c r="W17" t="inlineStr">
+        <is>
+          <t>Hedesunda</t>
+        </is>
+      </c>
+      <c r="Y17" t="inlineStr">
+        <is>
+          <t>2025-08-06</t>
+        </is>
+      </c>
+      <c r="AA17" t="inlineStr">
+        <is>
+          <t>2025-08-06</t>
+        </is>
+      </c>
+      <c r="AC17" t="inlineStr">
+        <is>
+          <t>Fjäder efter en tjädertupp, 32 cm lång</t>
+        </is>
+      </c>
+      <c r="AD17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT17" t="inlineStr"/>
+      <c r="AW17" t="inlineStr">
+        <is>
+          <t>Beke Regelin</t>
+        </is>
+      </c>
+      <c r="AX17" t="inlineStr">
+        <is>
+          <t>Beke Regelin, Clara Lerbro</t>
+        </is>
+      </c>
+      <c r="AY17" t="inlineStr"/>
+    </row>
+    <row r="18">
+      <c r="A18" t="n">
+        <v>127290240</v>
+      </c>
+      <c r="B18" t="n">
+        <v>98436</v>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E18" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>27</t>
+        </is>
+      </c>
+      <c r="J18" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K18" t="inlineStr"/>
+      <c r="L18" t="inlineStr"/>
+      <c r="N18" t="inlineStr"/>
+      <c r="P18" t="inlineStr">
+        <is>
+          <t>Österbyggebo, Gstr</t>
+        </is>
+      </c>
+      <c r="Q18" t="n">
+        <v>603879</v>
+      </c>
+      <c r="R18" t="n">
+        <v>6692720</v>
+      </c>
+      <c r="S18" t="n">
+        <v>10</v>
+      </c>
+      <c r="T18" t="inlineStr">
+        <is>
+          <t>Gävleborg</t>
+        </is>
+      </c>
+      <c r="U18" t="inlineStr">
+        <is>
+          <t>Gävle</t>
+        </is>
+      </c>
+      <c r="V18" t="inlineStr">
+        <is>
+          <t>Gästrikland</t>
+        </is>
+      </c>
+      <c r="W18" t="inlineStr">
+        <is>
+          <t>Hedesunda</t>
+        </is>
+      </c>
+      <c r="Y18" t="inlineStr">
+        <is>
+          <t>2025-08-06</t>
+        </is>
+      </c>
+      <c r="AA18" t="inlineStr">
+        <is>
+          <t>2025-08-06</t>
+        </is>
+      </c>
+      <c r="AD18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF18" t="inlineStr"/>
+      <c r="AG18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT18" t="inlineStr"/>
+      <c r="AW18" t="inlineStr">
+        <is>
+          <t>Clara Lerbro</t>
+        </is>
+      </c>
+      <c r="AX18" t="inlineStr">
+        <is>
+          <t>Clara Lerbro, Beke Regelin</t>
+        </is>
+      </c>
+      <c r="AY18" t="inlineStr"/>
+    </row>
+    <row r="19">
+      <c r="A19" t="n">
+        <v>127290254</v>
+      </c>
+      <c r="B19" t="n">
+        <v>91284</v>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E19" t="n">
+        <v>5447</v>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>Vedticka</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>Fuscoporia viticola</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>(Schwein.) Murrill</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr"/>
+      <c r="P19" t="inlineStr">
+        <is>
+          <t>Österbyggebo, Gstr</t>
+        </is>
+      </c>
+      <c r="Q19" t="n">
+        <v>603984</v>
+      </c>
+      <c r="R19" t="n">
+        <v>6692486</v>
+      </c>
+      <c r="S19" t="n">
+        <v>10</v>
+      </c>
+      <c r="T19" t="inlineStr">
+        <is>
+          <t>Gävleborg</t>
+        </is>
+      </c>
+      <c r="U19" t="inlineStr">
+        <is>
+          <t>Gävle</t>
+        </is>
+      </c>
+      <c r="V19" t="inlineStr">
+        <is>
+          <t>Gästrikland</t>
+        </is>
+      </c>
+      <c r="W19" t="inlineStr">
+        <is>
+          <t>Hedesunda</t>
+        </is>
+      </c>
+      <c r="Y19" t="inlineStr">
+        <is>
+          <t>2025-08-06</t>
+        </is>
+      </c>
+      <c r="AA19" t="inlineStr">
+        <is>
+          <t>2025-08-06</t>
+        </is>
+      </c>
+      <c r="AD19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT19" t="inlineStr"/>
+      <c r="AW19" t="inlineStr">
+        <is>
+          <t>Clara Lerbro</t>
+        </is>
+      </c>
+      <c r="AX19" t="inlineStr">
+        <is>
+          <t>Clara Lerbro, Beke Regelin</t>
+        </is>
+      </c>
+      <c r="AY19" t="inlineStr"/>
+    </row>
+    <row r="20">
+      <c r="A20" t="n">
+        <v>127290227</v>
+      </c>
+      <c r="B20" t="n">
+        <v>91319</v>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E20" t="n">
+        <v>1202</v>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>Ullticka</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>Phellinidium ferrugineofuscum</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr"/>
+      <c r="P20" t="inlineStr">
+        <is>
+          <t>Österbyggebo, Gstr</t>
+        </is>
+      </c>
+      <c r="Q20" t="n">
+        <v>603853</v>
+      </c>
+      <c r="R20" t="n">
+        <v>6692574</v>
+      </c>
+      <c r="S20" t="n">
+        <v>10</v>
+      </c>
+      <c r="T20" t="inlineStr">
+        <is>
+          <t>Gävleborg</t>
+        </is>
+      </c>
+      <c r="U20" t="inlineStr">
+        <is>
+          <t>Gävle</t>
+        </is>
+      </c>
+      <c r="V20" t="inlineStr">
+        <is>
+          <t>Gästrikland</t>
+        </is>
+      </c>
+      <c r="W20" t="inlineStr">
+        <is>
+          <t>Hedesunda</t>
+        </is>
+      </c>
+      <c r="Y20" t="inlineStr">
+        <is>
+          <t>2025-08-06</t>
+        </is>
+      </c>
+      <c r="AA20" t="inlineStr">
+        <is>
+          <t>2025-08-06</t>
+        </is>
+      </c>
+      <c r="AD20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT20" t="inlineStr"/>
+      <c r="AW20" t="inlineStr">
+        <is>
+          <t>Clara Lerbro</t>
+        </is>
+      </c>
+      <c r="AX20" t="inlineStr">
+        <is>
+          <t>Clara Lerbro, Beke Regelin</t>
+        </is>
+      </c>
+      <c r="AY20" t="inlineStr"/>
+    </row>
+    <row r="21">
+      <c r="A21" t="n">
+        <v>127290226</v>
+      </c>
+      <c r="B21" t="n">
+        <v>92601</v>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E21" t="n">
+        <v>4361</v>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>Orange taggsvamp</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>Hydnellum aurantiacum</t>
+        </is>
+      </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>(Batsch:Fr.) P.Karst.</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J21" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
+      <c r="K21" t="inlineStr"/>
+      <c r="N21" t="inlineStr"/>
+      <c r="P21" t="inlineStr">
+        <is>
+          <t>Österbyggebo, Gstr</t>
+        </is>
+      </c>
+      <c r="Q21" t="n">
+        <v>603857</v>
+      </c>
+      <c r="R21" t="n">
+        <v>6692565</v>
+      </c>
+      <c r="S21" t="n">
+        <v>10</v>
+      </c>
+      <c r="T21" t="inlineStr">
+        <is>
+          <t>Gävleborg</t>
+        </is>
+      </c>
+      <c r="U21" t="inlineStr">
+        <is>
+          <t>Gävle</t>
+        </is>
+      </c>
+      <c r="V21" t="inlineStr">
+        <is>
+          <t>Gästrikland</t>
+        </is>
+      </c>
+      <c r="W21" t="inlineStr">
+        <is>
+          <t>Hedesunda</t>
+        </is>
+      </c>
+      <c r="Y21" t="inlineStr">
+        <is>
+          <t>2025-08-06</t>
+        </is>
+      </c>
+      <c r="AA21" t="inlineStr">
+        <is>
+          <t>2025-08-06</t>
+        </is>
+      </c>
+      <c r="AD21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF21" t="inlineStr"/>
+      <c r="AG21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT21" t="inlineStr"/>
+      <c r="AW21" t="inlineStr">
+        <is>
+          <t>Clara Lerbro</t>
+        </is>
+      </c>
+      <c r="AX21" t="inlineStr">
+        <is>
+          <t>Clara Lerbro, Beke Regelin</t>
+        </is>
+      </c>
+      <c r="AY21" t="inlineStr"/>
+    </row>
+    <row r="22">
+      <c r="A22" t="n">
+        <v>127290260</v>
+      </c>
+      <c r="B22" t="n">
+        <v>98436</v>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E22" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr"/>
+      <c r="P22" t="inlineStr">
+        <is>
+          <t>Österbyggebo, Gstr</t>
+        </is>
+      </c>
+      <c r="Q22" t="n">
+        <v>603977</v>
+      </c>
+      <c r="R22" t="n">
+        <v>6692392</v>
+      </c>
+      <c r="S22" t="n">
+        <v>10</v>
+      </c>
+      <c r="T22" t="inlineStr">
+        <is>
+          <t>Gävleborg</t>
+        </is>
+      </c>
+      <c r="U22" t="inlineStr">
+        <is>
+          <t>Gävle</t>
+        </is>
+      </c>
+      <c r="V22" t="inlineStr">
+        <is>
+          <t>Gästrikland</t>
+        </is>
+      </c>
+      <c r="W22" t="inlineStr">
+        <is>
+          <t>Hedesunda</t>
+        </is>
+      </c>
+      <c r="Y22" t="inlineStr">
+        <is>
+          <t>2025-08-06</t>
+        </is>
+      </c>
+      <c r="AA22" t="inlineStr">
+        <is>
+          <t>2025-08-06</t>
+        </is>
+      </c>
+      <c r="AD22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT22" t="inlineStr"/>
+      <c r="AW22" t="inlineStr">
+        <is>
+          <t>Clara Lerbro</t>
+        </is>
+      </c>
+      <c r="AX22" t="inlineStr">
+        <is>
+          <t>Clara Lerbro, Beke Regelin</t>
+        </is>
+      </c>
+      <c r="AY22" t="inlineStr"/>
+    </row>
+    <row r="23">
+      <c r="A23" t="n">
+        <v>127290239</v>
+      </c>
+      <c r="B23" t="n">
+        <v>91284</v>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E23" t="n">
+        <v>5447</v>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>Vedticka</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>Fuscoporia viticola</t>
+        </is>
+      </c>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>(Schwein.) Murrill</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr"/>
+      <c r="P23" t="inlineStr">
+        <is>
+          <t>Österbyggebo, Gstr</t>
+        </is>
+      </c>
+      <c r="Q23" t="n">
+        <v>603877</v>
+      </c>
+      <c r="R23" t="n">
+        <v>6692706</v>
+      </c>
+      <c r="S23" t="n">
+        <v>10</v>
+      </c>
+      <c r="T23" t="inlineStr">
+        <is>
+          <t>Gävleborg</t>
+        </is>
+      </c>
+      <c r="U23" t="inlineStr">
+        <is>
+          <t>Gävle</t>
+        </is>
+      </c>
+      <c r="V23" t="inlineStr">
+        <is>
+          <t>Gästrikland</t>
+        </is>
+      </c>
+      <c r="W23" t="inlineStr">
+        <is>
+          <t>Hedesunda</t>
+        </is>
+      </c>
+      <c r="Y23" t="inlineStr">
+        <is>
+          <t>2025-08-06</t>
+        </is>
+      </c>
+      <c r="AA23" t="inlineStr">
+        <is>
+          <t>2025-08-06</t>
+        </is>
+      </c>
+      <c r="AD23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT23" t="inlineStr"/>
+      <c r="AW23" t="inlineStr">
+        <is>
+          <t>Clara Lerbro</t>
+        </is>
+      </c>
+      <c r="AX23" t="inlineStr">
+        <is>
+          <t>Clara Lerbro, Beke Regelin</t>
+        </is>
+      </c>
+      <c r="AY23" t="inlineStr"/>
+    </row>
+    <row r="24">
+      <c r="A24" t="n">
+        <v>127290244</v>
+      </c>
+      <c r="B24" t="n">
+        <v>98436</v>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E24" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H24" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr">
+        <is>
+          <t>22</t>
+        </is>
+      </c>
+      <c r="J24" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K24" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
+      <c r="L24" t="inlineStr"/>
+      <c r="N24" t="inlineStr"/>
+      <c r="P24" t="inlineStr">
+        <is>
+          <t>Österbyggebo, Gstr</t>
+        </is>
+      </c>
+      <c r="Q24" t="n">
+        <v>603911</v>
+      </c>
+      <c r="R24" t="n">
+        <v>6692665</v>
+      </c>
+      <c r="S24" t="n">
+        <v>10</v>
+      </c>
+      <c r="T24" t="inlineStr">
+        <is>
+          <t>Gävleborg</t>
+        </is>
+      </c>
+      <c r="U24" t="inlineStr">
+        <is>
+          <t>Gävle</t>
+        </is>
+      </c>
+      <c r="V24" t="inlineStr">
+        <is>
+          <t>Gästrikland</t>
+        </is>
+      </c>
+      <c r="W24" t="inlineStr">
+        <is>
+          <t>Hedesunda</t>
+        </is>
+      </c>
+      <c r="Y24" t="inlineStr">
+        <is>
+          <t>2025-08-06</t>
+        </is>
+      </c>
+      <c r="AA24" t="inlineStr">
+        <is>
+          <t>2025-08-06</t>
+        </is>
+      </c>
+      <c r="AD24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF24" t="inlineStr"/>
+      <c r="AG24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT24" t="inlineStr"/>
+      <c r="AW24" t="inlineStr">
+        <is>
+          <t>Clara Lerbro</t>
+        </is>
+      </c>
+      <c r="AX24" t="inlineStr">
+        <is>
+          <t>Clara Lerbro, Beke Regelin</t>
+        </is>
+      </c>
+      <c r="AY24" t="inlineStr"/>
+    </row>
+    <row r="25">
+      <c r="A25" t="n">
+        <v>127290238</v>
+      </c>
+      <c r="B25" t="n">
+        <v>98436</v>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E25" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H25" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="J25" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K25" t="inlineStr">
+        <is>
+          <t>överblommad</t>
+        </is>
+      </c>
+      <c r="L25" t="inlineStr"/>
+      <c r="N25" t="inlineStr"/>
+      <c r="P25" t="inlineStr">
+        <is>
+          <t>Österbyggebo, Gstr</t>
+        </is>
+      </c>
+      <c r="Q25" t="n">
+        <v>603891</v>
+      </c>
+      <c r="R25" t="n">
+        <v>6692711</v>
+      </c>
+      <c r="S25" t="n">
+        <v>10</v>
+      </c>
+      <c r="T25" t="inlineStr">
+        <is>
+          <t>Gävleborg</t>
+        </is>
+      </c>
+      <c r="U25" t="inlineStr">
+        <is>
+          <t>Gävle</t>
+        </is>
+      </c>
+      <c r="V25" t="inlineStr">
+        <is>
+          <t>Gästrikland</t>
+        </is>
+      </c>
+      <c r="W25" t="inlineStr">
+        <is>
+          <t>Hedesunda</t>
+        </is>
+      </c>
+      <c r="Y25" t="inlineStr">
+        <is>
+          <t>2025-08-06</t>
+        </is>
+      </c>
+      <c r="AA25" t="inlineStr">
+        <is>
+          <t>2025-08-06</t>
+        </is>
+      </c>
+      <c r="AD25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF25" t="inlineStr"/>
+      <c r="AG25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT25" t="inlineStr"/>
+      <c r="AW25" t="inlineStr">
+        <is>
+          <t>Clara Lerbro</t>
+        </is>
+      </c>
+      <c r="AX25" t="inlineStr">
+        <is>
+          <t>Clara Lerbro, Beke Regelin</t>
+        </is>
+      </c>
+      <c r="AY25" t="inlineStr"/>
+    </row>
+    <row r="26">
+      <c r="A26" t="n">
+        <v>127290246</v>
+      </c>
+      <c r="B26" t="n">
+        <v>92609</v>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E26" t="n">
+        <v>4364</v>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>Dropptaggsvamp</t>
+        </is>
+      </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>Hydnellum ferrugineum</t>
+        </is>
+      </c>
+      <c r="H26" t="inlineStr">
+        <is>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr"/>
+      <c r="P26" t="inlineStr">
+        <is>
+          <t>Österbyggebo, Gstr</t>
+        </is>
+      </c>
+      <c r="Q26" t="n">
+        <v>603977</v>
+      </c>
+      <c r="R26" t="n">
+        <v>6692615</v>
+      </c>
+      <c r="S26" t="n">
+        <v>10</v>
+      </c>
+      <c r="T26" t="inlineStr">
+        <is>
+          <t>Gävleborg</t>
+        </is>
+      </c>
+      <c r="U26" t="inlineStr">
+        <is>
+          <t>Gävle</t>
+        </is>
+      </c>
+      <c r="V26" t="inlineStr">
+        <is>
+          <t>Gästrikland</t>
+        </is>
+      </c>
+      <c r="W26" t="inlineStr">
+        <is>
+          <t>Hedesunda</t>
+        </is>
+      </c>
+      <c r="Y26" t="inlineStr">
+        <is>
+          <t>2025-08-06</t>
+        </is>
+      </c>
+      <c r="AA26" t="inlineStr">
+        <is>
+          <t>2025-08-06</t>
+        </is>
+      </c>
+      <c r="AD26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT26" t="inlineStr"/>
+      <c r="AW26" t="inlineStr">
+        <is>
+          <t>Clara Lerbro</t>
+        </is>
+      </c>
+      <c r="AX26" t="inlineStr">
+        <is>
+          <t>Clara Lerbro, Beke Regelin</t>
+        </is>
+      </c>
+      <c r="AY26" t="inlineStr"/>
+    </row>
+    <row r="27">
+      <c r="A27" t="n">
+        <v>127290225</v>
+      </c>
+      <c r="B27" t="n">
+        <v>98436</v>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E27" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H27" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr">
+        <is>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="J27" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K27" t="inlineStr">
+        <is>
+          <t>överblommad</t>
+        </is>
+      </c>
+      <c r="L27" t="inlineStr"/>
+      <c r="N27" t="inlineStr"/>
+      <c r="P27" t="inlineStr">
+        <is>
+          <t>Österbyggebo, Gstr</t>
+        </is>
+      </c>
+      <c r="Q27" t="n">
+        <v>603879</v>
+      </c>
+      <c r="R27" t="n">
+        <v>6692501</v>
+      </c>
+      <c r="S27" t="n">
+        <v>10</v>
+      </c>
+      <c r="T27" t="inlineStr">
+        <is>
+          <t>Gävleborg</t>
+        </is>
+      </c>
+      <c r="U27" t="inlineStr">
+        <is>
+          <t>Gävle</t>
+        </is>
+      </c>
+      <c r="V27" t="inlineStr">
+        <is>
+          <t>Gästrikland</t>
+        </is>
+      </c>
+      <c r="W27" t="inlineStr">
+        <is>
+          <t>Hedesunda</t>
+        </is>
+      </c>
+      <c r="Y27" t="inlineStr">
+        <is>
+          <t>2025-08-06</t>
+        </is>
+      </c>
+      <c r="AA27" t="inlineStr">
+        <is>
+          <t>2025-08-06</t>
+        </is>
+      </c>
+      <c r="AD27" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE27" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF27" t="inlineStr"/>
+      <c r="AG27" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT27" t="inlineStr"/>
+      <c r="AW27" t="inlineStr">
+        <is>
+          <t>Clara Lerbro</t>
+        </is>
+      </c>
+      <c r="AX27" t="inlineStr">
+        <is>
+          <t>Clara Lerbro, Beke Regelin</t>
+        </is>
+      </c>
+      <c r="AY27" t="inlineStr"/>
+    </row>
+    <row r="28">
+      <c r="A28" t="n">
+        <v>127290242</v>
+      </c>
+      <c r="B28" t="n">
+        <v>98436</v>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E28" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H28" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="J28" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K28" t="inlineStr">
+        <is>
+          <t>överblommad</t>
+        </is>
+      </c>
+      <c r="L28" t="inlineStr"/>
+      <c r="N28" t="inlineStr"/>
+      <c r="P28" t="inlineStr">
+        <is>
+          <t>Österbyggebo, Gstr</t>
+        </is>
+      </c>
+      <c r="Q28" t="n">
+        <v>603879</v>
+      </c>
+      <c r="R28" t="n">
+        <v>6692700</v>
+      </c>
+      <c r="S28" t="n">
+        <v>10</v>
+      </c>
+      <c r="T28" t="inlineStr">
+        <is>
+          <t>Gävleborg</t>
+        </is>
+      </c>
+      <c r="U28" t="inlineStr">
+        <is>
+          <t>Gävle</t>
+        </is>
+      </c>
+      <c r="V28" t="inlineStr">
+        <is>
+          <t>Gästrikland</t>
+        </is>
+      </c>
+      <c r="W28" t="inlineStr">
+        <is>
+          <t>Hedesunda</t>
+        </is>
+      </c>
+      <c r="Y28" t="inlineStr">
+        <is>
+          <t>2025-08-06</t>
+        </is>
+      </c>
+      <c r="AA28" t="inlineStr">
+        <is>
+          <t>2025-08-06</t>
+        </is>
+      </c>
+      <c r="AD28" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE28" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF28" t="inlineStr"/>
+      <c r="AG28" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT28" t="inlineStr"/>
+      <c r="AW28" t="inlineStr">
+        <is>
+          <t>Clara Lerbro</t>
+        </is>
+      </c>
+      <c r="AX28" t="inlineStr">
+        <is>
+          <t>Clara Lerbro, Beke Regelin</t>
+        </is>
+      </c>
+      <c r="AY28" t="inlineStr"/>
+    </row>
+    <row r="29">
+      <c r="A29" t="n">
+        <v>127290232</v>
+      </c>
+      <c r="B29" t="n">
+        <v>98436</v>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E29" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G29" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H29" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="J29" t="inlineStr">
+        <is>
+          <t>dm²</t>
+        </is>
+      </c>
+      <c r="K29" t="inlineStr">
+        <is>
+          <t>överblommad</t>
+        </is>
+      </c>
+      <c r="P29" t="inlineStr">
+        <is>
+          <t>Österbyggebo, Gstr</t>
+        </is>
+      </c>
+      <c r="Q29" t="n">
+        <v>603845</v>
+      </c>
+      <c r="R29" t="n">
+        <v>6692678</v>
+      </c>
+      <c r="S29" t="n">
+        <v>10</v>
+      </c>
+      <c r="T29" t="inlineStr">
+        <is>
+          <t>Gävleborg</t>
+        </is>
+      </c>
+      <c r="U29" t="inlineStr">
+        <is>
+          <t>Gävle</t>
+        </is>
+      </c>
+      <c r="V29" t="inlineStr">
+        <is>
+          <t>Gästrikland</t>
+        </is>
+      </c>
+      <c r="W29" t="inlineStr">
+        <is>
+          <t>Hedesunda</t>
+        </is>
+      </c>
+      <c r="Y29" t="inlineStr">
+        <is>
+          <t>2025-08-06</t>
+        </is>
+      </c>
+      <c r="AA29" t="inlineStr">
+        <is>
+          <t>2025-08-06</t>
+        </is>
+      </c>
+      <c r="AD29" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE29" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG29" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT29" t="inlineStr"/>
+      <c r="AW29" t="inlineStr">
+        <is>
+          <t>Clara Lerbro</t>
+        </is>
+      </c>
+      <c r="AX29" t="inlineStr">
+        <is>
+          <t>Clara Lerbro, Beke Regelin</t>
+        </is>
+      </c>
+      <c r="AY29" t="inlineStr"/>
+    </row>
+    <row r="30">
+      <c r="A30" t="n">
+        <v>127290257</v>
+      </c>
+      <c r="B30" t="n">
+        <v>91284</v>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E30" t="n">
+        <v>5447</v>
+      </c>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>Vedticka</t>
+        </is>
+      </c>
+      <c r="G30" t="inlineStr">
+        <is>
+          <t>Fuscoporia viticola</t>
+        </is>
+      </c>
+      <c r="H30" t="inlineStr">
+        <is>
+          <t>(Schwein.) Murrill</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr"/>
+      <c r="P30" t="inlineStr">
+        <is>
+          <t>Österbyggebo, Gstr</t>
+        </is>
+      </c>
+      <c r="Q30" t="n">
+        <v>603981</v>
+      </c>
+      <c r="R30" t="n">
+        <v>6692457</v>
+      </c>
+      <c r="S30" t="n">
+        <v>10</v>
+      </c>
+      <c r="T30" t="inlineStr">
+        <is>
+          <t>Gävleborg</t>
+        </is>
+      </c>
+      <c r="U30" t="inlineStr">
+        <is>
+          <t>Gävle</t>
+        </is>
+      </c>
+      <c r="V30" t="inlineStr">
+        <is>
+          <t>Gästrikland</t>
+        </is>
+      </c>
+      <c r="W30" t="inlineStr">
+        <is>
+          <t>Hedesunda</t>
+        </is>
+      </c>
+      <c r="Y30" t="inlineStr">
+        <is>
+          <t>2025-08-06</t>
+        </is>
+      </c>
+      <c r="AA30" t="inlineStr">
+        <is>
+          <t>2025-08-06</t>
+        </is>
+      </c>
+      <c r="AD30" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE30" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG30" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT30" t="inlineStr"/>
+      <c r="AW30" t="inlineStr">
+        <is>
+          <t>Clara Lerbro</t>
+        </is>
+      </c>
+      <c r="AX30" t="inlineStr">
+        <is>
+          <t>Clara Lerbro, Beke Regelin</t>
+        </is>
+      </c>
+      <c r="AY30" t="inlineStr"/>
+    </row>
+    <row r="31">
+      <c r="A31" t="n">
+        <v>127290234</v>
+      </c>
+      <c r="B31" t="n">
+        <v>91284</v>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E31" t="n">
+        <v>5447</v>
+      </c>
+      <c r="F31" t="inlineStr">
+        <is>
+          <t>Vedticka</t>
+        </is>
+      </c>
+      <c r="G31" t="inlineStr">
+        <is>
+          <t>Fuscoporia viticola</t>
+        </is>
+      </c>
+      <c r="H31" t="inlineStr">
+        <is>
+          <t>(Schwein.) Murrill</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr"/>
+      <c r="P31" t="inlineStr">
+        <is>
+          <t>Österbyggebo, Gstr</t>
+        </is>
+      </c>
+      <c r="Q31" t="n">
+        <v>603860</v>
+      </c>
+      <c r="R31" t="n">
+        <v>6692678</v>
+      </c>
+      <c r="S31" t="n">
+        <v>10</v>
+      </c>
+      <c r="T31" t="inlineStr">
+        <is>
+          <t>Gävleborg</t>
+        </is>
+      </c>
+      <c r="U31" t="inlineStr">
+        <is>
+          <t>Gävle</t>
+        </is>
+      </c>
+      <c r="V31" t="inlineStr">
+        <is>
+          <t>Gästrikland</t>
+        </is>
+      </c>
+      <c r="W31" t="inlineStr">
+        <is>
+          <t>Hedesunda</t>
+        </is>
+      </c>
+      <c r="Y31" t="inlineStr">
+        <is>
+          <t>2025-08-06</t>
+        </is>
+      </c>
+      <c r="AA31" t="inlineStr">
+        <is>
+          <t>2025-08-06</t>
+        </is>
+      </c>
+      <c r="AD31" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE31" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG31" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT31" t="inlineStr"/>
+      <c r="AW31" t="inlineStr">
+        <is>
+          <t>Clara Lerbro</t>
+        </is>
+      </c>
+      <c r="AX31" t="inlineStr">
+        <is>
+          <t>Clara Lerbro, Beke Regelin</t>
+        </is>
+      </c>
+      <c r="AY31" t="inlineStr"/>
+    </row>
+    <row r="32">
+      <c r="A32" t="n">
+        <v>127290241</v>
+      </c>
+      <c r="B32" t="n">
+        <v>98436</v>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E32" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F32" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G32" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H32" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I32" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="J32" t="inlineStr">
+        <is>
+          <t>dm²</t>
+        </is>
+      </c>
+      <c r="K32" t="inlineStr">
+        <is>
+          <t>överblommad</t>
+        </is>
+      </c>
+      <c r="P32" t="inlineStr">
+        <is>
+          <t>Österbyggebo, Gstr</t>
+        </is>
+      </c>
+      <c r="Q32" t="n">
+        <v>603880</v>
+      </c>
+      <c r="R32" t="n">
+        <v>6692710</v>
+      </c>
+      <c r="S32" t="n">
+        <v>10</v>
+      </c>
+      <c r="T32" t="inlineStr">
+        <is>
+          <t>Gävleborg</t>
+        </is>
+      </c>
+      <c r="U32" t="inlineStr">
+        <is>
+          <t>Gävle</t>
+        </is>
+      </c>
+      <c r="V32" t="inlineStr">
+        <is>
+          <t>Gästrikland</t>
+        </is>
+      </c>
+      <c r="W32" t="inlineStr">
+        <is>
+          <t>Hedesunda</t>
+        </is>
+      </c>
+      <c r="Y32" t="inlineStr">
+        <is>
+          <t>2025-08-06</t>
+        </is>
+      </c>
+      <c r="AA32" t="inlineStr">
+        <is>
+          <t>2025-08-06</t>
+        </is>
+      </c>
+      <c r="AD32" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE32" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG32" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT32" t="inlineStr"/>
+      <c r="AW32" t="inlineStr">
+        <is>
+          <t>Clara Lerbro</t>
+        </is>
+      </c>
+      <c r="AX32" t="inlineStr">
+        <is>
+          <t>Clara Lerbro, Beke Regelin</t>
+        </is>
+      </c>
+      <c r="AY32" t="inlineStr"/>
+    </row>
+    <row r="33">
+      <c r="A33" t="n">
+        <v>127290230</v>
+      </c>
+      <c r="B33" t="n">
+        <v>91284</v>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E33" t="n">
+        <v>5447</v>
+      </c>
+      <c r="F33" t="inlineStr">
+        <is>
+          <t>Vedticka</t>
+        </is>
+      </c>
+      <c r="G33" t="inlineStr">
+        <is>
+          <t>Fuscoporia viticola</t>
+        </is>
+      </c>
+      <c r="H33" t="inlineStr">
+        <is>
+          <t>(Schwein.) Murrill</t>
+        </is>
+      </c>
+      <c r="I33" t="inlineStr"/>
+      <c r="P33" t="inlineStr">
+        <is>
+          <t>Österbyggebo, Gstr</t>
+        </is>
+      </c>
+      <c r="Q33" t="n">
+        <v>603797</v>
+      </c>
+      <c r="R33" t="n">
+        <v>6692638</v>
+      </c>
+      <c r="S33" t="n">
+        <v>10</v>
+      </c>
+      <c r="T33" t="inlineStr">
+        <is>
+          <t>Gävleborg</t>
+        </is>
+      </c>
+      <c r="U33" t="inlineStr">
+        <is>
+          <t>Gävle</t>
+        </is>
+      </c>
+      <c r="V33" t="inlineStr">
+        <is>
+          <t>Gästrikland</t>
+        </is>
+      </c>
+      <c r="W33" t="inlineStr">
+        <is>
+          <t>Hedesunda</t>
+        </is>
+      </c>
+      <c r="Y33" t="inlineStr">
+        <is>
+          <t>2025-08-06</t>
+        </is>
+      </c>
+      <c r="AA33" t="inlineStr">
+        <is>
+          <t>2025-08-06</t>
+        </is>
+      </c>
+      <c r="AD33" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE33" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG33" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT33" t="inlineStr"/>
+      <c r="AW33" t="inlineStr">
+        <is>
+          <t>Clara Lerbro</t>
+        </is>
+      </c>
+      <c r="AX33" t="inlineStr">
+        <is>
+          <t>Clara Lerbro, Beke Regelin</t>
+        </is>
+      </c>
+      <c r="AY33" t="inlineStr"/>
+    </row>
+    <row r="34">
+      <c r="A34" t="n">
+        <v>127290250</v>
+      </c>
+      <c r="B34" t="n">
+        <v>105471</v>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E34" t="n">
+        <v>221144</v>
+      </c>
+      <c r="F34" t="inlineStr">
+        <is>
+          <t>Grönpyrola</t>
+        </is>
+      </c>
+      <c r="G34" t="inlineStr">
+        <is>
+          <t>Pyrola chlorantha</t>
+        </is>
+      </c>
+      <c r="H34" t="inlineStr">
+        <is>
+          <t>Sw.</t>
+        </is>
+      </c>
+      <c r="I34" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="J34" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K34" t="inlineStr"/>
+      <c r="L34" t="inlineStr"/>
+      <c r="N34" t="inlineStr"/>
+      <c r="P34" t="inlineStr">
+        <is>
+          <t>Österbyggebo, Gstr</t>
+        </is>
+      </c>
+      <c r="Q34" t="n">
+        <v>603965</v>
+      </c>
+      <c r="R34" t="n">
+        <v>6692480</v>
+      </c>
+      <c r="S34" t="n">
+        <v>10</v>
+      </c>
+      <c r="T34" t="inlineStr">
+        <is>
+          <t>Gävleborg</t>
+        </is>
+      </c>
+      <c r="U34" t="inlineStr">
+        <is>
+          <t>Gävle</t>
+        </is>
+      </c>
+      <c r="V34" t="inlineStr">
+        <is>
+          <t>Gästrikland</t>
+        </is>
+      </c>
+      <c r="W34" t="inlineStr">
+        <is>
+          <t>Hedesunda</t>
+        </is>
+      </c>
+      <c r="Y34" t="inlineStr">
+        <is>
+          <t>2025-08-06</t>
+        </is>
+      </c>
+      <c r="AA34" t="inlineStr">
+        <is>
+          <t>2025-08-06</t>
+        </is>
+      </c>
+      <c r="AD34" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE34" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF34" t="inlineStr"/>
+      <c r="AG34" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT34" t="inlineStr"/>
+      <c r="AW34" t="inlineStr">
+        <is>
+          <t>Clara Lerbro</t>
+        </is>
+      </c>
+      <c r="AX34" t="inlineStr">
+        <is>
+          <t>Clara Lerbro, Beke Regelin</t>
+        </is>
+      </c>
+      <c r="AY34" t="inlineStr"/>
+    </row>
+    <row r="35">
+      <c r="A35" t="n">
+        <v>127290235</v>
+      </c>
+      <c r="B35" t="n">
+        <v>105471</v>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E35" t="n">
+        <v>221144</v>
+      </c>
+      <c r="F35" t="inlineStr">
+        <is>
+          <t>Grönpyrola</t>
+        </is>
+      </c>
+      <c r="G35" t="inlineStr">
+        <is>
+          <t>Pyrola chlorantha</t>
+        </is>
+      </c>
+      <c r="H35" t="inlineStr">
+        <is>
+          <t>Sw.</t>
+        </is>
+      </c>
+      <c r="I35" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="J35" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K35" t="inlineStr"/>
+      <c r="L35" t="inlineStr"/>
+      <c r="N35" t="inlineStr"/>
+      <c r="P35" t="inlineStr">
+        <is>
+          <t>Österbyggebo, Gstr</t>
+        </is>
+      </c>
+      <c r="Q35" t="n">
+        <v>603865</v>
+      </c>
+      <c r="R35" t="n">
+        <v>6692727</v>
+      </c>
+      <c r="S35" t="n">
+        <v>10</v>
+      </c>
+      <c r="T35" t="inlineStr">
+        <is>
+          <t>Gävleborg</t>
+        </is>
+      </c>
+      <c r="U35" t="inlineStr">
+        <is>
+          <t>Gävle</t>
+        </is>
+      </c>
+      <c r="V35" t="inlineStr">
+        <is>
+          <t>Gästrikland</t>
+        </is>
+      </c>
+      <c r="W35" t="inlineStr">
+        <is>
+          <t>Hedesunda</t>
+        </is>
+      </c>
+      <c r="Y35" t="inlineStr">
+        <is>
+          <t>2025-08-06</t>
+        </is>
+      </c>
+      <c r="AA35" t="inlineStr">
+        <is>
+          <t>2025-08-06</t>
+        </is>
+      </c>
+      <c r="AD35" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE35" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF35" t="inlineStr"/>
+      <c r="AG35" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT35" t="inlineStr"/>
+      <c r="AW35" t="inlineStr">
+        <is>
+          <t>Clara Lerbro</t>
+        </is>
+      </c>
+      <c r="AX35" t="inlineStr">
+        <is>
+          <t>Clara Lerbro, Beke Regelin</t>
+        </is>
+      </c>
+      <c r="AY35" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 31590-2025 artfynd.xlsx
+++ b/artfynd/A 31590-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>127264982</v>
       </c>
       <c r="B2" t="n">
-        <v>98436</v>
+        <v>98442</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -793,7 +793,7 @@
         <v>127283088</v>
       </c>
       <c r="B3" t="n">
-        <v>105471</v>
+        <v>105477</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -894,7 +894,7 @@
         <v>127264978</v>
       </c>
       <c r="B4" t="n">
-        <v>97314</v>
+        <v>97320</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -992,7 +992,7 @@
         <v>127283086</v>
       </c>
       <c r="B5" t="n">
-        <v>98436</v>
+        <v>98442</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1093,7 +1093,7 @@
         <v>127283078</v>
       </c>
       <c r="B6" t="n">
-        <v>91284</v>
+        <v>91290</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1194,7 +1194,7 @@
         <v>127264973</v>
       </c>
       <c r="B7" t="n">
-        <v>97314</v>
+        <v>97320</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1291,7 +1291,7 @@
         <v>127283087</v>
       </c>
       <c r="B8" t="n">
-        <v>105471</v>
+        <v>105477</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1392,7 +1392,7 @@
         <v>127283085</v>
       </c>
       <c r="B9" t="n">
-        <v>98436</v>
+        <v>98442</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1595,7 +1595,7 @@
         <v>127283083</v>
       </c>
       <c r="B11" t="n">
-        <v>92601</v>
+        <v>92607</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1696,7 +1696,7 @@
         <v>127283084</v>
       </c>
       <c r="B12" t="n">
-        <v>98436</v>
+        <v>98442</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1802,7 +1802,7 @@
         <v>127290259</v>
       </c>
       <c r="B13" t="n">
-        <v>98436</v>
+        <v>98442</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1913,61 +1913,45 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>127290258</v>
+        <v>127290233</v>
       </c>
       <c r="B14" t="n">
-        <v>98436</v>
+        <v>91325</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>220787</v>
+        <v>1202</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I14" t="inlineStr">
-        <is>
-          <t>15</t>
-        </is>
-      </c>
-      <c r="J14" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K14" t="inlineStr">
-        <is>
-          <t>överblommad</t>
-        </is>
-      </c>
-      <c r="L14" t="inlineStr"/>
-      <c r="N14" t="inlineStr"/>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
           <t>Österbyggebo, Gstr</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>603981</v>
+        <v>603850</v>
       </c>
       <c r="R14" t="n">
-        <v>6692427</v>
+        <v>6692680</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2008,7 +1992,6 @@
       <c r="AE14" t="b">
         <v>0</v>
       </c>
-      <c r="AF14" t="inlineStr"/>
       <c r="AG14" t="b">
         <v>0</v>
       </c>
@@ -2027,10 +2010,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>127290233</v>
+        <v>127290255</v>
       </c>
       <c r="B15" t="n">
-        <v>91319</v>
+        <v>91339</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2038,21 +2021,21 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>1202</v>
+        <v>1204</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Gränsticka</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Phellopilus nigrolimitatus</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2062,10 +2045,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>603850</v>
+        <v>603980</v>
       </c>
       <c r="R15" t="n">
-        <v>6692680</v>
+        <v>6692483</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2124,45 +2107,49 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>127290255</v>
+        <v>127283080</v>
       </c>
       <c r="B16" t="n">
-        <v>91333</v>
+        <v>56849</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>1204</v>
+        <v>100138</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Gränsticka</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Phellopilus nigrolimitatus</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
+      <c r="K16" t="inlineStr"/>
+      <c r="L16" t="inlineStr"/>
+      <c r="M16" t="inlineStr"/>
+      <c r="N16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
-          <t>Österbyggebo, Gstr</t>
+          <t>Gråtängarna, Gstr</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>603980</v>
+        <v>603972</v>
       </c>
       <c r="R16" t="n">
-        <v>6692483</v>
+        <v>6692667</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2197,6 +2184,11 @@
           <t>2025-08-06</t>
         </is>
       </c>
+      <c r="AC16" t="inlineStr">
+        <is>
+          <t>Fjäder efter en tjädertupp, 32 cm lång</t>
+        </is>
+      </c>
       <c r="AD16" t="b">
         <v>0</v>
       </c>
@@ -2209,61 +2201,73 @@
       <c r="AT16" t="inlineStr"/>
       <c r="AW16" t="inlineStr">
         <is>
-          <t>Clara Lerbro</t>
+          <t>Beke Regelin</t>
         </is>
       </c>
       <c r="AX16" t="inlineStr">
         <is>
-          <t>Clara Lerbro, Beke Regelin</t>
+          <t>Beke Regelin, Clara Lerbro</t>
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>127283080</v>
+        <v>127290258</v>
       </c>
       <c r="B17" t="n">
-        <v>56849</v>
+        <v>98442</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>100138</v>
+        <v>220787</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
-        </is>
-      </c>
-      <c r="I17" t="inlineStr"/>
-      <c r="K17" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="J17" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K17" t="inlineStr">
+        <is>
+          <t>överblommad</t>
+        </is>
+      </c>
       <c r="L17" t="inlineStr"/>
-      <c r="M17" t="inlineStr"/>
       <c r="N17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
-          <t>Gråtängarna, Gstr</t>
+          <t>Österbyggebo, Gstr</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>603972</v>
+        <v>603981</v>
       </c>
       <c r="R17" t="n">
-        <v>6692667</v>
+        <v>6692427</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2298,29 +2302,25 @@
           <t>2025-08-06</t>
         </is>
       </c>
-      <c r="AC17" t="inlineStr">
-        <is>
-          <t>Fjäder efter en tjädertupp, 32 cm lång</t>
-        </is>
-      </c>
       <c r="AD17" t="b">
         <v>0</v>
       </c>
       <c r="AE17" t="b">
         <v>0</v>
       </c>
+      <c r="AF17" t="inlineStr"/>
       <c r="AG17" t="b">
         <v>0</v>
       </c>
       <c r="AT17" t="inlineStr"/>
       <c r="AW17" t="inlineStr">
         <is>
-          <t>Beke Regelin</t>
+          <t>Clara Lerbro</t>
         </is>
       </c>
       <c r="AX17" t="inlineStr">
         <is>
-          <t>Beke Regelin, Clara Lerbro</t>
+          <t>Clara Lerbro, Beke Regelin</t>
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
@@ -2330,7 +2330,7 @@
         <v>127290240</v>
       </c>
       <c r="B18" t="n">
-        <v>98436</v>
+        <v>98442</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2440,7 +2440,7 @@
         <v>127290254</v>
       </c>
       <c r="B19" t="n">
-        <v>91284</v>
+        <v>91290</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2537,7 +2537,7 @@
         <v>127290227</v>
       </c>
       <c r="B20" t="n">
-        <v>91319</v>
+        <v>91325</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2634,7 +2634,7 @@
         <v>127290226</v>
       </c>
       <c r="B21" t="n">
-        <v>92601</v>
+        <v>92607</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2740,32 +2740,32 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>127290260</v>
+        <v>127290239</v>
       </c>
       <c r="B22" t="n">
-        <v>98436</v>
+        <v>91290</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>220787</v>
+        <v>5447</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -2775,10 +2775,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>603977</v>
+        <v>603877</v>
       </c>
       <c r="R22" t="n">
-        <v>6692392</v>
+        <v>6692706</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2837,32 +2837,32 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>127290239</v>
+        <v>127290260</v>
       </c>
       <c r="B23" t="n">
-        <v>91284</v>
+        <v>98442</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>5447</v>
+        <v>220787</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -2872,10 +2872,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>603877</v>
+        <v>603977</v>
       </c>
       <c r="R23" t="n">
-        <v>6692706</v>
+        <v>6692392</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -2937,7 +2937,7 @@
         <v>127290244</v>
       </c>
       <c r="B24" t="n">
-        <v>98436</v>
+        <v>98442</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3051,7 +3051,7 @@
         <v>127290238</v>
       </c>
       <c r="B25" t="n">
-        <v>98436</v>
+        <v>98442</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3165,7 +3165,7 @@
         <v>127290246</v>
       </c>
       <c r="B26" t="n">
-        <v>92609</v>
+        <v>92615</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3262,7 +3262,7 @@
         <v>127290225</v>
       </c>
       <c r="B27" t="n">
-        <v>98436</v>
+        <v>98442</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3376,7 +3376,7 @@
         <v>127290242</v>
       </c>
       <c r="B28" t="n">
-        <v>98436</v>
+        <v>98442</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3490,7 +3490,7 @@
         <v>127290232</v>
       </c>
       <c r="B29" t="n">
-        <v>98436</v>
+        <v>98442</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3601,7 +3601,7 @@
         <v>127290257</v>
       </c>
       <c r="B30" t="n">
-        <v>91284</v>
+        <v>91290</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3698,7 +3698,7 @@
         <v>127290234</v>
       </c>
       <c r="B31" t="n">
-        <v>91284</v>
+        <v>91290</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3795,7 +3795,7 @@
         <v>127290241</v>
       </c>
       <c r="B32" t="n">
-        <v>98436</v>
+        <v>98442</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3906,7 +3906,7 @@
         <v>127290230</v>
       </c>
       <c r="B33" t="n">
-        <v>91284</v>
+        <v>91290</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4003,7 +4003,7 @@
         <v>127290250</v>
       </c>
       <c r="B34" t="n">
-        <v>105471</v>
+        <v>105477</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4113,7 +4113,7 @@
         <v>127290235</v>
       </c>
       <c r="B35" t="n">
-        <v>105471</v>
+        <v>105477</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>

--- a/artfynd/A 31590-2025 artfynd.xlsx
+++ b/artfynd/A 31590-2025 artfynd.xlsx
@@ -1490,45 +1490,48 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>127283076</v>
+        <v>127283083</v>
       </c>
       <c r="B10" t="n">
-        <v>56849</v>
+        <v>92607</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>100138</v>
+        <v>4361</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Orange taggsvamp</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Hydnellum aurantiacum</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Batsch:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
+      <c r="J10" t="inlineStr"/>
+      <c r="K10" t="inlineStr"/>
+      <c r="N10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
           <t>Gråtängarna, Gstr</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>603964</v>
+        <v>603807</v>
       </c>
       <c r="R10" t="n">
-        <v>6692543</v>
+        <v>6692702</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1563,17 +1566,13 @@
           <t>2025-08-06</t>
         </is>
       </c>
-      <c r="AC10" t="inlineStr">
-        <is>
-          <t>spillning</t>
-        </is>
-      </c>
       <c r="AD10" t="b">
         <v>0</v>
       </c>
       <c r="AE10" t="b">
         <v>0</v>
       </c>
+      <c r="AF10" t="inlineStr"/>
       <c r="AG10" t="b">
         <v>0</v>
       </c>
@@ -1592,48 +1591,45 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>127283083</v>
+        <v>127283076</v>
       </c>
       <c r="B11" t="n">
-        <v>92607</v>
+        <v>56849</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>4361</v>
+        <v>100138</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Orange taggsvamp</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Hydnellum aurantiacum</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Batsch:Fr.) P.Karst.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
-      <c r="J11" t="inlineStr"/>
-      <c r="K11" t="inlineStr"/>
-      <c r="N11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
           <t>Gråtängarna, Gstr</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>603807</v>
+        <v>603964</v>
       </c>
       <c r="R11" t="n">
-        <v>6692702</v>
+        <v>6692543</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1668,13 +1664,17 @@
           <t>2025-08-06</t>
         </is>
       </c>
+      <c r="AC11" t="inlineStr">
+        <is>
+          <t>spillning</t>
+        </is>
+      </c>
       <c r="AD11" t="b">
         <v>0</v>
       </c>
       <c r="AE11" t="b">
         <v>0</v>
       </c>
-      <c r="AF11" t="inlineStr"/>
       <c r="AG11" t="b">
         <v>0</v>
       </c>
@@ -2740,32 +2740,32 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>127290239</v>
+        <v>127290260</v>
       </c>
       <c r="B22" t="n">
-        <v>91290</v>
+        <v>98442</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>5447</v>
+        <v>220787</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -2775,10 +2775,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>603877</v>
+        <v>603977</v>
       </c>
       <c r="R22" t="n">
-        <v>6692706</v>
+        <v>6692392</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2837,32 +2837,32 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>127290260</v>
+        <v>127290239</v>
       </c>
       <c r="B23" t="n">
-        <v>98442</v>
+        <v>91290</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>220787</v>
+        <v>5447</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -2872,10 +2872,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>603977</v>
+        <v>603877</v>
       </c>
       <c r="R23" t="n">
-        <v>6692392</v>
+        <v>6692706</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>

--- a/artfynd/A 31590-2025 artfynd.xlsx
+++ b/artfynd/A 31590-2025 artfynd.xlsx
@@ -3695,45 +3695,59 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>127290234</v>
+        <v>127290241</v>
       </c>
       <c r="B31" t="n">
-        <v>91290</v>
+        <v>98442</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>5447</v>
+        <v>220787</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
-        </is>
-      </c>
-      <c r="I31" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="J31" t="inlineStr">
+        <is>
+          <t>dm²</t>
+        </is>
+      </c>
+      <c r="K31" t="inlineStr">
+        <is>
+          <t>överblommad</t>
+        </is>
+      </c>
       <c r="P31" t="inlineStr">
         <is>
           <t>Österbyggebo, Gstr</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>603860</v>
+        <v>603880</v>
       </c>
       <c r="R31" t="n">
-        <v>6692678</v>
+        <v>6692710</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3792,59 +3806,45 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>127290241</v>
+        <v>127290234</v>
       </c>
       <c r="B32" t="n">
-        <v>98442</v>
+        <v>91290</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>220787</v>
+        <v>5447</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I32" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="J32" t="inlineStr">
-        <is>
-          <t>dm²</t>
-        </is>
-      </c>
-      <c r="K32" t="inlineStr">
-        <is>
-          <t>överblommad</t>
-        </is>
-      </c>
+          <t>(Schwein.) Murrill</t>
+        </is>
+      </c>
+      <c r="I32" t="inlineStr"/>
       <c r="P32" t="inlineStr">
         <is>
           <t>Österbyggebo, Gstr</t>
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>603880</v>
+        <v>603860</v>
       </c>
       <c r="R32" t="n">
-        <v>6692710</v>
+        <v>6692678</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>

--- a/artfynd/A 31590-2025 artfynd.xlsx
+++ b/artfynd/A 31590-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>127264982</v>
       </c>
       <c r="B2" t="n">
-        <v>98442</v>
+        <v>98443</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -793,7 +793,7 @@
         <v>127283088</v>
       </c>
       <c r="B3" t="n">
-        <v>105477</v>
+        <v>105478</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -894,7 +894,7 @@
         <v>127264978</v>
       </c>
       <c r="B4" t="n">
-        <v>97320</v>
+        <v>97321</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -992,7 +992,7 @@
         <v>127283086</v>
       </c>
       <c r="B5" t="n">
-        <v>98442</v>
+        <v>98443</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1093,7 +1093,7 @@
         <v>127283078</v>
       </c>
       <c r="B6" t="n">
-        <v>91290</v>
+        <v>91291</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1194,7 +1194,7 @@
         <v>127264973</v>
       </c>
       <c r="B7" t="n">
-        <v>97320</v>
+        <v>97321</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1291,7 +1291,7 @@
         <v>127283087</v>
       </c>
       <c r="B8" t="n">
-        <v>105477</v>
+        <v>105478</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1392,7 +1392,7 @@
         <v>127283085</v>
       </c>
       <c r="B9" t="n">
-        <v>98442</v>
+        <v>98443</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1493,7 +1493,7 @@
         <v>127283083</v>
       </c>
       <c r="B10" t="n">
-        <v>92607</v>
+        <v>92608</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1696,7 +1696,7 @@
         <v>127283084</v>
       </c>
       <c r="B12" t="n">
-        <v>98442</v>
+        <v>98443</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1802,7 +1802,7 @@
         <v>127290259</v>
       </c>
       <c r="B13" t="n">
-        <v>98442</v>
+        <v>98443</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1913,45 +1913,61 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>127290233</v>
+        <v>127290258</v>
       </c>
       <c r="B14" t="n">
-        <v>91325</v>
+        <v>98443</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>1202</v>
+        <v>220787</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I14" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="J14" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K14" t="inlineStr">
+        <is>
+          <t>överblommad</t>
+        </is>
+      </c>
+      <c r="L14" t="inlineStr"/>
+      <c r="N14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
           <t>Österbyggebo, Gstr</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>603850</v>
+        <v>603981</v>
       </c>
       <c r="R14" t="n">
-        <v>6692680</v>
+        <v>6692427</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -1992,6 +2008,7 @@
       <c r="AE14" t="b">
         <v>0</v>
       </c>
+      <c r="AF14" t="inlineStr"/>
       <c r="AG14" t="b">
         <v>0</v>
       </c>
@@ -2010,10 +2027,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>127290255</v>
+        <v>127290233</v>
       </c>
       <c r="B15" t="n">
-        <v>91339</v>
+        <v>91326</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2021,21 +2038,21 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>1204</v>
+        <v>1202</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Gränsticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Phellopilus nigrolimitatus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2045,10 +2062,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>603980</v>
+        <v>603850</v>
       </c>
       <c r="R15" t="n">
-        <v>6692483</v>
+        <v>6692680</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2107,49 +2124,45 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>127283080</v>
+        <v>127290255</v>
       </c>
       <c r="B16" t="n">
-        <v>56849</v>
+        <v>91340</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>100138</v>
+        <v>1204</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Gränsticka</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Phellopilus nigrolimitatus</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
-      <c r="K16" t="inlineStr"/>
-      <c r="L16" t="inlineStr"/>
-      <c r="M16" t="inlineStr"/>
-      <c r="N16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
-          <t>Gråtängarna, Gstr</t>
+          <t>Österbyggebo, Gstr</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>603972</v>
+        <v>603980</v>
       </c>
       <c r="R16" t="n">
-        <v>6692667</v>
+        <v>6692483</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2184,11 +2197,6 @@
           <t>2025-08-06</t>
         </is>
       </c>
-      <c r="AC16" t="inlineStr">
-        <is>
-          <t>Fjäder efter en tjädertupp, 32 cm lång</t>
-        </is>
-      </c>
       <c r="AD16" t="b">
         <v>0</v>
       </c>
@@ -2201,73 +2209,61 @@
       <c r="AT16" t="inlineStr"/>
       <c r="AW16" t="inlineStr">
         <is>
-          <t>Beke Regelin</t>
+          <t>Clara Lerbro</t>
         </is>
       </c>
       <c r="AX16" t="inlineStr">
         <is>
-          <t>Beke Regelin, Clara Lerbro</t>
+          <t>Clara Lerbro, Beke Regelin</t>
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>127290258</v>
+        <v>127283080</v>
       </c>
       <c r="B17" t="n">
-        <v>98442</v>
+        <v>56849</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>220787</v>
+        <v>100138</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I17" t="inlineStr">
-        <is>
-          <t>15</t>
-        </is>
-      </c>
-      <c r="J17" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K17" t="inlineStr">
-        <is>
-          <t>överblommad</t>
-        </is>
-      </c>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr"/>
+      <c r="K17" t="inlineStr"/>
       <c r="L17" t="inlineStr"/>
+      <c r="M17" t="inlineStr"/>
       <c r="N17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
-          <t>Österbyggebo, Gstr</t>
+          <t>Gråtängarna, Gstr</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>603981</v>
+        <v>603972</v>
       </c>
       <c r="R17" t="n">
-        <v>6692427</v>
+        <v>6692667</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2302,25 +2298,29 @@
           <t>2025-08-06</t>
         </is>
       </c>
+      <c r="AC17" t="inlineStr">
+        <is>
+          <t>Fjäder efter en tjädertupp, 32 cm lång</t>
+        </is>
+      </c>
       <c r="AD17" t="b">
         <v>0</v>
       </c>
       <c r="AE17" t="b">
         <v>0</v>
       </c>
-      <c r="AF17" t="inlineStr"/>
       <c r="AG17" t="b">
         <v>0</v>
       </c>
       <c r="AT17" t="inlineStr"/>
       <c r="AW17" t="inlineStr">
         <is>
-          <t>Clara Lerbro</t>
+          <t>Beke Regelin</t>
         </is>
       </c>
       <c r="AX17" t="inlineStr">
         <is>
-          <t>Clara Lerbro, Beke Regelin</t>
+          <t>Beke Regelin, Clara Lerbro</t>
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
@@ -2330,7 +2330,7 @@
         <v>127290240</v>
       </c>
       <c r="B18" t="n">
-        <v>98442</v>
+        <v>98443</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2440,7 +2440,7 @@
         <v>127290254</v>
       </c>
       <c r="B19" t="n">
-        <v>91290</v>
+        <v>91291</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2537,7 +2537,7 @@
         <v>127290227</v>
       </c>
       <c r="B20" t="n">
-        <v>91325</v>
+        <v>91326</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2634,7 +2634,7 @@
         <v>127290226</v>
       </c>
       <c r="B21" t="n">
-        <v>92607</v>
+        <v>92608</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2740,32 +2740,32 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>127290260</v>
+        <v>127290239</v>
       </c>
       <c r="B22" t="n">
-        <v>98442</v>
+        <v>91291</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>220787</v>
+        <v>5447</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -2775,10 +2775,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>603977</v>
+        <v>603877</v>
       </c>
       <c r="R22" t="n">
-        <v>6692392</v>
+        <v>6692706</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2837,32 +2837,32 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>127290239</v>
+        <v>127290260</v>
       </c>
       <c r="B23" t="n">
-        <v>91290</v>
+        <v>98443</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>5447</v>
+        <v>220787</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -2872,10 +2872,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>603877</v>
+        <v>603977</v>
       </c>
       <c r="R23" t="n">
-        <v>6692706</v>
+        <v>6692392</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -2937,7 +2937,7 @@
         <v>127290244</v>
       </c>
       <c r="B24" t="n">
-        <v>98442</v>
+        <v>98443</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3051,7 +3051,7 @@
         <v>127290238</v>
       </c>
       <c r="B25" t="n">
-        <v>98442</v>
+        <v>98443</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3165,7 +3165,7 @@
         <v>127290246</v>
       </c>
       <c r="B26" t="n">
-        <v>92615</v>
+        <v>92616</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3262,7 +3262,7 @@
         <v>127290225</v>
       </c>
       <c r="B27" t="n">
-        <v>98442</v>
+        <v>98443</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3373,10 +3373,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>127290242</v>
+        <v>127290232</v>
       </c>
       <c r="B28" t="n">
-        <v>98442</v>
+        <v>98443</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3403,12 +3403,12 @@
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>4</t>
         </is>
       </c>
       <c r="J28" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
+          <t>dm²</t>
         </is>
       </c>
       <c r="K28" t="inlineStr">
@@ -3416,18 +3416,16 @@
           <t>överblommad</t>
         </is>
       </c>
-      <c r="L28" t="inlineStr"/>
-      <c r="N28" t="inlineStr"/>
       <c r="P28" t="inlineStr">
         <is>
           <t>Österbyggebo, Gstr</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>603879</v>
+        <v>603845</v>
       </c>
       <c r="R28" t="n">
-        <v>6692700</v>
+        <v>6692678</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3468,7 +3466,6 @@
       <c r="AE28" t="b">
         <v>0</v>
       </c>
-      <c r="AF28" t="inlineStr"/>
       <c r="AG28" t="b">
         <v>0</v>
       </c>
@@ -3487,10 +3484,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>127290232</v>
+        <v>127290242</v>
       </c>
       <c r="B29" t="n">
-        <v>98442</v>
+        <v>98443</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3517,12 +3514,12 @@
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>9</t>
         </is>
       </c>
       <c r="J29" t="inlineStr">
         <is>
-          <t>dm²</t>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="K29" t="inlineStr">
@@ -3530,16 +3527,18 @@
           <t>överblommad</t>
         </is>
       </c>
+      <c r="L29" t="inlineStr"/>
+      <c r="N29" t="inlineStr"/>
       <c r="P29" t="inlineStr">
         <is>
           <t>Österbyggebo, Gstr</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>603845</v>
+        <v>603879</v>
       </c>
       <c r="R29" t="n">
-        <v>6692678</v>
+        <v>6692700</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3580,6 +3579,7 @@
       <c r="AE29" t="b">
         <v>0</v>
       </c>
+      <c r="AF29" t="inlineStr"/>
       <c r="AG29" t="b">
         <v>0</v>
       </c>
@@ -3601,7 +3601,7 @@
         <v>127290257</v>
       </c>
       <c r="B30" t="n">
-        <v>91290</v>
+        <v>91291</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3695,59 +3695,45 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>127290241</v>
+        <v>127290234</v>
       </c>
       <c r="B31" t="n">
-        <v>98442</v>
+        <v>91291</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>220787</v>
+        <v>5447</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I31" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="J31" t="inlineStr">
-        <is>
-          <t>dm²</t>
-        </is>
-      </c>
-      <c r="K31" t="inlineStr">
-        <is>
-          <t>överblommad</t>
-        </is>
-      </c>
+          <t>(Schwein.) Murrill</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr"/>
       <c r="P31" t="inlineStr">
         <is>
           <t>Österbyggebo, Gstr</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>603880</v>
+        <v>603860</v>
       </c>
       <c r="R31" t="n">
-        <v>6692710</v>
+        <v>6692678</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3806,45 +3792,59 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>127290234</v>
+        <v>127290241</v>
       </c>
       <c r="B32" t="n">
-        <v>91290</v>
+        <v>98443</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>5447</v>
+        <v>220787</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
-        </is>
-      </c>
-      <c r="I32" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I32" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="J32" t="inlineStr">
+        <is>
+          <t>dm²</t>
+        </is>
+      </c>
+      <c r="K32" t="inlineStr">
+        <is>
+          <t>överblommad</t>
+        </is>
+      </c>
       <c r="P32" t="inlineStr">
         <is>
           <t>Österbyggebo, Gstr</t>
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>603860</v>
+        <v>603880</v>
       </c>
       <c r="R32" t="n">
-        <v>6692678</v>
+        <v>6692710</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -3906,7 +3906,7 @@
         <v>127290230</v>
       </c>
       <c r="B33" t="n">
-        <v>91290</v>
+        <v>91291</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4003,7 +4003,7 @@
         <v>127290250</v>
       </c>
       <c r="B34" t="n">
-        <v>105477</v>
+        <v>105478</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4113,7 +4113,7 @@
         <v>127290235</v>
       </c>
       <c r="B35" t="n">
-        <v>105477</v>
+        <v>105478</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>

--- a/artfynd/A 31590-2025 artfynd.xlsx
+++ b/artfynd/A 31590-2025 artfynd.xlsx
@@ -1913,61 +1913,45 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>127290258</v>
+        <v>127290233</v>
       </c>
       <c r="B14" t="n">
-        <v>98443</v>
+        <v>91326</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>220787</v>
+        <v>1202</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I14" t="inlineStr">
-        <is>
-          <t>15</t>
-        </is>
-      </c>
-      <c r="J14" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K14" t="inlineStr">
-        <is>
-          <t>överblommad</t>
-        </is>
-      </c>
-      <c r="L14" t="inlineStr"/>
-      <c r="N14" t="inlineStr"/>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
           <t>Österbyggebo, Gstr</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>603981</v>
+        <v>603850</v>
       </c>
       <c r="R14" t="n">
-        <v>6692427</v>
+        <v>6692680</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2008,7 +1992,6 @@
       <c r="AE14" t="b">
         <v>0</v>
       </c>
-      <c r="AF14" t="inlineStr"/>
       <c r="AG14" t="b">
         <v>0</v>
       </c>
@@ -2027,10 +2010,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>127290233</v>
+        <v>127290255</v>
       </c>
       <c r="B15" t="n">
-        <v>91326</v>
+        <v>91340</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2038,21 +2021,21 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>1202</v>
+        <v>1204</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Gränsticka</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Phellopilus nigrolimitatus</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2062,10 +2045,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>603850</v>
+        <v>603980</v>
       </c>
       <c r="R15" t="n">
-        <v>6692680</v>
+        <v>6692483</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2124,45 +2107,49 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>127290255</v>
+        <v>127283080</v>
       </c>
       <c r="B16" t="n">
-        <v>91340</v>
+        <v>56849</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>1204</v>
+        <v>100138</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Gränsticka</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Phellopilus nigrolimitatus</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
+      <c r="K16" t="inlineStr"/>
+      <c r="L16" t="inlineStr"/>
+      <c r="M16" t="inlineStr"/>
+      <c r="N16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
-          <t>Österbyggebo, Gstr</t>
+          <t>Gråtängarna, Gstr</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>603980</v>
+        <v>603972</v>
       </c>
       <c r="R16" t="n">
-        <v>6692483</v>
+        <v>6692667</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2197,6 +2184,11 @@
           <t>2025-08-06</t>
         </is>
       </c>
+      <c r="AC16" t="inlineStr">
+        <is>
+          <t>Fjäder efter en tjädertupp, 32 cm lång</t>
+        </is>
+      </c>
       <c r="AD16" t="b">
         <v>0</v>
       </c>
@@ -2209,61 +2201,73 @@
       <c r="AT16" t="inlineStr"/>
       <c r="AW16" t="inlineStr">
         <is>
-          <t>Clara Lerbro</t>
+          <t>Beke Regelin</t>
         </is>
       </c>
       <c r="AX16" t="inlineStr">
         <is>
-          <t>Clara Lerbro, Beke Regelin</t>
+          <t>Beke Regelin, Clara Lerbro</t>
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>127283080</v>
+        <v>127290258</v>
       </c>
       <c r="B17" t="n">
-        <v>56849</v>
+        <v>98443</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>100138</v>
+        <v>220787</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
-        </is>
-      </c>
-      <c r="I17" t="inlineStr"/>
-      <c r="K17" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="J17" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K17" t="inlineStr">
+        <is>
+          <t>överblommad</t>
+        </is>
+      </c>
       <c r="L17" t="inlineStr"/>
-      <c r="M17" t="inlineStr"/>
       <c r="N17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
-          <t>Gråtängarna, Gstr</t>
+          <t>Österbyggebo, Gstr</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>603972</v>
+        <v>603981</v>
       </c>
       <c r="R17" t="n">
-        <v>6692667</v>
+        <v>6692427</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2298,29 +2302,25 @@
           <t>2025-08-06</t>
         </is>
       </c>
-      <c r="AC17" t="inlineStr">
-        <is>
-          <t>Fjäder efter en tjädertupp, 32 cm lång</t>
-        </is>
-      </c>
       <c r="AD17" t="b">
         <v>0</v>
       </c>
       <c r="AE17" t="b">
         <v>0</v>
       </c>
+      <c r="AF17" t="inlineStr"/>
       <c r="AG17" t="b">
         <v>0</v>
       </c>
       <c r="AT17" t="inlineStr"/>
       <c r="AW17" t="inlineStr">
         <is>
-          <t>Beke Regelin</t>
+          <t>Clara Lerbro</t>
         </is>
       </c>
       <c r="AX17" t="inlineStr">
         <is>
-          <t>Beke Regelin, Clara Lerbro</t>
+          <t>Clara Lerbro, Beke Regelin</t>
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>

--- a/artfynd/A 31590-2025 artfynd.xlsx
+++ b/artfynd/A 31590-2025 artfynd.xlsx
@@ -2631,56 +2631,45 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>127290226</v>
+        <v>127290260</v>
       </c>
       <c r="B21" t="n">
-        <v>92608</v>
+        <v>98443</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>4361</v>
+        <v>220787</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Orange taggsvamp</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Hydnellum aurantiacum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Batsch:Fr.) P.Karst.</t>
-        </is>
-      </c>
-      <c r="I21" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="J21" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
-      <c r="K21" t="inlineStr"/>
-      <c r="N21" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
           <t>Österbyggebo, Gstr</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>603857</v>
+        <v>603977</v>
       </c>
       <c r="R21" t="n">
-        <v>6692565</v>
+        <v>6692392</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2721,7 +2710,6 @@
       <c r="AE21" t="b">
         <v>0</v>
       </c>
-      <c r="AF21" t="inlineStr"/>
       <c r="AG21" t="b">
         <v>0</v>
       </c>
@@ -2740,45 +2728,56 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>127290239</v>
+        <v>127290226</v>
       </c>
       <c r="B22" t="n">
-        <v>91291</v>
+        <v>92608</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>5447</v>
+        <v>4361</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Orange taggsvamp</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Hydnellum aurantiacum</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
-        </is>
-      </c>
-      <c r="I22" t="inlineStr"/>
+          <t>(Batsch:Fr.) P.Karst.</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J22" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
+      <c r="K22" t="inlineStr"/>
+      <c r="N22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
           <t>Österbyggebo, Gstr</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>603877</v>
+        <v>603857</v>
       </c>
       <c r="R22" t="n">
-        <v>6692706</v>
+        <v>6692565</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2819,6 +2818,7 @@
       <c r="AE22" t="b">
         <v>0</v>
       </c>
+      <c r="AF22" t="inlineStr"/>
       <c r="AG22" t="b">
         <v>0</v>
       </c>
@@ -2837,32 +2837,32 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>127290260</v>
+        <v>127290239</v>
       </c>
       <c r="B23" t="n">
-        <v>98443</v>
+        <v>91291</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>220787</v>
+        <v>5447</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -2872,10 +2872,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>603977</v>
+        <v>603877</v>
       </c>
       <c r="R23" t="n">
-        <v>6692392</v>
+        <v>6692706</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3373,7 +3373,7 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>127290232</v>
+        <v>127290242</v>
       </c>
       <c r="B28" t="n">
         <v>98443</v>
@@ -3403,12 +3403,12 @@
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>9</t>
         </is>
       </c>
       <c r="J28" t="inlineStr">
         <is>
-          <t>dm²</t>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="K28" t="inlineStr">
@@ -3416,16 +3416,18 @@
           <t>överblommad</t>
         </is>
       </c>
+      <c r="L28" t="inlineStr"/>
+      <c r="N28" t="inlineStr"/>
       <c r="P28" t="inlineStr">
         <is>
           <t>Österbyggebo, Gstr</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>603845</v>
+        <v>603879</v>
       </c>
       <c r="R28" t="n">
-        <v>6692678</v>
+        <v>6692700</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3466,6 +3468,7 @@
       <c r="AE28" t="b">
         <v>0</v>
       </c>
+      <c r="AF28" t="inlineStr"/>
       <c r="AG28" t="b">
         <v>0</v>
       </c>
@@ -3484,7 +3487,7 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>127290242</v>
+        <v>127290232</v>
       </c>
       <c r="B29" t="n">
         <v>98443</v>
@@ -3514,12 +3517,12 @@
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>4</t>
         </is>
       </c>
       <c r="J29" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
+          <t>dm²</t>
         </is>
       </c>
       <c r="K29" t="inlineStr">
@@ -3527,18 +3530,16 @@
           <t>överblommad</t>
         </is>
       </c>
-      <c r="L29" t="inlineStr"/>
-      <c r="N29" t="inlineStr"/>
       <c r="P29" t="inlineStr">
         <is>
           <t>Österbyggebo, Gstr</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>603879</v>
+        <v>603845</v>
       </c>
       <c r="R29" t="n">
-        <v>6692700</v>
+        <v>6692678</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3579,7 +3580,6 @@
       <c r="AE29" t="b">
         <v>0</v>
       </c>
-      <c r="AF29" t="inlineStr"/>
       <c r="AG29" t="b">
         <v>0</v>
       </c>

--- a/artfynd/A 31590-2025 artfynd.xlsx
+++ b/artfynd/A 31590-2025 artfynd.xlsx
@@ -1913,45 +1913,61 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>127290233</v>
+        <v>127290258</v>
       </c>
       <c r="B14" t="n">
-        <v>91326</v>
+        <v>98443</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>1202</v>
+        <v>220787</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I14" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="J14" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K14" t="inlineStr">
+        <is>
+          <t>överblommad</t>
+        </is>
+      </c>
+      <c r="L14" t="inlineStr"/>
+      <c r="N14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
           <t>Österbyggebo, Gstr</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>603850</v>
+        <v>603981</v>
       </c>
       <c r="R14" t="n">
-        <v>6692680</v>
+        <v>6692427</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -1992,6 +2008,7 @@
       <c r="AE14" t="b">
         <v>0</v>
       </c>
+      <c r="AF14" t="inlineStr"/>
       <c r="AG14" t="b">
         <v>0</v>
       </c>
@@ -2010,10 +2027,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>127290255</v>
+        <v>127290233</v>
       </c>
       <c r="B15" t="n">
-        <v>91340</v>
+        <v>91326</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2021,21 +2038,21 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>1204</v>
+        <v>1202</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Gränsticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Phellopilus nigrolimitatus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2045,10 +2062,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>603980</v>
+        <v>603850</v>
       </c>
       <c r="R15" t="n">
-        <v>6692483</v>
+        <v>6692680</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2107,49 +2124,45 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>127283080</v>
+        <v>127290255</v>
       </c>
       <c r="B16" t="n">
-        <v>56849</v>
+        <v>91340</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>100138</v>
+        <v>1204</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Gränsticka</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Phellopilus nigrolimitatus</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
-      <c r="K16" t="inlineStr"/>
-      <c r="L16" t="inlineStr"/>
-      <c r="M16" t="inlineStr"/>
-      <c r="N16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
-          <t>Gråtängarna, Gstr</t>
+          <t>Österbyggebo, Gstr</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>603972</v>
+        <v>603980</v>
       </c>
       <c r="R16" t="n">
-        <v>6692667</v>
+        <v>6692483</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2184,11 +2197,6 @@
           <t>2025-08-06</t>
         </is>
       </c>
-      <c r="AC16" t="inlineStr">
-        <is>
-          <t>Fjäder efter en tjädertupp, 32 cm lång</t>
-        </is>
-      </c>
       <c r="AD16" t="b">
         <v>0</v>
       </c>
@@ -2201,73 +2209,61 @@
       <c r="AT16" t="inlineStr"/>
       <c r="AW16" t="inlineStr">
         <is>
-          <t>Beke Regelin</t>
+          <t>Clara Lerbro</t>
         </is>
       </c>
       <c r="AX16" t="inlineStr">
         <is>
-          <t>Beke Regelin, Clara Lerbro</t>
+          <t>Clara Lerbro, Beke Regelin</t>
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>127290258</v>
+        <v>127283080</v>
       </c>
       <c r="B17" t="n">
-        <v>98443</v>
+        <v>56849</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>220787</v>
+        <v>100138</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I17" t="inlineStr">
-        <is>
-          <t>15</t>
-        </is>
-      </c>
-      <c r="J17" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K17" t="inlineStr">
-        <is>
-          <t>överblommad</t>
-        </is>
-      </c>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr"/>
+      <c r="K17" t="inlineStr"/>
       <c r="L17" t="inlineStr"/>
+      <c r="M17" t="inlineStr"/>
       <c r="N17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
-          <t>Österbyggebo, Gstr</t>
+          <t>Gråtängarna, Gstr</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>603981</v>
+        <v>603972</v>
       </c>
       <c r="R17" t="n">
-        <v>6692427</v>
+        <v>6692667</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2302,25 +2298,29 @@
           <t>2025-08-06</t>
         </is>
       </c>
+      <c r="AC17" t="inlineStr">
+        <is>
+          <t>Fjäder efter en tjädertupp, 32 cm lång</t>
+        </is>
+      </c>
       <c r="AD17" t="b">
         <v>0</v>
       </c>
       <c r="AE17" t="b">
         <v>0</v>
       </c>
-      <c r="AF17" t="inlineStr"/>
       <c r="AG17" t="b">
         <v>0</v>
       </c>
       <c r="AT17" t="inlineStr"/>
       <c r="AW17" t="inlineStr">
         <is>
-          <t>Clara Lerbro</t>
+          <t>Beke Regelin</t>
         </is>
       </c>
       <c r="AX17" t="inlineStr">
         <is>
-          <t>Clara Lerbro, Beke Regelin</t>
+          <t>Beke Regelin, Clara Lerbro</t>
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
@@ -2631,45 +2631,56 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>127290260</v>
+        <v>127290226</v>
       </c>
       <c r="B21" t="n">
-        <v>98443</v>
+        <v>92608</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>220787</v>
+        <v>4361</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Orange taggsvamp</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hydnellum aurantiacum</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I21" t="inlineStr"/>
+          <t>(Batsch:Fr.) P.Karst.</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J21" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
+      <c r="K21" t="inlineStr"/>
+      <c r="N21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
           <t>Österbyggebo, Gstr</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>603977</v>
+        <v>603857</v>
       </c>
       <c r="R21" t="n">
-        <v>6692392</v>
+        <v>6692565</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2710,6 +2721,7 @@
       <c r="AE21" t="b">
         <v>0</v>
       </c>
+      <c r="AF21" t="inlineStr"/>
       <c r="AG21" t="b">
         <v>0</v>
       </c>
@@ -2728,56 +2740,45 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>127290226</v>
+        <v>127290239</v>
       </c>
       <c r="B22" t="n">
-        <v>92608</v>
+        <v>91291</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>4361</v>
+        <v>5447</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Orange taggsvamp</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Hydnellum aurantiacum</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Batsch:Fr.) P.Karst.</t>
-        </is>
-      </c>
-      <c r="I22" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="J22" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
-      <c r="K22" t="inlineStr"/>
-      <c r="N22" t="inlineStr"/>
+          <t>(Schwein.) Murrill</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
           <t>Österbyggebo, Gstr</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>603857</v>
+        <v>603877</v>
       </c>
       <c r="R22" t="n">
-        <v>6692565</v>
+        <v>6692706</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2818,7 +2819,6 @@
       <c r="AE22" t="b">
         <v>0</v>
       </c>
-      <c r="AF22" t="inlineStr"/>
       <c r="AG22" t="b">
         <v>0</v>
       </c>
@@ -2837,32 +2837,32 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>127290239</v>
+        <v>127290260</v>
       </c>
       <c r="B23" t="n">
-        <v>91291</v>
+        <v>98443</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>5447</v>
+        <v>220787</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -2872,10 +2872,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>603877</v>
+        <v>603977</v>
       </c>
       <c r="R23" t="n">
-        <v>6692706</v>
+        <v>6692392</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -4000,7 +4000,7 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>127290250</v>
+        <v>127290235</v>
       </c>
       <c r="B34" t="n">
         <v>105478</v>
@@ -4030,7 +4030,7 @@
       </c>
       <c r="I34" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>11</t>
         </is>
       </c>
       <c r="J34" t="inlineStr">
@@ -4047,10 +4047,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>603965</v>
+        <v>603865</v>
       </c>
       <c r="R34" t="n">
-        <v>6692480</v>
+        <v>6692727</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4110,7 +4110,7 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>127290235</v>
+        <v>127290250</v>
       </c>
       <c r="B35" t="n">
         <v>105478</v>
@@ -4140,7 +4140,7 @@
       </c>
       <c r="I35" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>6</t>
         </is>
       </c>
       <c r="J35" t="inlineStr">
@@ -4157,10 +4157,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>603865</v>
+        <v>603965</v>
       </c>
       <c r="R35" t="n">
-        <v>6692727</v>
+        <v>6692480</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>

--- a/artfynd/A 31590-2025 artfynd.xlsx
+++ b/artfynd/A 31590-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>127264982</v>
       </c>
       <c r="B2" t="n">
-        <v>98443</v>
+        <v>98447</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -793,7 +793,7 @@
         <v>127283088</v>
       </c>
       <c r="B3" t="n">
-        <v>105478</v>
+        <v>105484</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -894,7 +894,7 @@
         <v>127264978</v>
       </c>
       <c r="B4" t="n">
-        <v>97321</v>
+        <v>97325</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -992,7 +992,7 @@
         <v>127283086</v>
       </c>
       <c r="B5" t="n">
-        <v>98443</v>
+        <v>98447</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1093,7 +1093,7 @@
         <v>127283078</v>
       </c>
       <c r="B6" t="n">
-        <v>91291</v>
+        <v>91295</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1194,7 +1194,7 @@
         <v>127264973</v>
       </c>
       <c r="B7" t="n">
-        <v>97321</v>
+        <v>97325</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1291,7 +1291,7 @@
         <v>127283087</v>
       </c>
       <c r="B8" t="n">
-        <v>105478</v>
+        <v>105484</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1392,7 +1392,7 @@
         <v>127283085</v>
       </c>
       <c r="B9" t="n">
-        <v>98443</v>
+        <v>98447</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1490,48 +1490,45 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>127283083</v>
+        <v>127283076</v>
       </c>
       <c r="B10" t="n">
-        <v>92608</v>
+        <v>56853</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>4361</v>
+        <v>100138</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Orange taggsvamp</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Hydnellum aurantiacum</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Batsch:Fr.) P.Karst.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
-      <c r="J10" t="inlineStr"/>
-      <c r="K10" t="inlineStr"/>
-      <c r="N10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
           <t>Gråtängarna, Gstr</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>603807</v>
+        <v>603964</v>
       </c>
       <c r="R10" t="n">
-        <v>6692702</v>
+        <v>6692543</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1566,13 +1563,17 @@
           <t>2025-08-06</t>
         </is>
       </c>
+      <c r="AC10" t="inlineStr">
+        <is>
+          <t>spillning</t>
+        </is>
+      </c>
       <c r="AD10" t="b">
         <v>0</v>
       </c>
       <c r="AE10" t="b">
         <v>0</v>
       </c>
-      <c r="AF10" t="inlineStr"/>
       <c r="AG10" t="b">
         <v>0</v>
       </c>
@@ -1591,45 +1592,48 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>127283076</v>
+        <v>127283083</v>
       </c>
       <c r="B11" t="n">
-        <v>56849</v>
+        <v>92612</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>100138</v>
+        <v>4361</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Orange taggsvamp</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Hydnellum aurantiacum</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Batsch:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
+      <c r="J11" t="inlineStr"/>
+      <c r="K11" t="inlineStr"/>
+      <c r="N11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
           <t>Gråtängarna, Gstr</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>603964</v>
+        <v>603807</v>
       </c>
       <c r="R11" t="n">
-        <v>6692543</v>
+        <v>6692702</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1664,17 +1668,13 @@
           <t>2025-08-06</t>
         </is>
       </c>
-      <c r="AC11" t="inlineStr">
-        <is>
-          <t>spillning</t>
-        </is>
-      </c>
       <c r="AD11" t="b">
         <v>0</v>
       </c>
       <c r="AE11" t="b">
         <v>0</v>
       </c>
+      <c r="AF11" t="inlineStr"/>
       <c r="AG11" t="b">
         <v>0</v>
       </c>
@@ -1696,7 +1696,7 @@
         <v>127283084</v>
       </c>
       <c r="B12" t="n">
-        <v>98443</v>
+        <v>98447</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1802,7 +1802,7 @@
         <v>127290259</v>
       </c>
       <c r="B13" t="n">
-        <v>98443</v>
+        <v>98447</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1913,61 +1913,45 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>127290258</v>
+        <v>127290233</v>
       </c>
       <c r="B14" t="n">
-        <v>98443</v>
+        <v>91330</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>220787</v>
+        <v>1202</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I14" t="inlineStr">
-        <is>
-          <t>15</t>
-        </is>
-      </c>
-      <c r="J14" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K14" t="inlineStr">
-        <is>
-          <t>överblommad</t>
-        </is>
-      </c>
-      <c r="L14" t="inlineStr"/>
-      <c r="N14" t="inlineStr"/>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
           <t>Österbyggebo, Gstr</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>603981</v>
+        <v>603850</v>
       </c>
       <c r="R14" t="n">
-        <v>6692427</v>
+        <v>6692680</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2008,7 +1992,6 @@
       <c r="AE14" t="b">
         <v>0</v>
       </c>
-      <c r="AF14" t="inlineStr"/>
       <c r="AG14" t="b">
         <v>0</v>
       </c>
@@ -2027,10 +2010,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>127290233</v>
+        <v>127290255</v>
       </c>
       <c r="B15" t="n">
-        <v>91326</v>
+        <v>91344</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2038,21 +2021,21 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>1202</v>
+        <v>1204</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Gränsticka</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Phellopilus nigrolimitatus</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2062,10 +2045,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>603850</v>
+        <v>603980</v>
       </c>
       <c r="R15" t="n">
-        <v>6692680</v>
+        <v>6692483</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2124,45 +2107,49 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>127290255</v>
+        <v>127283080</v>
       </c>
       <c r="B16" t="n">
-        <v>91340</v>
+        <v>56853</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>1204</v>
+        <v>100138</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Gränsticka</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Phellopilus nigrolimitatus</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
+      <c r="K16" t="inlineStr"/>
+      <c r="L16" t="inlineStr"/>
+      <c r="M16" t="inlineStr"/>
+      <c r="N16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
-          <t>Österbyggebo, Gstr</t>
+          <t>Gråtängarna, Gstr</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>603980</v>
+        <v>603972</v>
       </c>
       <c r="R16" t="n">
-        <v>6692483</v>
+        <v>6692667</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2197,6 +2184,11 @@
           <t>2025-08-06</t>
         </is>
       </c>
+      <c r="AC16" t="inlineStr">
+        <is>
+          <t>Fjäder efter en tjädertupp, 32 cm lång</t>
+        </is>
+      </c>
       <c r="AD16" t="b">
         <v>0</v>
       </c>
@@ -2209,61 +2201,73 @@
       <c r="AT16" t="inlineStr"/>
       <c r="AW16" t="inlineStr">
         <is>
-          <t>Clara Lerbro</t>
+          <t>Beke Regelin</t>
         </is>
       </c>
       <c r="AX16" t="inlineStr">
         <is>
-          <t>Clara Lerbro, Beke Regelin</t>
+          <t>Beke Regelin, Clara Lerbro</t>
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>127283080</v>
+        <v>127290258</v>
       </c>
       <c r="B17" t="n">
-        <v>56849</v>
+        <v>98447</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>100138</v>
+        <v>220787</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
-        </is>
-      </c>
-      <c r="I17" t="inlineStr"/>
-      <c r="K17" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="J17" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K17" t="inlineStr">
+        <is>
+          <t>överblommad</t>
+        </is>
+      </c>
       <c r="L17" t="inlineStr"/>
-      <c r="M17" t="inlineStr"/>
       <c r="N17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
-          <t>Gråtängarna, Gstr</t>
+          <t>Österbyggebo, Gstr</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>603972</v>
+        <v>603981</v>
       </c>
       <c r="R17" t="n">
-        <v>6692667</v>
+        <v>6692427</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2298,29 +2302,25 @@
           <t>2025-08-06</t>
         </is>
       </c>
-      <c r="AC17" t="inlineStr">
-        <is>
-          <t>Fjäder efter en tjädertupp, 32 cm lång</t>
-        </is>
-      </c>
       <c r="AD17" t="b">
         <v>0</v>
       </c>
       <c r="AE17" t="b">
         <v>0</v>
       </c>
+      <c r="AF17" t="inlineStr"/>
       <c r="AG17" t="b">
         <v>0</v>
       </c>
       <c r="AT17" t="inlineStr"/>
       <c r="AW17" t="inlineStr">
         <is>
-          <t>Beke Regelin</t>
+          <t>Clara Lerbro</t>
         </is>
       </c>
       <c r="AX17" t="inlineStr">
         <is>
-          <t>Beke Regelin, Clara Lerbro</t>
+          <t>Clara Lerbro, Beke Regelin</t>
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
@@ -2330,7 +2330,7 @@
         <v>127290240</v>
       </c>
       <c r="B18" t="n">
-        <v>98443</v>
+        <v>98447</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2440,7 +2440,7 @@
         <v>127290254</v>
       </c>
       <c r="B19" t="n">
-        <v>91291</v>
+        <v>91295</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2537,7 +2537,7 @@
         <v>127290227</v>
       </c>
       <c r="B20" t="n">
-        <v>91326</v>
+        <v>91330</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2634,7 +2634,7 @@
         <v>127290226</v>
       </c>
       <c r="B21" t="n">
-        <v>92608</v>
+        <v>92612</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2743,7 +2743,7 @@
         <v>127290239</v>
       </c>
       <c r="B22" t="n">
-        <v>91291</v>
+        <v>91295</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2840,7 +2840,7 @@
         <v>127290260</v>
       </c>
       <c r="B23" t="n">
-        <v>98443</v>
+        <v>98447</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2937,7 +2937,7 @@
         <v>127290244</v>
       </c>
       <c r="B24" t="n">
-        <v>98443</v>
+        <v>98447</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3051,7 +3051,7 @@
         <v>127290238</v>
       </c>
       <c r="B25" t="n">
-        <v>98443</v>
+        <v>98447</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3165,7 +3165,7 @@
         <v>127290246</v>
       </c>
       <c r="B26" t="n">
-        <v>92616</v>
+        <v>92620</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3262,7 +3262,7 @@
         <v>127290225</v>
       </c>
       <c r="B27" t="n">
-        <v>98443</v>
+        <v>98447</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3376,7 +3376,7 @@
         <v>127290242</v>
       </c>
       <c r="B28" t="n">
-        <v>98443</v>
+        <v>98447</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3490,7 +3490,7 @@
         <v>127290232</v>
       </c>
       <c r="B29" t="n">
-        <v>98443</v>
+        <v>98447</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3601,7 +3601,7 @@
         <v>127290257</v>
       </c>
       <c r="B30" t="n">
-        <v>91291</v>
+        <v>91295</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3698,7 +3698,7 @@
         <v>127290234</v>
       </c>
       <c r="B31" t="n">
-        <v>91291</v>
+        <v>91295</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3795,7 +3795,7 @@
         <v>127290241</v>
       </c>
       <c r="B32" t="n">
-        <v>98443</v>
+        <v>98447</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3906,7 +3906,7 @@
         <v>127290230</v>
       </c>
       <c r="B33" t="n">
-        <v>91291</v>
+        <v>91295</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4000,10 +4000,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>127290235</v>
+        <v>127290250</v>
       </c>
       <c r="B34" t="n">
-        <v>105478</v>
+        <v>105484</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4030,7 +4030,7 @@
       </c>
       <c r="I34" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>6</t>
         </is>
       </c>
       <c r="J34" t="inlineStr">
@@ -4047,10 +4047,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>603865</v>
+        <v>603965</v>
       </c>
       <c r="R34" t="n">
-        <v>6692727</v>
+        <v>6692480</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4110,10 +4110,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>127290250</v>
+        <v>127290235</v>
       </c>
       <c r="B35" t="n">
-        <v>105478</v>
+        <v>105484</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4140,7 +4140,7 @@
       </c>
       <c r="I35" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>11</t>
         </is>
       </c>
       <c r="J35" t="inlineStr">
@@ -4157,10 +4157,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>603965</v>
+        <v>603865</v>
       </c>
       <c r="R35" t="n">
-        <v>6692480</v>
+        <v>6692727</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>

--- a/artfynd/A 31590-2025 artfynd.xlsx
+++ b/artfynd/A 31590-2025 artfynd.xlsx
@@ -1490,45 +1490,48 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>127283076</v>
+        <v>127283083</v>
       </c>
       <c r="B10" t="n">
-        <v>56853</v>
+        <v>92612</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>100138</v>
+        <v>4361</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Orange taggsvamp</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Hydnellum aurantiacum</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Batsch:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
+      <c r="J10" t="inlineStr"/>
+      <c r="K10" t="inlineStr"/>
+      <c r="N10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
           <t>Gråtängarna, Gstr</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>603964</v>
+        <v>603807</v>
       </c>
       <c r="R10" t="n">
-        <v>6692543</v>
+        <v>6692702</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1563,17 +1566,13 @@
           <t>2025-08-06</t>
         </is>
       </c>
-      <c r="AC10" t="inlineStr">
-        <is>
-          <t>spillning</t>
-        </is>
-      </c>
       <c r="AD10" t="b">
         <v>0</v>
       </c>
       <c r="AE10" t="b">
         <v>0</v>
       </c>
+      <c r="AF10" t="inlineStr"/>
       <c r="AG10" t="b">
         <v>0</v>
       </c>
@@ -1592,48 +1591,45 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>127283083</v>
+        <v>127283076</v>
       </c>
       <c r="B11" t="n">
-        <v>92612</v>
+        <v>56853</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>4361</v>
+        <v>100138</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Orange taggsvamp</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Hydnellum aurantiacum</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Batsch:Fr.) P.Karst.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
-      <c r="J11" t="inlineStr"/>
-      <c r="K11" t="inlineStr"/>
-      <c r="N11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
           <t>Gråtängarna, Gstr</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>603807</v>
+        <v>603964</v>
       </c>
       <c r="R11" t="n">
-        <v>6692702</v>
+        <v>6692543</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1668,13 +1664,17 @@
           <t>2025-08-06</t>
         </is>
       </c>
+      <c r="AC11" t="inlineStr">
+        <is>
+          <t>spillning</t>
+        </is>
+      </c>
       <c r="AD11" t="b">
         <v>0</v>
       </c>
       <c r="AE11" t="b">
         <v>0</v>
       </c>
-      <c r="AF11" t="inlineStr"/>
       <c r="AG11" t="b">
         <v>0</v>
       </c>
@@ -2631,56 +2631,45 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>127290226</v>
+        <v>127290239</v>
       </c>
       <c r="B21" t="n">
-        <v>92612</v>
+        <v>91295</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>4361</v>
+        <v>5447</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Orange taggsvamp</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Hydnellum aurantiacum</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Batsch:Fr.) P.Karst.</t>
-        </is>
-      </c>
-      <c r="I21" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="J21" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
-      <c r="K21" t="inlineStr"/>
-      <c r="N21" t="inlineStr"/>
+          <t>(Schwein.) Murrill</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
           <t>Österbyggebo, Gstr</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>603857</v>
+        <v>603877</v>
       </c>
       <c r="R21" t="n">
-        <v>6692565</v>
+        <v>6692706</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2721,7 +2710,6 @@
       <c r="AE21" t="b">
         <v>0</v>
       </c>
-      <c r="AF21" t="inlineStr"/>
       <c r="AG21" t="b">
         <v>0</v>
       </c>
@@ -2740,32 +2728,32 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>127290239</v>
+        <v>127290260</v>
       </c>
       <c r="B22" t="n">
-        <v>91295</v>
+        <v>98447</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>5447</v>
+        <v>220787</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -2775,10 +2763,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>603877</v>
+        <v>603977</v>
       </c>
       <c r="R22" t="n">
-        <v>6692706</v>
+        <v>6692392</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2837,45 +2825,56 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>127290260</v>
+        <v>127290226</v>
       </c>
       <c r="B23" t="n">
-        <v>98447</v>
+        <v>92612</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>220787</v>
+        <v>4361</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Orange taggsvamp</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hydnellum aurantiacum</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I23" t="inlineStr"/>
+          <t>(Batsch:Fr.) P.Karst.</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J23" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
+      <c r="K23" t="inlineStr"/>
+      <c r="N23" t="inlineStr"/>
       <c r="P23" t="inlineStr">
         <is>
           <t>Österbyggebo, Gstr</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>603977</v>
+        <v>603857</v>
       </c>
       <c r="R23" t="n">
-        <v>6692392</v>
+        <v>6692565</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -2916,6 +2915,7 @@
       <c r="AE23" t="b">
         <v>0</v>
       </c>
+      <c r="AF23" t="inlineStr"/>
       <c r="AG23" t="b">
         <v>0</v>
       </c>

--- a/artfynd/A 31590-2025 artfynd.xlsx
+++ b/artfynd/A 31590-2025 artfynd.xlsx
@@ -2631,32 +2631,32 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>127290239</v>
+        <v>127290260</v>
       </c>
       <c r="B21" t="n">
-        <v>91295</v>
+        <v>98447</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>5447</v>
+        <v>220787</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2666,10 +2666,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>603877</v>
+        <v>603977</v>
       </c>
       <c r="R21" t="n">
-        <v>6692706</v>
+        <v>6692392</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2728,45 +2728,56 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>127290260</v>
+        <v>127290226</v>
       </c>
       <c r="B22" t="n">
-        <v>98447</v>
+        <v>92612</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>220787</v>
+        <v>4361</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Orange taggsvamp</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hydnellum aurantiacum</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I22" t="inlineStr"/>
+          <t>(Batsch:Fr.) P.Karst.</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J22" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
+      <c r="K22" t="inlineStr"/>
+      <c r="N22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
           <t>Österbyggebo, Gstr</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>603977</v>
+        <v>603857</v>
       </c>
       <c r="R22" t="n">
-        <v>6692392</v>
+        <v>6692565</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2807,6 +2818,7 @@
       <c r="AE22" t="b">
         <v>0</v>
       </c>
+      <c r="AF22" t="inlineStr"/>
       <c r="AG22" t="b">
         <v>0</v>
       </c>
@@ -2825,56 +2837,45 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>127290226</v>
+        <v>127290239</v>
       </c>
       <c r="B23" t="n">
-        <v>92612</v>
+        <v>91295</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>4361</v>
+        <v>5447</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Orange taggsvamp</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Hydnellum aurantiacum</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Batsch:Fr.) P.Karst.</t>
-        </is>
-      </c>
-      <c r="I23" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="J23" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
-      <c r="K23" t="inlineStr"/>
-      <c r="N23" t="inlineStr"/>
+          <t>(Schwein.) Murrill</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr"/>
       <c r="P23" t="inlineStr">
         <is>
           <t>Österbyggebo, Gstr</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>603857</v>
+        <v>603877</v>
       </c>
       <c r="R23" t="n">
-        <v>6692565</v>
+        <v>6692706</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -2915,7 +2916,6 @@
       <c r="AE23" t="b">
         <v>0</v>
       </c>
-      <c r="AF23" t="inlineStr"/>
       <c r="AG23" t="b">
         <v>0</v>
       </c>
@@ -3695,45 +3695,59 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>127290234</v>
+        <v>127290241</v>
       </c>
       <c r="B31" t="n">
-        <v>91295</v>
+        <v>98447</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>5447</v>
+        <v>220787</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
-        </is>
-      </c>
-      <c r="I31" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="J31" t="inlineStr">
+        <is>
+          <t>dm²</t>
+        </is>
+      </c>
+      <c r="K31" t="inlineStr">
+        <is>
+          <t>överblommad</t>
+        </is>
+      </c>
       <c r="P31" t="inlineStr">
         <is>
           <t>Österbyggebo, Gstr</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>603860</v>
+        <v>603880</v>
       </c>
       <c r="R31" t="n">
-        <v>6692678</v>
+        <v>6692710</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3792,59 +3806,45 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>127290241</v>
+        <v>127290234</v>
       </c>
       <c r="B32" t="n">
-        <v>98447</v>
+        <v>91295</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>220787</v>
+        <v>5447</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I32" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="J32" t="inlineStr">
-        <is>
-          <t>dm²</t>
-        </is>
-      </c>
-      <c r="K32" t="inlineStr">
-        <is>
-          <t>överblommad</t>
-        </is>
-      </c>
+          <t>(Schwein.) Murrill</t>
+        </is>
+      </c>
+      <c r="I32" t="inlineStr"/>
       <c r="P32" t="inlineStr">
         <is>
           <t>Österbyggebo, Gstr</t>
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>603880</v>
+        <v>603860</v>
       </c>
       <c r="R32" t="n">
-        <v>6692710</v>
+        <v>6692678</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>

--- a/artfynd/A 31590-2025 artfynd.xlsx
+++ b/artfynd/A 31590-2025 artfynd.xlsx
@@ -1490,48 +1490,45 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>127283083</v>
+        <v>127283076</v>
       </c>
       <c r="B10" t="n">
-        <v>92612</v>
+        <v>56853</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>4361</v>
+        <v>100138</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Orange taggsvamp</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Hydnellum aurantiacum</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Batsch:Fr.) P.Karst.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
-      <c r="J10" t="inlineStr"/>
-      <c r="K10" t="inlineStr"/>
-      <c r="N10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
           <t>Gråtängarna, Gstr</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>603807</v>
+        <v>603964</v>
       </c>
       <c r="R10" t="n">
-        <v>6692702</v>
+        <v>6692543</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1566,13 +1563,17 @@
           <t>2025-08-06</t>
         </is>
       </c>
+      <c r="AC10" t="inlineStr">
+        <is>
+          <t>spillning</t>
+        </is>
+      </c>
       <c r="AD10" t="b">
         <v>0</v>
       </c>
       <c r="AE10" t="b">
         <v>0</v>
       </c>
-      <c r="AF10" t="inlineStr"/>
       <c r="AG10" t="b">
         <v>0</v>
       </c>
@@ -1591,45 +1592,48 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>127283076</v>
+        <v>127283083</v>
       </c>
       <c r="B11" t="n">
-        <v>56853</v>
+        <v>92612</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>100138</v>
+        <v>4361</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Orange taggsvamp</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Hydnellum aurantiacum</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Batsch:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
+      <c r="J11" t="inlineStr"/>
+      <c r="K11" t="inlineStr"/>
+      <c r="N11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
           <t>Gråtängarna, Gstr</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>603964</v>
+        <v>603807</v>
       </c>
       <c r="R11" t="n">
-        <v>6692543</v>
+        <v>6692702</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1664,17 +1668,13 @@
           <t>2025-08-06</t>
         </is>
       </c>
-      <c r="AC11" t="inlineStr">
-        <is>
-          <t>spillning</t>
-        </is>
-      </c>
       <c r="AD11" t="b">
         <v>0</v>
       </c>
       <c r="AE11" t="b">
         <v>0</v>
       </c>
+      <c r="AF11" t="inlineStr"/>
       <c r="AG11" t="b">
         <v>0</v>
       </c>

--- a/artfynd/A 31590-2025 artfynd.xlsx
+++ b/artfynd/A 31590-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>127264982</v>
       </c>
       <c r="B2" t="n">
-        <v>98447</v>
+        <v>98448</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -793,7 +793,7 @@
         <v>127283088</v>
       </c>
       <c r="B3" t="n">
-        <v>105484</v>
+        <v>105486</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -992,7 +992,7 @@
         <v>127283086</v>
       </c>
       <c r="B5" t="n">
-        <v>98447</v>
+        <v>98448</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1291,7 +1291,7 @@
         <v>127283087</v>
       </c>
       <c r="B8" t="n">
-        <v>105484</v>
+        <v>105486</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1392,7 +1392,7 @@
         <v>127283085</v>
       </c>
       <c r="B9" t="n">
-        <v>98447</v>
+        <v>98448</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1490,45 +1490,48 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>127283076</v>
+        <v>127283083</v>
       </c>
       <c r="B10" t="n">
-        <v>56853</v>
+        <v>92612</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>100138</v>
+        <v>4361</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Orange taggsvamp</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Hydnellum aurantiacum</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Batsch:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
+      <c r="J10" t="inlineStr"/>
+      <c r="K10" t="inlineStr"/>
+      <c r="N10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
           <t>Gråtängarna, Gstr</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>603964</v>
+        <v>603807</v>
       </c>
       <c r="R10" t="n">
-        <v>6692543</v>
+        <v>6692702</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1563,17 +1566,13 @@
           <t>2025-08-06</t>
         </is>
       </c>
-      <c r="AC10" t="inlineStr">
-        <is>
-          <t>spillning</t>
-        </is>
-      </c>
       <c r="AD10" t="b">
         <v>0</v>
       </c>
       <c r="AE10" t="b">
         <v>0</v>
       </c>
+      <c r="AF10" t="inlineStr"/>
       <c r="AG10" t="b">
         <v>0</v>
       </c>
@@ -1592,48 +1591,45 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>127283083</v>
+        <v>127283076</v>
       </c>
       <c r="B11" t="n">
-        <v>92612</v>
+        <v>56853</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>4361</v>
+        <v>100138</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Orange taggsvamp</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Hydnellum aurantiacum</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Batsch:Fr.) P.Karst.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
-      <c r="J11" t="inlineStr"/>
-      <c r="K11" t="inlineStr"/>
-      <c r="N11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
           <t>Gråtängarna, Gstr</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>603807</v>
+        <v>603964</v>
       </c>
       <c r="R11" t="n">
-        <v>6692702</v>
+        <v>6692543</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1668,13 +1664,17 @@
           <t>2025-08-06</t>
         </is>
       </c>
+      <c r="AC11" t="inlineStr">
+        <is>
+          <t>spillning</t>
+        </is>
+      </c>
       <c r="AD11" t="b">
         <v>0</v>
       </c>
       <c r="AE11" t="b">
         <v>0</v>
       </c>
-      <c r="AF11" t="inlineStr"/>
       <c r="AG11" t="b">
         <v>0</v>
       </c>
@@ -1696,7 +1696,7 @@
         <v>127283084</v>
       </c>
       <c r="B12" t="n">
-        <v>98447</v>
+        <v>98448</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1802,7 +1802,7 @@
         <v>127290259</v>
       </c>
       <c r="B13" t="n">
-        <v>98447</v>
+        <v>98448</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1913,45 +1913,49 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>127290233</v>
+        <v>127283080</v>
       </c>
       <c r="B14" t="n">
-        <v>91330</v>
+        <v>56853</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>1202</v>
+        <v>100138</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
+      <c r="K14" t="inlineStr"/>
+      <c r="L14" t="inlineStr"/>
+      <c r="M14" t="inlineStr"/>
+      <c r="N14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
-          <t>Österbyggebo, Gstr</t>
+          <t>Gråtängarna, Gstr</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>603850</v>
+        <v>603972</v>
       </c>
       <c r="R14" t="n">
-        <v>6692680</v>
+        <v>6692667</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -1986,6 +1990,11 @@
           <t>2025-08-06</t>
         </is>
       </c>
+      <c r="AC14" t="inlineStr">
+        <is>
+          <t>Fjäder efter en tjädertupp, 32 cm lång</t>
+        </is>
+      </c>
       <c r="AD14" t="b">
         <v>0</v>
       </c>
@@ -1998,22 +2007,22 @@
       <c r="AT14" t="inlineStr"/>
       <c r="AW14" t="inlineStr">
         <is>
-          <t>Clara Lerbro</t>
+          <t>Beke Regelin</t>
         </is>
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>Clara Lerbro, Beke Regelin</t>
+          <t>Beke Regelin, Clara Lerbro</t>
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>127290255</v>
+        <v>127290233</v>
       </c>
       <c r="B15" t="n">
-        <v>91344</v>
+        <v>91330</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2021,21 +2030,21 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>1204</v>
+        <v>1202</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Gränsticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Phellopilus nigrolimitatus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2045,10 +2054,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>603980</v>
+        <v>603850</v>
       </c>
       <c r="R15" t="n">
-        <v>6692483</v>
+        <v>6692680</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2107,49 +2116,45 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>127283080</v>
+        <v>127290255</v>
       </c>
       <c r="B16" t="n">
-        <v>56853</v>
+        <v>91344</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>100138</v>
+        <v>1204</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Gränsticka</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Phellopilus nigrolimitatus</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
-      <c r="K16" t="inlineStr"/>
-      <c r="L16" t="inlineStr"/>
-      <c r="M16" t="inlineStr"/>
-      <c r="N16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
-          <t>Gråtängarna, Gstr</t>
+          <t>Österbyggebo, Gstr</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>603972</v>
+        <v>603980</v>
       </c>
       <c r="R16" t="n">
-        <v>6692667</v>
+        <v>6692483</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2184,11 +2189,6 @@
           <t>2025-08-06</t>
         </is>
       </c>
-      <c r="AC16" t="inlineStr">
-        <is>
-          <t>Fjäder efter en tjädertupp, 32 cm lång</t>
-        </is>
-      </c>
       <c r="AD16" t="b">
         <v>0</v>
       </c>
@@ -2201,12 +2201,12 @@
       <c r="AT16" t="inlineStr"/>
       <c r="AW16" t="inlineStr">
         <is>
-          <t>Beke Regelin</t>
+          <t>Clara Lerbro</t>
         </is>
       </c>
       <c r="AX16" t="inlineStr">
         <is>
-          <t>Beke Regelin, Clara Lerbro</t>
+          <t>Clara Lerbro, Beke Regelin</t>
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
@@ -2216,7 +2216,7 @@
         <v>127290258</v>
       </c>
       <c r="B17" t="n">
-        <v>98447</v>
+        <v>98448</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2330,7 +2330,7 @@
         <v>127290240</v>
       </c>
       <c r="B18" t="n">
-        <v>98447</v>
+        <v>98448</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2631,45 +2631,56 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>127290260</v>
+        <v>127290226</v>
       </c>
       <c r="B21" t="n">
-        <v>98447</v>
+        <v>92612</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>220787</v>
+        <v>4361</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Orange taggsvamp</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hydnellum aurantiacum</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I21" t="inlineStr"/>
+          <t>(Batsch:Fr.) P.Karst.</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J21" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
+      <c r="K21" t="inlineStr"/>
+      <c r="N21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
           <t>Österbyggebo, Gstr</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>603977</v>
+        <v>603857</v>
       </c>
       <c r="R21" t="n">
-        <v>6692392</v>
+        <v>6692565</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2710,6 +2721,7 @@
       <c r="AE21" t="b">
         <v>0</v>
       </c>
+      <c r="AF21" t="inlineStr"/>
       <c r="AG21" t="b">
         <v>0</v>
       </c>
@@ -2728,56 +2740,45 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>127290226</v>
+        <v>127290239</v>
       </c>
       <c r="B22" t="n">
-        <v>92612</v>
+        <v>91295</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>4361</v>
+        <v>5447</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Orange taggsvamp</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Hydnellum aurantiacum</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Batsch:Fr.) P.Karst.</t>
-        </is>
-      </c>
-      <c r="I22" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="J22" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
-      <c r="K22" t="inlineStr"/>
-      <c r="N22" t="inlineStr"/>
+          <t>(Schwein.) Murrill</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
           <t>Österbyggebo, Gstr</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>603857</v>
+        <v>603877</v>
       </c>
       <c r="R22" t="n">
-        <v>6692565</v>
+        <v>6692706</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2818,7 +2819,6 @@
       <c r="AE22" t="b">
         <v>0</v>
       </c>
-      <c r="AF22" t="inlineStr"/>
       <c r="AG22" t="b">
         <v>0</v>
       </c>
@@ -2837,32 +2837,32 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>127290239</v>
+        <v>127290260</v>
       </c>
       <c r="B23" t="n">
-        <v>91295</v>
+        <v>98448</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>5447</v>
+        <v>220787</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -2872,10 +2872,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>603877</v>
+        <v>603977</v>
       </c>
       <c r="R23" t="n">
-        <v>6692706</v>
+        <v>6692392</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -2937,7 +2937,7 @@
         <v>127290244</v>
       </c>
       <c r="B24" t="n">
-        <v>98447</v>
+        <v>98448</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3051,7 +3051,7 @@
         <v>127290238</v>
       </c>
       <c r="B25" t="n">
-        <v>98447</v>
+        <v>98448</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3262,7 +3262,7 @@
         <v>127290225</v>
       </c>
       <c r="B27" t="n">
-        <v>98447</v>
+        <v>98448</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3373,10 +3373,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>127290242</v>
+        <v>127290232</v>
       </c>
       <c r="B28" t="n">
-        <v>98447</v>
+        <v>98448</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3403,12 +3403,12 @@
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>4</t>
         </is>
       </c>
       <c r="J28" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
+          <t>dm²</t>
         </is>
       </c>
       <c r="K28" t="inlineStr">
@@ -3416,18 +3416,16 @@
           <t>överblommad</t>
         </is>
       </c>
-      <c r="L28" t="inlineStr"/>
-      <c r="N28" t="inlineStr"/>
       <c r="P28" t="inlineStr">
         <is>
           <t>Österbyggebo, Gstr</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>603879</v>
+        <v>603845</v>
       </c>
       <c r="R28" t="n">
-        <v>6692700</v>
+        <v>6692678</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3468,7 +3466,6 @@
       <c r="AE28" t="b">
         <v>0</v>
       </c>
-      <c r="AF28" t="inlineStr"/>
       <c r="AG28" t="b">
         <v>0</v>
       </c>
@@ -3487,10 +3484,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>127290232</v>
+        <v>127290242</v>
       </c>
       <c r="B29" t="n">
-        <v>98447</v>
+        <v>98448</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3517,12 +3514,12 @@
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>9</t>
         </is>
       </c>
       <c r="J29" t="inlineStr">
         <is>
-          <t>dm²</t>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="K29" t="inlineStr">
@@ -3530,16 +3527,18 @@
           <t>överblommad</t>
         </is>
       </c>
+      <c r="L29" t="inlineStr"/>
+      <c r="N29" t="inlineStr"/>
       <c r="P29" t="inlineStr">
         <is>
           <t>Österbyggebo, Gstr</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>603845</v>
+        <v>603879</v>
       </c>
       <c r="R29" t="n">
-        <v>6692678</v>
+        <v>6692700</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3580,6 +3579,7 @@
       <c r="AE29" t="b">
         <v>0</v>
       </c>
+      <c r="AF29" t="inlineStr"/>
       <c r="AG29" t="b">
         <v>0</v>
       </c>
@@ -3698,7 +3698,7 @@
         <v>127290241</v>
       </c>
       <c r="B31" t="n">
-        <v>98447</v>
+        <v>98448</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -4003,7 +4003,7 @@
         <v>127290250</v>
       </c>
       <c r="B34" t="n">
-        <v>105484</v>
+        <v>105486</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4113,7 +4113,7 @@
         <v>127290235</v>
       </c>
       <c r="B35" t="n">
-        <v>105484</v>
+        <v>105486</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>

--- a/artfynd/A 31590-2025 artfynd.xlsx
+++ b/artfynd/A 31590-2025 artfynd.xlsx
@@ -1913,49 +1913,45 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>127283080</v>
+        <v>127290233</v>
       </c>
       <c r="B14" t="n">
-        <v>56853</v>
+        <v>91330</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>100138</v>
+        <v>1202</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
-      <c r="K14" t="inlineStr"/>
-      <c r="L14" t="inlineStr"/>
-      <c r="M14" t="inlineStr"/>
-      <c r="N14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
-          <t>Gråtängarna, Gstr</t>
+          <t>Österbyggebo, Gstr</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>603972</v>
+        <v>603850</v>
       </c>
       <c r="R14" t="n">
-        <v>6692667</v>
+        <v>6692680</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -1990,11 +1986,6 @@
           <t>2025-08-06</t>
         </is>
       </c>
-      <c r="AC14" t="inlineStr">
-        <is>
-          <t>Fjäder efter en tjädertupp, 32 cm lång</t>
-        </is>
-      </c>
       <c r="AD14" t="b">
         <v>0</v>
       </c>
@@ -2007,22 +1998,22 @@
       <c r="AT14" t="inlineStr"/>
       <c r="AW14" t="inlineStr">
         <is>
-          <t>Beke Regelin</t>
+          <t>Clara Lerbro</t>
         </is>
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>Beke Regelin, Clara Lerbro</t>
+          <t>Clara Lerbro, Beke Regelin</t>
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>127290233</v>
+        <v>127290255</v>
       </c>
       <c r="B15" t="n">
-        <v>91330</v>
+        <v>91344</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2030,21 +2021,21 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>1202</v>
+        <v>1204</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Gränsticka</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Phellopilus nigrolimitatus</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2054,10 +2045,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>603850</v>
+        <v>603980</v>
       </c>
       <c r="R15" t="n">
-        <v>6692680</v>
+        <v>6692483</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2116,45 +2107,61 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>127290255</v>
+        <v>127290258</v>
       </c>
       <c r="B16" t="n">
-        <v>91344</v>
+        <v>98448</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>1204</v>
+        <v>220787</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Gränsticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Phellopilus nigrolimitatus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
-        </is>
-      </c>
-      <c r="I16" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="J16" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K16" t="inlineStr">
+        <is>
+          <t>överblommad</t>
+        </is>
+      </c>
+      <c r="L16" t="inlineStr"/>
+      <c r="N16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
           <t>Österbyggebo, Gstr</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>603980</v>
+        <v>603981</v>
       </c>
       <c r="R16" t="n">
-        <v>6692483</v>
+        <v>6692427</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2195,6 +2202,7 @@
       <c r="AE16" t="b">
         <v>0</v>
       </c>
+      <c r="AF16" t="inlineStr"/>
       <c r="AG16" t="b">
         <v>0</v>
       </c>
@@ -2213,61 +2221,49 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>127290258</v>
+        <v>127283080</v>
       </c>
       <c r="B17" t="n">
-        <v>98448</v>
+        <v>56853</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>220787</v>
+        <v>100138</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I17" t="inlineStr">
-        <is>
-          <t>15</t>
-        </is>
-      </c>
-      <c r="J17" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K17" t="inlineStr">
-        <is>
-          <t>överblommad</t>
-        </is>
-      </c>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr"/>
+      <c r="K17" t="inlineStr"/>
       <c r="L17" t="inlineStr"/>
+      <c r="M17" t="inlineStr"/>
       <c r="N17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
-          <t>Österbyggebo, Gstr</t>
+          <t>Gråtängarna, Gstr</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>603981</v>
+        <v>603972</v>
       </c>
       <c r="R17" t="n">
-        <v>6692427</v>
+        <v>6692667</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2302,25 +2298,29 @@
           <t>2025-08-06</t>
         </is>
       </c>
+      <c r="AC17" t="inlineStr">
+        <is>
+          <t>Fjäder efter en tjädertupp, 32 cm lång</t>
+        </is>
+      </c>
       <c r="AD17" t="b">
         <v>0</v>
       </c>
       <c r="AE17" t="b">
         <v>0</v>
       </c>
-      <c r="AF17" t="inlineStr"/>
       <c r="AG17" t="b">
         <v>0</v>
       </c>
       <c r="AT17" t="inlineStr"/>
       <c r="AW17" t="inlineStr">
         <is>
-          <t>Clara Lerbro</t>
+          <t>Beke Regelin</t>
         </is>
       </c>
       <c r="AX17" t="inlineStr">
         <is>
-          <t>Clara Lerbro, Beke Regelin</t>
+          <t>Beke Regelin, Clara Lerbro</t>
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>

--- a/artfynd/A 31590-2025 artfynd.xlsx
+++ b/artfynd/A 31590-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>127264982</v>
       </c>
       <c r="B2" t="n">
-        <v>98448</v>
+        <v>98450</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -793,7 +793,7 @@
         <v>127283088</v>
       </c>
       <c r="B3" t="n">
-        <v>105486</v>
+        <v>105488</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -894,7 +894,7 @@
         <v>127264978</v>
       </c>
       <c r="B4" t="n">
-        <v>97325</v>
+        <v>97327</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -992,7 +992,7 @@
         <v>127283086</v>
       </c>
       <c r="B5" t="n">
-        <v>98448</v>
+        <v>98450</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1093,7 +1093,7 @@
         <v>127283078</v>
       </c>
       <c r="B6" t="n">
-        <v>91295</v>
+        <v>91297</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1194,7 +1194,7 @@
         <v>127264973</v>
       </c>
       <c r="B7" t="n">
-        <v>97325</v>
+        <v>97327</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1291,7 +1291,7 @@
         <v>127283087</v>
       </c>
       <c r="B8" t="n">
-        <v>105486</v>
+        <v>105488</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1392,7 +1392,7 @@
         <v>127283085</v>
       </c>
       <c r="B9" t="n">
-        <v>98448</v>
+        <v>98450</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1490,48 +1490,45 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>127283083</v>
+        <v>127283076</v>
       </c>
       <c r="B10" t="n">
-        <v>92612</v>
+        <v>56855</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>4361</v>
+        <v>100138</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Orange taggsvamp</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Hydnellum aurantiacum</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Batsch:Fr.) P.Karst.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
-      <c r="J10" t="inlineStr"/>
-      <c r="K10" t="inlineStr"/>
-      <c r="N10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
           <t>Gråtängarna, Gstr</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>603807</v>
+        <v>603964</v>
       </c>
       <c r="R10" t="n">
-        <v>6692702</v>
+        <v>6692543</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1566,13 +1563,17 @@
           <t>2025-08-06</t>
         </is>
       </c>
+      <c r="AC10" t="inlineStr">
+        <is>
+          <t>spillning</t>
+        </is>
+      </c>
       <c r="AD10" t="b">
         <v>0</v>
       </c>
       <c r="AE10" t="b">
         <v>0</v>
       </c>
-      <c r="AF10" t="inlineStr"/>
       <c r="AG10" t="b">
         <v>0</v>
       </c>
@@ -1591,45 +1592,48 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>127283076</v>
+        <v>127283083</v>
       </c>
       <c r="B11" t="n">
-        <v>56853</v>
+        <v>92614</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>100138</v>
+        <v>4361</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Orange taggsvamp</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Hydnellum aurantiacum</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Batsch:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
+      <c r="J11" t="inlineStr"/>
+      <c r="K11" t="inlineStr"/>
+      <c r="N11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
           <t>Gråtängarna, Gstr</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>603964</v>
+        <v>603807</v>
       </c>
       <c r="R11" t="n">
-        <v>6692543</v>
+        <v>6692702</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1664,17 +1668,13 @@
           <t>2025-08-06</t>
         </is>
       </c>
-      <c r="AC11" t="inlineStr">
-        <is>
-          <t>spillning</t>
-        </is>
-      </c>
       <c r="AD11" t="b">
         <v>0</v>
       </c>
       <c r="AE11" t="b">
         <v>0</v>
       </c>
+      <c r="AF11" t="inlineStr"/>
       <c r="AG11" t="b">
         <v>0</v>
       </c>
@@ -1696,7 +1696,7 @@
         <v>127283084</v>
       </c>
       <c r="B12" t="n">
-        <v>98448</v>
+        <v>98450</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1802,7 +1802,7 @@
         <v>127290259</v>
       </c>
       <c r="B13" t="n">
-        <v>98448</v>
+        <v>98450</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1913,45 +1913,61 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>127290233</v>
+        <v>127290258</v>
       </c>
       <c r="B14" t="n">
-        <v>91330</v>
+        <v>98450</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>1202</v>
+        <v>220787</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I14" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="J14" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K14" t="inlineStr">
+        <is>
+          <t>överblommad</t>
+        </is>
+      </c>
+      <c r="L14" t="inlineStr"/>
+      <c r="N14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
           <t>Österbyggebo, Gstr</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>603850</v>
+        <v>603981</v>
       </c>
       <c r="R14" t="n">
-        <v>6692680</v>
+        <v>6692427</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -1992,6 +2008,7 @@
       <c r="AE14" t="b">
         <v>0</v>
       </c>
+      <c r="AF14" t="inlineStr"/>
       <c r="AG14" t="b">
         <v>0</v>
       </c>
@@ -2010,10 +2027,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>127290255</v>
+        <v>127290233</v>
       </c>
       <c r="B15" t="n">
-        <v>91344</v>
+        <v>91332</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2021,21 +2038,21 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>1204</v>
+        <v>1202</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Gränsticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Phellopilus nigrolimitatus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2045,10 +2062,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>603980</v>
+        <v>603850</v>
       </c>
       <c r="R15" t="n">
-        <v>6692483</v>
+        <v>6692680</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2107,61 +2124,45 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>127290258</v>
+        <v>127290255</v>
       </c>
       <c r="B16" t="n">
-        <v>98448</v>
+        <v>91346</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>220787</v>
+        <v>1204</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Gränsticka</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellopilus nigrolimitatus</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I16" t="inlineStr">
-        <is>
-          <t>15</t>
-        </is>
-      </c>
-      <c r="J16" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K16" t="inlineStr">
-        <is>
-          <t>överblommad</t>
-        </is>
-      </c>
-      <c r="L16" t="inlineStr"/>
-      <c r="N16" t="inlineStr"/>
+          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
           <t>Österbyggebo, Gstr</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>603981</v>
+        <v>603980</v>
       </c>
       <c r="R16" t="n">
-        <v>6692427</v>
+        <v>6692483</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2202,7 +2203,6 @@
       <c r="AE16" t="b">
         <v>0</v>
       </c>
-      <c r="AF16" t="inlineStr"/>
       <c r="AG16" t="b">
         <v>0</v>
       </c>
@@ -2224,7 +2224,7 @@
         <v>127283080</v>
       </c>
       <c r="B17" t="n">
-        <v>56853</v>
+        <v>56855</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2330,7 +2330,7 @@
         <v>127290240</v>
       </c>
       <c r="B18" t="n">
-        <v>98448</v>
+        <v>98450</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2440,7 +2440,7 @@
         <v>127290254</v>
       </c>
       <c r="B19" t="n">
-        <v>91295</v>
+        <v>91297</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2537,7 +2537,7 @@
         <v>127290227</v>
       </c>
       <c r="B20" t="n">
-        <v>91330</v>
+        <v>91332</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2631,56 +2631,45 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>127290226</v>
+        <v>127290260</v>
       </c>
       <c r="B21" t="n">
-        <v>92612</v>
+        <v>98450</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>4361</v>
+        <v>220787</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Orange taggsvamp</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Hydnellum aurantiacum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Batsch:Fr.) P.Karst.</t>
-        </is>
-      </c>
-      <c r="I21" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="J21" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
-      <c r="K21" t="inlineStr"/>
-      <c r="N21" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
           <t>Österbyggebo, Gstr</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>603857</v>
+        <v>603977</v>
       </c>
       <c r="R21" t="n">
-        <v>6692565</v>
+        <v>6692392</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2721,7 +2710,6 @@
       <c r="AE21" t="b">
         <v>0</v>
       </c>
-      <c r="AF21" t="inlineStr"/>
       <c r="AG21" t="b">
         <v>0</v>
       </c>
@@ -2740,45 +2728,56 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>127290239</v>
+        <v>127290226</v>
       </c>
       <c r="B22" t="n">
-        <v>91295</v>
+        <v>92614</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>5447</v>
+        <v>4361</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Orange taggsvamp</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Hydnellum aurantiacum</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
-        </is>
-      </c>
-      <c r="I22" t="inlineStr"/>
+          <t>(Batsch:Fr.) P.Karst.</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J22" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
+      <c r="K22" t="inlineStr"/>
+      <c r="N22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
           <t>Österbyggebo, Gstr</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>603877</v>
+        <v>603857</v>
       </c>
       <c r="R22" t="n">
-        <v>6692706</v>
+        <v>6692565</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2819,6 +2818,7 @@
       <c r="AE22" t="b">
         <v>0</v>
       </c>
+      <c r="AF22" t="inlineStr"/>
       <c r="AG22" t="b">
         <v>0</v>
       </c>
@@ -2837,32 +2837,32 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>127290260</v>
+        <v>127290239</v>
       </c>
       <c r="B23" t="n">
-        <v>98448</v>
+        <v>91297</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>220787</v>
+        <v>5447</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -2872,10 +2872,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>603977</v>
+        <v>603877</v>
       </c>
       <c r="R23" t="n">
-        <v>6692392</v>
+        <v>6692706</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -2937,7 +2937,7 @@
         <v>127290244</v>
       </c>
       <c r="B24" t="n">
-        <v>98448</v>
+        <v>98450</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3051,7 +3051,7 @@
         <v>127290238</v>
       </c>
       <c r="B25" t="n">
-        <v>98448</v>
+        <v>98450</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3165,7 +3165,7 @@
         <v>127290246</v>
       </c>
       <c r="B26" t="n">
-        <v>92620</v>
+        <v>92622</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3262,7 +3262,7 @@
         <v>127290225</v>
       </c>
       <c r="B27" t="n">
-        <v>98448</v>
+        <v>98450</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3376,7 +3376,7 @@
         <v>127290232</v>
       </c>
       <c r="B28" t="n">
-        <v>98448</v>
+        <v>98450</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3487,7 +3487,7 @@
         <v>127290242</v>
       </c>
       <c r="B29" t="n">
-        <v>98448</v>
+        <v>98450</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3601,7 +3601,7 @@
         <v>127290257</v>
       </c>
       <c r="B30" t="n">
-        <v>91295</v>
+        <v>91297</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3695,59 +3695,45 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>127290241</v>
+        <v>127290234</v>
       </c>
       <c r="B31" t="n">
-        <v>98448</v>
+        <v>91297</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>220787</v>
+        <v>5447</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I31" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="J31" t="inlineStr">
-        <is>
-          <t>dm²</t>
-        </is>
-      </c>
-      <c r="K31" t="inlineStr">
-        <is>
-          <t>överblommad</t>
-        </is>
-      </c>
+          <t>(Schwein.) Murrill</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr"/>
       <c r="P31" t="inlineStr">
         <is>
           <t>Österbyggebo, Gstr</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>603880</v>
+        <v>603860</v>
       </c>
       <c r="R31" t="n">
-        <v>6692710</v>
+        <v>6692678</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3806,45 +3792,59 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>127290234</v>
+        <v>127290241</v>
       </c>
       <c r="B32" t="n">
-        <v>91295</v>
+        <v>98450</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>5447</v>
+        <v>220787</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
-        </is>
-      </c>
-      <c r="I32" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I32" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="J32" t="inlineStr">
+        <is>
+          <t>dm²</t>
+        </is>
+      </c>
+      <c r="K32" t="inlineStr">
+        <is>
+          <t>överblommad</t>
+        </is>
+      </c>
       <c r="P32" t="inlineStr">
         <is>
           <t>Österbyggebo, Gstr</t>
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>603860</v>
+        <v>603880</v>
       </c>
       <c r="R32" t="n">
-        <v>6692678</v>
+        <v>6692710</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -3906,7 +3906,7 @@
         <v>127290230</v>
       </c>
       <c r="B33" t="n">
-        <v>91295</v>
+        <v>91297</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4003,7 +4003,7 @@
         <v>127290250</v>
       </c>
       <c r="B34" t="n">
-        <v>105486</v>
+        <v>105488</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4113,7 +4113,7 @@
         <v>127290235</v>
       </c>
       <c r="B35" t="n">
-        <v>105486</v>
+        <v>105488</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>

--- a/artfynd/A 31590-2025 artfynd.xlsx
+++ b/artfynd/A 31590-2025 artfynd.xlsx
@@ -1490,45 +1490,48 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>127283076</v>
+        <v>127283083</v>
       </c>
       <c r="B10" t="n">
-        <v>56855</v>
+        <v>92614</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>100138</v>
+        <v>4361</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Orange taggsvamp</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Hydnellum aurantiacum</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Batsch:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
+      <c r="J10" t="inlineStr"/>
+      <c r="K10" t="inlineStr"/>
+      <c r="N10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
           <t>Gråtängarna, Gstr</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>603964</v>
+        <v>603807</v>
       </c>
       <c r="R10" t="n">
-        <v>6692543</v>
+        <v>6692702</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1563,17 +1566,13 @@
           <t>2025-08-06</t>
         </is>
       </c>
-      <c r="AC10" t="inlineStr">
-        <is>
-          <t>spillning</t>
-        </is>
-      </c>
       <c r="AD10" t="b">
         <v>0</v>
       </c>
       <c r="AE10" t="b">
         <v>0</v>
       </c>
+      <c r="AF10" t="inlineStr"/>
       <c r="AG10" t="b">
         <v>0</v>
       </c>
@@ -1592,48 +1591,45 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>127283083</v>
+        <v>127283076</v>
       </c>
       <c r="B11" t="n">
-        <v>92614</v>
+        <v>56855</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>4361</v>
+        <v>100138</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Orange taggsvamp</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Hydnellum aurantiacum</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Batsch:Fr.) P.Karst.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
-      <c r="J11" t="inlineStr"/>
-      <c r="K11" t="inlineStr"/>
-      <c r="N11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
           <t>Gråtängarna, Gstr</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>603807</v>
+        <v>603964</v>
       </c>
       <c r="R11" t="n">
-        <v>6692702</v>
+        <v>6692543</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1668,13 +1664,17 @@
           <t>2025-08-06</t>
         </is>
       </c>
+      <c r="AC11" t="inlineStr">
+        <is>
+          <t>spillning</t>
+        </is>
+      </c>
       <c r="AD11" t="b">
         <v>0</v>
       </c>
       <c r="AE11" t="b">
         <v>0</v>
       </c>
-      <c r="AF11" t="inlineStr"/>
       <c r="AG11" t="b">
         <v>0</v>
       </c>
@@ -1913,61 +1913,45 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>127290258</v>
+        <v>127290233</v>
       </c>
       <c r="B14" t="n">
-        <v>98450</v>
+        <v>91332</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>220787</v>
+        <v>1202</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I14" t="inlineStr">
-        <is>
-          <t>15</t>
-        </is>
-      </c>
-      <c r="J14" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K14" t="inlineStr">
-        <is>
-          <t>överblommad</t>
-        </is>
-      </c>
-      <c r="L14" t="inlineStr"/>
-      <c r="N14" t="inlineStr"/>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
           <t>Österbyggebo, Gstr</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>603981</v>
+        <v>603850</v>
       </c>
       <c r="R14" t="n">
-        <v>6692427</v>
+        <v>6692680</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2008,7 +1992,6 @@
       <c r="AE14" t="b">
         <v>0</v>
       </c>
-      <c r="AF14" t="inlineStr"/>
       <c r="AG14" t="b">
         <v>0</v>
       </c>
@@ -2027,10 +2010,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>127290233</v>
+        <v>127290255</v>
       </c>
       <c r="B15" t="n">
-        <v>91332</v>
+        <v>91346</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2038,21 +2021,21 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>1202</v>
+        <v>1204</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Gränsticka</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Phellopilus nigrolimitatus</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2062,10 +2045,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>603850</v>
+        <v>603980</v>
       </c>
       <c r="R15" t="n">
-        <v>6692680</v>
+        <v>6692483</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2124,45 +2107,49 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>127290255</v>
+        <v>127283080</v>
       </c>
       <c r="B16" t="n">
-        <v>91346</v>
+        <v>56855</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>1204</v>
+        <v>100138</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Gränsticka</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Phellopilus nigrolimitatus</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
+      <c r="K16" t="inlineStr"/>
+      <c r="L16" t="inlineStr"/>
+      <c r="M16" t="inlineStr"/>
+      <c r="N16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
-          <t>Österbyggebo, Gstr</t>
+          <t>Gråtängarna, Gstr</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>603980</v>
+        <v>603972</v>
       </c>
       <c r="R16" t="n">
-        <v>6692483</v>
+        <v>6692667</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2197,6 +2184,11 @@
           <t>2025-08-06</t>
         </is>
       </c>
+      <c r="AC16" t="inlineStr">
+        <is>
+          <t>Fjäder efter en tjädertupp, 32 cm lång</t>
+        </is>
+      </c>
       <c r="AD16" t="b">
         <v>0</v>
       </c>
@@ -2209,61 +2201,73 @@
       <c r="AT16" t="inlineStr"/>
       <c r="AW16" t="inlineStr">
         <is>
-          <t>Clara Lerbro</t>
+          <t>Beke Regelin</t>
         </is>
       </c>
       <c r="AX16" t="inlineStr">
         <is>
-          <t>Clara Lerbro, Beke Regelin</t>
+          <t>Beke Regelin, Clara Lerbro</t>
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>127283080</v>
+        <v>127290258</v>
       </c>
       <c r="B17" t="n">
-        <v>56855</v>
+        <v>98450</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>100138</v>
+        <v>220787</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
-        </is>
-      </c>
-      <c r="I17" t="inlineStr"/>
-      <c r="K17" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="J17" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K17" t="inlineStr">
+        <is>
+          <t>överblommad</t>
+        </is>
+      </c>
       <c r="L17" t="inlineStr"/>
-      <c r="M17" t="inlineStr"/>
       <c r="N17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
-          <t>Gråtängarna, Gstr</t>
+          <t>Österbyggebo, Gstr</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>603972</v>
+        <v>603981</v>
       </c>
       <c r="R17" t="n">
-        <v>6692667</v>
+        <v>6692427</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2298,29 +2302,25 @@
           <t>2025-08-06</t>
         </is>
       </c>
-      <c r="AC17" t="inlineStr">
-        <is>
-          <t>Fjäder efter en tjädertupp, 32 cm lång</t>
-        </is>
-      </c>
       <c r="AD17" t="b">
         <v>0</v>
       </c>
       <c r="AE17" t="b">
         <v>0</v>
       </c>
+      <c r="AF17" t="inlineStr"/>
       <c r="AG17" t="b">
         <v>0</v>
       </c>
       <c r="AT17" t="inlineStr"/>
       <c r="AW17" t="inlineStr">
         <is>
-          <t>Beke Regelin</t>
+          <t>Clara Lerbro</t>
         </is>
       </c>
       <c r="AX17" t="inlineStr">
         <is>
-          <t>Beke Regelin, Clara Lerbro</t>
+          <t>Clara Lerbro, Beke Regelin</t>
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
@@ -2631,32 +2631,32 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>127290260</v>
+        <v>127290239</v>
       </c>
       <c r="B21" t="n">
-        <v>98450</v>
+        <v>91297</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>220787</v>
+        <v>5447</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2666,10 +2666,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>603977</v>
+        <v>603877</v>
       </c>
       <c r="R21" t="n">
-        <v>6692392</v>
+        <v>6692706</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2837,32 +2837,32 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>127290239</v>
+        <v>127290260</v>
       </c>
       <c r="B23" t="n">
-        <v>91297</v>
+        <v>98450</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>5447</v>
+        <v>220787</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -2872,10 +2872,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>603877</v>
+        <v>603977</v>
       </c>
       <c r="R23" t="n">
-        <v>6692706</v>
+        <v>6692392</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3373,7 +3373,7 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>127290232</v>
+        <v>127290242</v>
       </c>
       <c r="B28" t="n">
         <v>98450</v>
@@ -3403,12 +3403,12 @@
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>9</t>
         </is>
       </c>
       <c r="J28" t="inlineStr">
         <is>
-          <t>dm²</t>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="K28" t="inlineStr">
@@ -3416,16 +3416,18 @@
           <t>överblommad</t>
         </is>
       </c>
+      <c r="L28" t="inlineStr"/>
+      <c r="N28" t="inlineStr"/>
       <c r="P28" t="inlineStr">
         <is>
           <t>Österbyggebo, Gstr</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>603845</v>
+        <v>603879</v>
       </c>
       <c r="R28" t="n">
-        <v>6692678</v>
+        <v>6692700</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3466,6 +3468,7 @@
       <c r="AE28" t="b">
         <v>0</v>
       </c>
+      <c r="AF28" t="inlineStr"/>
       <c r="AG28" t="b">
         <v>0</v>
       </c>
@@ -3484,7 +3487,7 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>127290242</v>
+        <v>127290232</v>
       </c>
       <c r="B29" t="n">
         <v>98450</v>
@@ -3514,12 +3517,12 @@
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>4</t>
         </is>
       </c>
       <c r="J29" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
+          <t>dm²</t>
         </is>
       </c>
       <c r="K29" t="inlineStr">
@@ -3527,18 +3530,16 @@
           <t>överblommad</t>
         </is>
       </c>
-      <c r="L29" t="inlineStr"/>
-      <c r="N29" t="inlineStr"/>
       <c r="P29" t="inlineStr">
         <is>
           <t>Österbyggebo, Gstr</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>603879</v>
+        <v>603845</v>
       </c>
       <c r="R29" t="n">
-        <v>6692700</v>
+        <v>6692678</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3579,7 +3580,6 @@
       <c r="AE29" t="b">
         <v>0</v>
       </c>
-      <c r="AF29" t="inlineStr"/>
       <c r="AG29" t="b">
         <v>0</v>
       </c>

--- a/artfynd/A 31590-2025 artfynd.xlsx
+++ b/artfynd/A 31590-2025 artfynd.xlsx
@@ -2107,49 +2107,61 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>127283080</v>
+        <v>127290258</v>
       </c>
       <c r="B16" t="n">
-        <v>56855</v>
+        <v>98450</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>100138</v>
+        <v>220787</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
-        </is>
-      </c>
-      <c r="I16" t="inlineStr"/>
-      <c r="K16" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="J16" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K16" t="inlineStr">
+        <is>
+          <t>överblommad</t>
+        </is>
+      </c>
       <c r="L16" t="inlineStr"/>
-      <c r="M16" t="inlineStr"/>
       <c r="N16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
-          <t>Gråtängarna, Gstr</t>
+          <t>Österbyggebo, Gstr</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>603972</v>
+        <v>603981</v>
       </c>
       <c r="R16" t="n">
-        <v>6692667</v>
+        <v>6692427</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2184,90 +2196,74 @@
           <t>2025-08-06</t>
         </is>
       </c>
-      <c r="AC16" t="inlineStr">
-        <is>
-          <t>Fjäder efter en tjädertupp, 32 cm lång</t>
-        </is>
-      </c>
       <c r="AD16" t="b">
         <v>0</v>
       </c>
       <c r="AE16" t="b">
         <v>0</v>
       </c>
+      <c r="AF16" t="inlineStr"/>
       <c r="AG16" t="b">
         <v>0</v>
       </c>
       <c r="AT16" t="inlineStr"/>
       <c r="AW16" t="inlineStr">
         <is>
-          <t>Beke Regelin</t>
+          <t>Clara Lerbro</t>
         </is>
       </c>
       <c r="AX16" t="inlineStr">
         <is>
-          <t>Beke Regelin, Clara Lerbro</t>
+          <t>Clara Lerbro, Beke Regelin</t>
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>127290258</v>
+        <v>127283080</v>
       </c>
       <c r="B17" t="n">
-        <v>98450</v>
+        <v>56855</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>220787</v>
+        <v>100138</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I17" t="inlineStr">
-        <is>
-          <t>15</t>
-        </is>
-      </c>
-      <c r="J17" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K17" t="inlineStr">
-        <is>
-          <t>överblommad</t>
-        </is>
-      </c>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr"/>
+      <c r="K17" t="inlineStr"/>
       <c r="L17" t="inlineStr"/>
+      <c r="M17" t="inlineStr"/>
       <c r="N17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
-          <t>Österbyggebo, Gstr</t>
+          <t>Gråtängarna, Gstr</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>603981</v>
+        <v>603972</v>
       </c>
       <c r="R17" t="n">
-        <v>6692427</v>
+        <v>6692667</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2302,25 +2298,29 @@
           <t>2025-08-06</t>
         </is>
       </c>
+      <c r="AC17" t="inlineStr">
+        <is>
+          <t>Fjäder efter en tjädertupp, 32 cm lång</t>
+        </is>
+      </c>
       <c r="AD17" t="b">
         <v>0</v>
       </c>
       <c r="AE17" t="b">
         <v>0</v>
       </c>
-      <c r="AF17" t="inlineStr"/>
       <c r="AG17" t="b">
         <v>0</v>
       </c>
       <c r="AT17" t="inlineStr"/>
       <c r="AW17" t="inlineStr">
         <is>
-          <t>Clara Lerbro</t>
+          <t>Beke Regelin</t>
         </is>
       </c>
       <c r="AX17" t="inlineStr">
         <is>
-          <t>Clara Lerbro, Beke Regelin</t>
+          <t>Beke Regelin, Clara Lerbro</t>
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
@@ -2631,45 +2631,56 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>127290239</v>
+        <v>127290226</v>
       </c>
       <c r="B21" t="n">
-        <v>91297</v>
+        <v>92614</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>5447</v>
+        <v>4361</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Orange taggsvamp</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Hydnellum aurantiacum</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
-        </is>
-      </c>
-      <c r="I21" t="inlineStr"/>
+          <t>(Batsch:Fr.) P.Karst.</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J21" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
+      <c r="K21" t="inlineStr"/>
+      <c r="N21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
           <t>Österbyggebo, Gstr</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>603877</v>
+        <v>603857</v>
       </c>
       <c r="R21" t="n">
-        <v>6692706</v>
+        <v>6692565</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2710,6 +2721,7 @@
       <c r="AE21" t="b">
         <v>0</v>
       </c>
+      <c r="AF21" t="inlineStr"/>
       <c r="AG21" t="b">
         <v>0</v>
       </c>
@@ -2728,56 +2740,45 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>127290226</v>
+        <v>127290239</v>
       </c>
       <c r="B22" t="n">
-        <v>92614</v>
+        <v>91297</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>4361</v>
+        <v>5447</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Orange taggsvamp</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Hydnellum aurantiacum</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Batsch:Fr.) P.Karst.</t>
-        </is>
-      </c>
-      <c r="I22" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="J22" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
-      <c r="K22" t="inlineStr"/>
-      <c r="N22" t="inlineStr"/>
+          <t>(Schwein.) Murrill</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
           <t>Österbyggebo, Gstr</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>603857</v>
+        <v>603877</v>
       </c>
       <c r="R22" t="n">
-        <v>6692565</v>
+        <v>6692706</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2818,7 +2819,6 @@
       <c r="AE22" t="b">
         <v>0</v>
       </c>
-      <c r="AF22" t="inlineStr"/>
       <c r="AG22" t="b">
         <v>0</v>
       </c>
@@ -3695,45 +3695,59 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>127290234</v>
+        <v>127290241</v>
       </c>
       <c r="B31" t="n">
-        <v>91297</v>
+        <v>98450</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>5447</v>
+        <v>220787</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
-        </is>
-      </c>
-      <c r="I31" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="J31" t="inlineStr">
+        <is>
+          <t>dm²</t>
+        </is>
+      </c>
+      <c r="K31" t="inlineStr">
+        <is>
+          <t>överblommad</t>
+        </is>
+      </c>
       <c r="P31" t="inlineStr">
         <is>
           <t>Österbyggebo, Gstr</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>603860</v>
+        <v>603880</v>
       </c>
       <c r="R31" t="n">
-        <v>6692678</v>
+        <v>6692710</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3792,59 +3806,45 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>127290241</v>
+        <v>127290234</v>
       </c>
       <c r="B32" t="n">
-        <v>98450</v>
+        <v>91297</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>220787</v>
+        <v>5447</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I32" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="J32" t="inlineStr">
-        <is>
-          <t>dm²</t>
-        </is>
-      </c>
-      <c r="K32" t="inlineStr">
-        <is>
-          <t>överblommad</t>
-        </is>
-      </c>
+          <t>(Schwein.) Murrill</t>
+        </is>
+      </c>
+      <c r="I32" t="inlineStr"/>
       <c r="P32" t="inlineStr">
         <is>
           <t>Österbyggebo, Gstr</t>
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>603880</v>
+        <v>603860</v>
       </c>
       <c r="R32" t="n">
-        <v>6692710</v>
+        <v>6692678</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>

--- a/artfynd/A 31590-2025 artfynd.xlsx
+++ b/artfynd/A 31590-2025 artfynd.xlsx
@@ -2107,61 +2107,49 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>127290258</v>
+        <v>127283080</v>
       </c>
       <c r="B16" t="n">
-        <v>98450</v>
+        <v>56855</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>220787</v>
+        <v>100138</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I16" t="inlineStr">
-        <is>
-          <t>15</t>
-        </is>
-      </c>
-      <c r="J16" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K16" t="inlineStr">
-        <is>
-          <t>överblommad</t>
-        </is>
-      </c>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr"/>
+      <c r="K16" t="inlineStr"/>
       <c r="L16" t="inlineStr"/>
+      <c r="M16" t="inlineStr"/>
       <c r="N16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
-          <t>Österbyggebo, Gstr</t>
+          <t>Gråtängarna, Gstr</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>603981</v>
+        <v>603972</v>
       </c>
       <c r="R16" t="n">
-        <v>6692427</v>
+        <v>6692667</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2196,74 +2184,90 @@
           <t>2025-08-06</t>
         </is>
       </c>
+      <c r="AC16" t="inlineStr">
+        <is>
+          <t>Fjäder efter en tjädertupp, 32 cm lång</t>
+        </is>
+      </c>
       <c r="AD16" t="b">
         <v>0</v>
       </c>
       <c r="AE16" t="b">
         <v>0</v>
       </c>
-      <c r="AF16" t="inlineStr"/>
       <c r="AG16" t="b">
         <v>0</v>
       </c>
       <c r="AT16" t="inlineStr"/>
       <c r="AW16" t="inlineStr">
         <is>
-          <t>Clara Lerbro</t>
+          <t>Beke Regelin</t>
         </is>
       </c>
       <c r="AX16" t="inlineStr">
         <is>
-          <t>Clara Lerbro, Beke Regelin</t>
+          <t>Beke Regelin, Clara Lerbro</t>
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>127283080</v>
+        <v>127290258</v>
       </c>
       <c r="B17" t="n">
-        <v>56855</v>
+        <v>98450</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>100138</v>
+        <v>220787</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
-        </is>
-      </c>
-      <c r="I17" t="inlineStr"/>
-      <c r="K17" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="J17" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K17" t="inlineStr">
+        <is>
+          <t>överblommad</t>
+        </is>
+      </c>
       <c r="L17" t="inlineStr"/>
-      <c r="M17" t="inlineStr"/>
       <c r="N17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
-          <t>Gråtängarna, Gstr</t>
+          <t>Österbyggebo, Gstr</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>603972</v>
+        <v>603981</v>
       </c>
       <c r="R17" t="n">
-        <v>6692667</v>
+        <v>6692427</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2298,29 +2302,25 @@
           <t>2025-08-06</t>
         </is>
       </c>
-      <c r="AC17" t="inlineStr">
-        <is>
-          <t>Fjäder efter en tjädertupp, 32 cm lång</t>
-        </is>
-      </c>
       <c r="AD17" t="b">
         <v>0</v>
       </c>
       <c r="AE17" t="b">
         <v>0</v>
       </c>
+      <c r="AF17" t="inlineStr"/>
       <c r="AG17" t="b">
         <v>0</v>
       </c>
       <c r="AT17" t="inlineStr"/>
       <c r="AW17" t="inlineStr">
         <is>
-          <t>Beke Regelin</t>
+          <t>Clara Lerbro</t>
         </is>
       </c>
       <c r="AX17" t="inlineStr">
         <is>
-          <t>Beke Regelin, Clara Lerbro</t>
+          <t>Clara Lerbro, Beke Regelin</t>
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
@@ -3373,7 +3373,7 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>127290242</v>
+        <v>127290232</v>
       </c>
       <c r="B28" t="n">
         <v>98450</v>
@@ -3403,12 +3403,12 @@
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>4</t>
         </is>
       </c>
       <c r="J28" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
+          <t>dm²</t>
         </is>
       </c>
       <c r="K28" t="inlineStr">
@@ -3416,18 +3416,16 @@
           <t>överblommad</t>
         </is>
       </c>
-      <c r="L28" t="inlineStr"/>
-      <c r="N28" t="inlineStr"/>
       <c r="P28" t="inlineStr">
         <is>
           <t>Österbyggebo, Gstr</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>603879</v>
+        <v>603845</v>
       </c>
       <c r="R28" t="n">
-        <v>6692700</v>
+        <v>6692678</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3468,7 +3466,6 @@
       <c r="AE28" t="b">
         <v>0</v>
       </c>
-      <c r="AF28" t="inlineStr"/>
       <c r="AG28" t="b">
         <v>0</v>
       </c>
@@ -3487,7 +3484,7 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>127290232</v>
+        <v>127290242</v>
       </c>
       <c r="B29" t="n">
         <v>98450</v>
@@ -3517,12 +3514,12 @@
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>9</t>
         </is>
       </c>
       <c r="J29" t="inlineStr">
         <is>
-          <t>dm²</t>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="K29" t="inlineStr">
@@ -3530,16 +3527,18 @@
           <t>överblommad</t>
         </is>
       </c>
+      <c r="L29" t="inlineStr"/>
+      <c r="N29" t="inlineStr"/>
       <c r="P29" t="inlineStr">
         <is>
           <t>Österbyggebo, Gstr</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>603845</v>
+        <v>603879</v>
       </c>
       <c r="R29" t="n">
-        <v>6692678</v>
+        <v>6692700</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3580,6 +3579,7 @@
       <c r="AE29" t="b">
         <v>0</v>
       </c>
+      <c r="AF29" t="inlineStr"/>
       <c r="AG29" t="b">
         <v>0</v>
       </c>
@@ -3695,59 +3695,45 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>127290241</v>
+        <v>127290234</v>
       </c>
       <c r="B31" t="n">
-        <v>98450</v>
+        <v>91297</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>220787</v>
+        <v>5447</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I31" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="J31" t="inlineStr">
-        <is>
-          <t>dm²</t>
-        </is>
-      </c>
-      <c r="K31" t="inlineStr">
-        <is>
-          <t>överblommad</t>
-        </is>
-      </c>
+          <t>(Schwein.) Murrill</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr"/>
       <c r="P31" t="inlineStr">
         <is>
           <t>Österbyggebo, Gstr</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>603880</v>
+        <v>603860</v>
       </c>
       <c r="R31" t="n">
-        <v>6692710</v>
+        <v>6692678</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3806,45 +3792,59 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>127290234</v>
+        <v>127290241</v>
       </c>
       <c r="B32" t="n">
-        <v>91297</v>
+        <v>98450</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>5447</v>
+        <v>220787</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
-        </is>
-      </c>
-      <c r="I32" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I32" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="J32" t="inlineStr">
+        <is>
+          <t>dm²</t>
+        </is>
+      </c>
+      <c r="K32" t="inlineStr">
+        <is>
+          <t>överblommad</t>
+        </is>
+      </c>
       <c r="P32" t="inlineStr">
         <is>
           <t>Österbyggebo, Gstr</t>
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>603860</v>
+        <v>603880</v>
       </c>
       <c r="R32" t="n">
-        <v>6692678</v>
+        <v>6692710</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>

--- a/artfynd/A 31590-2025 artfynd.xlsx
+++ b/artfynd/A 31590-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>127264982</v>
       </c>
       <c r="B2" t="n">
-        <v>98450</v>
+        <v>98456</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -793,7 +793,7 @@
         <v>127283088</v>
       </c>
       <c r="B3" t="n">
-        <v>105488</v>
+        <v>105494</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -894,7 +894,7 @@
         <v>127264978</v>
       </c>
       <c r="B4" t="n">
-        <v>97327</v>
+        <v>97333</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -992,7 +992,7 @@
         <v>127283086</v>
       </c>
       <c r="B5" t="n">
-        <v>98450</v>
+        <v>98456</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1093,7 +1093,7 @@
         <v>127283078</v>
       </c>
       <c r="B6" t="n">
-        <v>91297</v>
+        <v>91303</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1194,7 +1194,7 @@
         <v>127264973</v>
       </c>
       <c r="B7" t="n">
-        <v>97327</v>
+        <v>97333</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1291,7 +1291,7 @@
         <v>127283087</v>
       </c>
       <c r="B8" t="n">
-        <v>105488</v>
+        <v>105494</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1392,7 +1392,7 @@
         <v>127283085</v>
       </c>
       <c r="B9" t="n">
-        <v>98450</v>
+        <v>98456</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1493,7 +1493,7 @@
         <v>127283083</v>
       </c>
       <c r="B10" t="n">
-        <v>92614</v>
+        <v>92620</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1696,7 +1696,7 @@
         <v>127283084</v>
       </c>
       <c r="B12" t="n">
-        <v>98450</v>
+        <v>98456</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1802,7 +1802,7 @@
         <v>127290259</v>
       </c>
       <c r="B13" t="n">
-        <v>98450</v>
+        <v>98456</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1916,7 +1916,7 @@
         <v>127290233</v>
       </c>
       <c r="B14" t="n">
-        <v>91332</v>
+        <v>91338</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2013,7 +2013,7 @@
         <v>127290255</v>
       </c>
       <c r="B15" t="n">
-        <v>91346</v>
+        <v>91352</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2107,49 +2107,61 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>127283080</v>
+        <v>127290258</v>
       </c>
       <c r="B16" t="n">
-        <v>56855</v>
+        <v>98456</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>100138</v>
+        <v>220787</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
-        </is>
-      </c>
-      <c r="I16" t="inlineStr"/>
-      <c r="K16" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="J16" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K16" t="inlineStr">
+        <is>
+          <t>överblommad</t>
+        </is>
+      </c>
       <c r="L16" t="inlineStr"/>
-      <c r="M16" t="inlineStr"/>
       <c r="N16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
-          <t>Gråtängarna, Gstr</t>
+          <t>Österbyggebo, Gstr</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>603972</v>
+        <v>603981</v>
       </c>
       <c r="R16" t="n">
-        <v>6692667</v>
+        <v>6692427</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2184,90 +2196,74 @@
           <t>2025-08-06</t>
         </is>
       </c>
-      <c r="AC16" t="inlineStr">
-        <is>
-          <t>Fjäder efter en tjädertupp, 32 cm lång</t>
-        </is>
-      </c>
       <c r="AD16" t="b">
         <v>0</v>
       </c>
       <c r="AE16" t="b">
         <v>0</v>
       </c>
+      <c r="AF16" t="inlineStr"/>
       <c r="AG16" t="b">
         <v>0</v>
       </c>
       <c r="AT16" t="inlineStr"/>
       <c r="AW16" t="inlineStr">
         <is>
-          <t>Beke Regelin</t>
+          <t>Clara Lerbro</t>
         </is>
       </c>
       <c r="AX16" t="inlineStr">
         <is>
-          <t>Beke Regelin, Clara Lerbro</t>
+          <t>Clara Lerbro, Beke Regelin</t>
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>127290258</v>
+        <v>127283080</v>
       </c>
       <c r="B17" t="n">
-        <v>98450</v>
+        <v>56855</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>220787</v>
+        <v>100138</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I17" t="inlineStr">
-        <is>
-          <t>15</t>
-        </is>
-      </c>
-      <c r="J17" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K17" t="inlineStr">
-        <is>
-          <t>överblommad</t>
-        </is>
-      </c>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr"/>
+      <c r="K17" t="inlineStr"/>
       <c r="L17" t="inlineStr"/>
+      <c r="M17" t="inlineStr"/>
       <c r="N17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
-          <t>Österbyggebo, Gstr</t>
+          <t>Gråtängarna, Gstr</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>603981</v>
+        <v>603972</v>
       </c>
       <c r="R17" t="n">
-        <v>6692427</v>
+        <v>6692667</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2302,25 +2298,29 @@
           <t>2025-08-06</t>
         </is>
       </c>
+      <c r="AC17" t="inlineStr">
+        <is>
+          <t>Fjäder efter en tjädertupp, 32 cm lång</t>
+        </is>
+      </c>
       <c r="AD17" t="b">
         <v>0</v>
       </c>
       <c r="AE17" t="b">
         <v>0</v>
       </c>
-      <c r="AF17" t="inlineStr"/>
       <c r="AG17" t="b">
         <v>0</v>
       </c>
       <c r="AT17" t="inlineStr"/>
       <c r="AW17" t="inlineStr">
         <is>
-          <t>Clara Lerbro</t>
+          <t>Beke Regelin</t>
         </is>
       </c>
       <c r="AX17" t="inlineStr">
         <is>
-          <t>Clara Lerbro, Beke Regelin</t>
+          <t>Beke Regelin, Clara Lerbro</t>
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
@@ -2330,7 +2330,7 @@
         <v>127290240</v>
       </c>
       <c r="B18" t="n">
-        <v>98450</v>
+        <v>98456</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2440,7 +2440,7 @@
         <v>127290254</v>
       </c>
       <c r="B19" t="n">
-        <v>91297</v>
+        <v>91303</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2537,7 +2537,7 @@
         <v>127290227</v>
       </c>
       <c r="B20" t="n">
-        <v>91332</v>
+        <v>91338</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2634,7 +2634,7 @@
         <v>127290226</v>
       </c>
       <c r="B21" t="n">
-        <v>92614</v>
+        <v>92620</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2743,7 +2743,7 @@
         <v>127290239</v>
       </c>
       <c r="B22" t="n">
-        <v>91297</v>
+        <v>91303</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2840,7 +2840,7 @@
         <v>127290260</v>
       </c>
       <c r="B23" t="n">
-        <v>98450</v>
+        <v>98456</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2937,7 +2937,7 @@
         <v>127290244</v>
       </c>
       <c r="B24" t="n">
-        <v>98450</v>
+        <v>98456</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3051,7 +3051,7 @@
         <v>127290238</v>
       </c>
       <c r="B25" t="n">
-        <v>98450</v>
+        <v>98456</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3165,7 +3165,7 @@
         <v>127290246</v>
       </c>
       <c r="B26" t="n">
-        <v>92622</v>
+        <v>92628</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3262,7 +3262,7 @@
         <v>127290225</v>
       </c>
       <c r="B27" t="n">
-        <v>98450</v>
+        <v>98456</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3373,10 +3373,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>127290232</v>
+        <v>127290242</v>
       </c>
       <c r="B28" t="n">
-        <v>98450</v>
+        <v>98456</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3403,12 +3403,12 @@
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>9</t>
         </is>
       </c>
       <c r="J28" t="inlineStr">
         <is>
-          <t>dm²</t>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="K28" t="inlineStr">
@@ -3416,16 +3416,18 @@
           <t>överblommad</t>
         </is>
       </c>
+      <c r="L28" t="inlineStr"/>
+      <c r="N28" t="inlineStr"/>
       <c r="P28" t="inlineStr">
         <is>
           <t>Österbyggebo, Gstr</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>603845</v>
+        <v>603879</v>
       </c>
       <c r="R28" t="n">
-        <v>6692678</v>
+        <v>6692700</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3466,6 +3468,7 @@
       <c r="AE28" t="b">
         <v>0</v>
       </c>
+      <c r="AF28" t="inlineStr"/>
       <c r="AG28" t="b">
         <v>0</v>
       </c>
@@ -3484,10 +3487,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>127290242</v>
+        <v>127290232</v>
       </c>
       <c r="B29" t="n">
-        <v>98450</v>
+        <v>98456</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3514,12 +3517,12 @@
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>4</t>
         </is>
       </c>
       <c r="J29" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
+          <t>dm²</t>
         </is>
       </c>
       <c r="K29" t="inlineStr">
@@ -3527,18 +3530,16 @@
           <t>överblommad</t>
         </is>
       </c>
-      <c r="L29" t="inlineStr"/>
-      <c r="N29" t="inlineStr"/>
       <c r="P29" t="inlineStr">
         <is>
           <t>Österbyggebo, Gstr</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>603879</v>
+        <v>603845</v>
       </c>
       <c r="R29" t="n">
-        <v>6692700</v>
+        <v>6692678</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3579,7 +3580,6 @@
       <c r="AE29" t="b">
         <v>0</v>
       </c>
-      <c r="AF29" t="inlineStr"/>
       <c r="AG29" t="b">
         <v>0</v>
       </c>
@@ -3601,7 +3601,7 @@
         <v>127290257</v>
       </c>
       <c r="B30" t="n">
-        <v>91297</v>
+        <v>91303</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3698,7 +3698,7 @@
         <v>127290234</v>
       </c>
       <c r="B31" t="n">
-        <v>91297</v>
+        <v>91303</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3795,7 +3795,7 @@
         <v>127290241</v>
       </c>
       <c r="B32" t="n">
-        <v>98450</v>
+        <v>98456</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3906,7 +3906,7 @@
         <v>127290230</v>
       </c>
       <c r="B33" t="n">
-        <v>91297</v>
+        <v>91303</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4003,7 +4003,7 @@
         <v>127290250</v>
       </c>
       <c r="B34" t="n">
-        <v>105488</v>
+        <v>105494</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4113,7 +4113,7 @@
         <v>127290235</v>
       </c>
       <c r="B35" t="n">
-        <v>105488</v>
+        <v>105494</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>

--- a/artfynd/A 31590-2025 artfynd.xlsx
+++ b/artfynd/A 31590-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>127264982</v>
       </c>
       <c r="B2" t="n">
-        <v>98456</v>
+        <v>98459</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -793,7 +793,7 @@
         <v>127283088</v>
       </c>
       <c r="B3" t="n">
-        <v>105494</v>
+        <v>105497</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -894,7 +894,7 @@
         <v>127264978</v>
       </c>
       <c r="B4" t="n">
-        <v>97333</v>
+        <v>97336</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -992,7 +992,7 @@
         <v>127283086</v>
       </c>
       <c r="B5" t="n">
-        <v>98456</v>
+        <v>98459</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1093,7 +1093,7 @@
         <v>127283078</v>
       </c>
       <c r="B6" t="n">
-        <v>91303</v>
+        <v>91306</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1194,7 +1194,7 @@
         <v>127264973</v>
       </c>
       <c r="B7" t="n">
-        <v>97333</v>
+        <v>97336</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1291,7 +1291,7 @@
         <v>127283087</v>
       </c>
       <c r="B8" t="n">
-        <v>105494</v>
+        <v>105497</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1392,7 +1392,7 @@
         <v>127283085</v>
       </c>
       <c r="B9" t="n">
-        <v>98456</v>
+        <v>98459</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1493,7 +1493,7 @@
         <v>127283083</v>
       </c>
       <c r="B10" t="n">
-        <v>92620</v>
+        <v>92623</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1594,7 +1594,7 @@
         <v>127283076</v>
       </c>
       <c r="B11" t="n">
-        <v>56855</v>
+        <v>56858</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1696,7 +1696,7 @@
         <v>127283084</v>
       </c>
       <c r="B12" t="n">
-        <v>98456</v>
+        <v>98459</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1802,7 +1802,7 @@
         <v>127290259</v>
       </c>
       <c r="B13" t="n">
-        <v>98456</v>
+        <v>98459</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1913,45 +1913,61 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>127290233</v>
+        <v>127290258</v>
       </c>
       <c r="B14" t="n">
-        <v>91338</v>
+        <v>98459</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>1202</v>
+        <v>220787</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I14" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="J14" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K14" t="inlineStr">
+        <is>
+          <t>överblommad</t>
+        </is>
+      </c>
+      <c r="L14" t="inlineStr"/>
+      <c r="N14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
           <t>Österbyggebo, Gstr</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>603850</v>
+        <v>603981</v>
       </c>
       <c r="R14" t="n">
-        <v>6692680</v>
+        <v>6692427</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -1992,6 +2008,7 @@
       <c r="AE14" t="b">
         <v>0</v>
       </c>
+      <c r="AF14" t="inlineStr"/>
       <c r="AG14" t="b">
         <v>0</v>
       </c>
@@ -2010,10 +2027,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>127290255</v>
+        <v>127290233</v>
       </c>
       <c r="B15" t="n">
-        <v>91352</v>
+        <v>91341</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2021,21 +2038,21 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>1204</v>
+        <v>1202</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Gränsticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Phellopilus nigrolimitatus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2045,10 +2062,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>603980</v>
+        <v>603850</v>
       </c>
       <c r="R15" t="n">
-        <v>6692483</v>
+        <v>6692680</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2107,61 +2124,45 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>127290258</v>
+        <v>127290255</v>
       </c>
       <c r="B16" t="n">
-        <v>98456</v>
+        <v>91355</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>220787</v>
+        <v>1204</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Gränsticka</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellopilus nigrolimitatus</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I16" t="inlineStr">
-        <is>
-          <t>15</t>
-        </is>
-      </c>
-      <c r="J16" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K16" t="inlineStr">
-        <is>
-          <t>överblommad</t>
-        </is>
-      </c>
-      <c r="L16" t="inlineStr"/>
-      <c r="N16" t="inlineStr"/>
+          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
           <t>Österbyggebo, Gstr</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>603981</v>
+        <v>603980</v>
       </c>
       <c r="R16" t="n">
-        <v>6692427</v>
+        <v>6692483</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2202,7 +2203,6 @@
       <c r="AE16" t="b">
         <v>0</v>
       </c>
-      <c r="AF16" t="inlineStr"/>
       <c r="AG16" t="b">
         <v>0</v>
       </c>
@@ -2224,7 +2224,7 @@
         <v>127283080</v>
       </c>
       <c r="B17" t="n">
-        <v>56855</v>
+        <v>56858</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2330,7 +2330,7 @@
         <v>127290240</v>
       </c>
       <c r="B18" t="n">
-        <v>98456</v>
+        <v>98459</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2440,7 +2440,7 @@
         <v>127290254</v>
       </c>
       <c r="B19" t="n">
-        <v>91303</v>
+        <v>91306</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2537,7 +2537,7 @@
         <v>127290227</v>
       </c>
       <c r="B20" t="n">
-        <v>91338</v>
+        <v>91341</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2631,56 +2631,45 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>127290226</v>
+        <v>127290260</v>
       </c>
       <c r="B21" t="n">
-        <v>92620</v>
+        <v>98459</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>4361</v>
+        <v>220787</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Orange taggsvamp</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Hydnellum aurantiacum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Batsch:Fr.) P.Karst.</t>
-        </is>
-      </c>
-      <c r="I21" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="J21" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
-      <c r="K21" t="inlineStr"/>
-      <c r="N21" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
           <t>Österbyggebo, Gstr</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>603857</v>
+        <v>603977</v>
       </c>
       <c r="R21" t="n">
-        <v>6692565</v>
+        <v>6692392</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2721,7 +2710,6 @@
       <c r="AE21" t="b">
         <v>0</v>
       </c>
-      <c r="AF21" t="inlineStr"/>
       <c r="AG21" t="b">
         <v>0</v>
       </c>
@@ -2740,45 +2728,56 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>127290239</v>
+        <v>127290226</v>
       </c>
       <c r="B22" t="n">
-        <v>91303</v>
+        <v>92623</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>5447</v>
+        <v>4361</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Orange taggsvamp</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Hydnellum aurantiacum</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
-        </is>
-      </c>
-      <c r="I22" t="inlineStr"/>
+          <t>(Batsch:Fr.) P.Karst.</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J22" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
+      <c r="K22" t="inlineStr"/>
+      <c r="N22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
           <t>Österbyggebo, Gstr</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>603877</v>
+        <v>603857</v>
       </c>
       <c r="R22" t="n">
-        <v>6692706</v>
+        <v>6692565</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2819,6 +2818,7 @@
       <c r="AE22" t="b">
         <v>0</v>
       </c>
+      <c r="AF22" t="inlineStr"/>
       <c r="AG22" t="b">
         <v>0</v>
       </c>
@@ -2837,32 +2837,32 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>127290260</v>
+        <v>127290239</v>
       </c>
       <c r="B23" t="n">
-        <v>98456</v>
+        <v>91306</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>220787</v>
+        <v>5447</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -2872,10 +2872,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>603977</v>
+        <v>603877</v>
       </c>
       <c r="R23" t="n">
-        <v>6692392</v>
+        <v>6692706</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -2937,7 +2937,7 @@
         <v>127290244</v>
       </c>
       <c r="B24" t="n">
-        <v>98456</v>
+        <v>98459</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3051,7 +3051,7 @@
         <v>127290238</v>
       </c>
       <c r="B25" t="n">
-        <v>98456</v>
+        <v>98459</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3165,7 +3165,7 @@
         <v>127290246</v>
       </c>
       <c r="B26" t="n">
-        <v>92628</v>
+        <v>92631</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3262,7 +3262,7 @@
         <v>127290225</v>
       </c>
       <c r="B27" t="n">
-        <v>98456</v>
+        <v>98459</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3373,10 +3373,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>127290242</v>
+        <v>127290232</v>
       </c>
       <c r="B28" t="n">
-        <v>98456</v>
+        <v>98459</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3403,12 +3403,12 @@
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>4</t>
         </is>
       </c>
       <c r="J28" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
+          <t>dm²</t>
         </is>
       </c>
       <c r="K28" t="inlineStr">
@@ -3416,18 +3416,16 @@
           <t>överblommad</t>
         </is>
       </c>
-      <c r="L28" t="inlineStr"/>
-      <c r="N28" t="inlineStr"/>
       <c r="P28" t="inlineStr">
         <is>
           <t>Österbyggebo, Gstr</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>603879</v>
+        <v>603845</v>
       </c>
       <c r="R28" t="n">
-        <v>6692700</v>
+        <v>6692678</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3468,7 +3466,6 @@
       <c r="AE28" t="b">
         <v>0</v>
       </c>
-      <c r="AF28" t="inlineStr"/>
       <c r="AG28" t="b">
         <v>0</v>
       </c>
@@ -3487,10 +3484,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>127290232</v>
+        <v>127290242</v>
       </c>
       <c r="B29" t="n">
-        <v>98456</v>
+        <v>98459</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3517,12 +3514,12 @@
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>9</t>
         </is>
       </c>
       <c r="J29" t="inlineStr">
         <is>
-          <t>dm²</t>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="K29" t="inlineStr">
@@ -3530,16 +3527,18 @@
           <t>överblommad</t>
         </is>
       </c>
+      <c r="L29" t="inlineStr"/>
+      <c r="N29" t="inlineStr"/>
       <c r="P29" t="inlineStr">
         <is>
           <t>Österbyggebo, Gstr</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>603845</v>
+        <v>603879</v>
       </c>
       <c r="R29" t="n">
-        <v>6692678</v>
+        <v>6692700</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3580,6 +3579,7 @@
       <c r="AE29" t="b">
         <v>0</v>
       </c>
+      <c r="AF29" t="inlineStr"/>
       <c r="AG29" t="b">
         <v>0</v>
       </c>
@@ -3601,7 +3601,7 @@
         <v>127290257</v>
       </c>
       <c r="B30" t="n">
-        <v>91303</v>
+        <v>91306</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3698,7 +3698,7 @@
         <v>127290234</v>
       </c>
       <c r="B31" t="n">
-        <v>91303</v>
+        <v>91306</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3795,7 +3795,7 @@
         <v>127290241</v>
       </c>
       <c r="B32" t="n">
-        <v>98456</v>
+        <v>98459</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3906,7 +3906,7 @@
         <v>127290230</v>
       </c>
       <c r="B33" t="n">
-        <v>91303</v>
+        <v>91306</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4003,7 +4003,7 @@
         <v>127290250</v>
       </c>
       <c r="B34" t="n">
-        <v>105494</v>
+        <v>105497</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4113,7 +4113,7 @@
         <v>127290235</v>
       </c>
       <c r="B35" t="n">
-        <v>105494</v>
+        <v>105497</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>

--- a/artfynd/A 31590-2025 artfynd.xlsx
+++ b/artfynd/A 31590-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>127264982</v>
       </c>
       <c r="B2" t="n">
-        <v>98459</v>
+        <v>98467</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -793,7 +793,7 @@
         <v>127283088</v>
       </c>
       <c r="B3" t="n">
-        <v>105497</v>
+        <v>105505</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -894,7 +894,7 @@
         <v>127264978</v>
       </c>
       <c r="B4" t="n">
-        <v>97336</v>
+        <v>97344</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -992,7 +992,7 @@
         <v>127283086</v>
       </c>
       <c r="B5" t="n">
-        <v>98459</v>
+        <v>98467</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1093,7 +1093,7 @@
         <v>127283078</v>
       </c>
       <c r="B6" t="n">
-        <v>91306</v>
+        <v>91314</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1194,7 +1194,7 @@
         <v>127264973</v>
       </c>
       <c r="B7" t="n">
-        <v>97336</v>
+        <v>97344</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1291,7 +1291,7 @@
         <v>127283087</v>
       </c>
       <c r="B8" t="n">
-        <v>105497</v>
+        <v>105505</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1392,7 +1392,7 @@
         <v>127283085</v>
       </c>
       <c r="B9" t="n">
-        <v>98459</v>
+        <v>98467</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1493,7 +1493,7 @@
         <v>127283083</v>
       </c>
       <c r="B10" t="n">
-        <v>92623</v>
+        <v>92631</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1594,7 +1594,7 @@
         <v>127283076</v>
       </c>
       <c r="B11" t="n">
-        <v>56858</v>
+        <v>56864</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1696,7 +1696,7 @@
         <v>127283084</v>
       </c>
       <c r="B12" t="n">
-        <v>98459</v>
+        <v>98467</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1802,7 +1802,7 @@
         <v>127290259</v>
       </c>
       <c r="B13" t="n">
-        <v>98459</v>
+        <v>98467</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1906,68 +1906,52 @@
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>Clara Lerbro, Beke Regelin</t>
+          <t>Beke Regelin, Clara Lerbro</t>
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>127290258</v>
+        <v>127290233</v>
       </c>
       <c r="B14" t="n">
-        <v>98459</v>
+        <v>91349</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>220787</v>
+        <v>1202</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I14" t="inlineStr">
-        <is>
-          <t>15</t>
-        </is>
-      </c>
-      <c r="J14" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K14" t="inlineStr">
-        <is>
-          <t>överblommad</t>
-        </is>
-      </c>
-      <c r="L14" t="inlineStr"/>
-      <c r="N14" t="inlineStr"/>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
           <t>Österbyggebo, Gstr</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>603981</v>
+        <v>603850</v>
       </c>
       <c r="R14" t="n">
-        <v>6692427</v>
+        <v>6692680</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2008,7 +1992,6 @@
       <c r="AE14" t="b">
         <v>0</v>
       </c>
-      <c r="AF14" t="inlineStr"/>
       <c r="AG14" t="b">
         <v>0</v>
       </c>
@@ -2020,17 +2003,17 @@
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>Clara Lerbro, Beke Regelin</t>
+          <t>Beke Regelin, Clara Lerbro</t>
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>127290233</v>
+        <v>127290255</v>
       </c>
       <c r="B15" t="n">
-        <v>91341</v>
+        <v>91363</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2038,21 +2021,21 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>1202</v>
+        <v>1204</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Gränsticka</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Phellopilus nigrolimitatus</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2062,10 +2045,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>603850</v>
+        <v>603980</v>
       </c>
       <c r="R15" t="n">
-        <v>6692680</v>
+        <v>6692483</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2117,52 +2100,56 @@
       </c>
       <c r="AX15" t="inlineStr">
         <is>
-          <t>Clara Lerbro, Beke Regelin</t>
+          <t>Beke Regelin, Clara Lerbro</t>
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>127290255</v>
+        <v>127283080</v>
       </c>
       <c r="B16" t="n">
-        <v>91355</v>
+        <v>56864</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>1204</v>
+        <v>100138</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Gränsticka</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Phellopilus nigrolimitatus</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
+      <c r="K16" t="inlineStr"/>
+      <c r="L16" t="inlineStr"/>
+      <c r="M16" t="inlineStr"/>
+      <c r="N16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
-          <t>Österbyggebo, Gstr</t>
+          <t>Gråtängarna, Gstr</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>603980</v>
+        <v>603972</v>
       </c>
       <c r="R16" t="n">
-        <v>6692483</v>
+        <v>6692667</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2197,6 +2184,11 @@
           <t>2025-08-06</t>
         </is>
       </c>
+      <c r="AC16" t="inlineStr">
+        <is>
+          <t>Fjäder efter en tjädertupp, 32 cm lång</t>
+        </is>
+      </c>
       <c r="AD16" t="b">
         <v>0</v>
       </c>
@@ -2209,61 +2201,73 @@
       <c r="AT16" t="inlineStr"/>
       <c r="AW16" t="inlineStr">
         <is>
-          <t>Clara Lerbro</t>
+          <t>Beke Regelin</t>
         </is>
       </c>
       <c r="AX16" t="inlineStr">
         <is>
-          <t>Clara Lerbro, Beke Regelin</t>
+          <t>Beke Regelin, Clara Lerbro</t>
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>127283080</v>
+        <v>127290258</v>
       </c>
       <c r="B17" t="n">
-        <v>56858</v>
+        <v>98467</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>100138</v>
+        <v>220787</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
-        </is>
-      </c>
-      <c r="I17" t="inlineStr"/>
-      <c r="K17" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="J17" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K17" t="inlineStr">
+        <is>
+          <t>överblommad</t>
+        </is>
+      </c>
       <c r="L17" t="inlineStr"/>
-      <c r="M17" t="inlineStr"/>
       <c r="N17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
-          <t>Gråtängarna, Gstr</t>
+          <t>Österbyggebo, Gstr</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>603972</v>
+        <v>603981</v>
       </c>
       <c r="R17" t="n">
-        <v>6692667</v>
+        <v>6692427</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2298,24 +2302,20 @@
           <t>2025-08-06</t>
         </is>
       </c>
-      <c r="AC17" t="inlineStr">
-        <is>
-          <t>Fjäder efter en tjädertupp, 32 cm lång</t>
-        </is>
-      </c>
       <c r="AD17" t="b">
         <v>0</v>
       </c>
       <c r="AE17" t="b">
         <v>0</v>
       </c>
+      <c r="AF17" t="inlineStr"/>
       <c r="AG17" t="b">
         <v>0</v>
       </c>
       <c r="AT17" t="inlineStr"/>
       <c r="AW17" t="inlineStr">
         <is>
-          <t>Beke Regelin</t>
+          <t>Clara Lerbro</t>
         </is>
       </c>
       <c r="AX17" t="inlineStr">
@@ -2330,7 +2330,7 @@
         <v>127290240</v>
       </c>
       <c r="B18" t="n">
-        <v>98459</v>
+        <v>98467</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2430,7 +2430,7 @@
       </c>
       <c r="AX18" t="inlineStr">
         <is>
-          <t>Clara Lerbro, Beke Regelin</t>
+          <t>Beke Regelin, Clara Lerbro</t>
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
@@ -2440,7 +2440,7 @@
         <v>127290254</v>
       </c>
       <c r="B19" t="n">
-        <v>91306</v>
+        <v>91314</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2527,7 +2527,7 @@
       </c>
       <c r="AX19" t="inlineStr">
         <is>
-          <t>Clara Lerbro, Beke Regelin</t>
+          <t>Beke Regelin, Clara Lerbro</t>
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
@@ -2537,7 +2537,7 @@
         <v>127290227</v>
       </c>
       <c r="B20" t="n">
-        <v>91341</v>
+        <v>91349</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2631,45 +2631,56 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>127290260</v>
+        <v>127290226</v>
       </c>
       <c r="B21" t="n">
-        <v>98459</v>
+        <v>92631</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>220787</v>
+        <v>4361</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Orange taggsvamp</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hydnellum aurantiacum</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I21" t="inlineStr"/>
+          <t>(Batsch:Fr.) P.Karst.</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J21" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
+      <c r="K21" t="inlineStr"/>
+      <c r="N21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
           <t>Österbyggebo, Gstr</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>603977</v>
+        <v>603857</v>
       </c>
       <c r="R21" t="n">
-        <v>6692392</v>
+        <v>6692565</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2710,6 +2721,7 @@
       <c r="AE21" t="b">
         <v>0</v>
       </c>
+      <c r="AF21" t="inlineStr"/>
       <c r="AG21" t="b">
         <v>0</v>
       </c>
@@ -2728,56 +2740,45 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>127290226</v>
+        <v>127290239</v>
       </c>
       <c r="B22" t="n">
-        <v>92623</v>
+        <v>91314</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>4361</v>
+        <v>5447</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Orange taggsvamp</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Hydnellum aurantiacum</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Batsch:Fr.) P.Karst.</t>
-        </is>
-      </c>
-      <c r="I22" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="J22" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
-      <c r="K22" t="inlineStr"/>
-      <c r="N22" t="inlineStr"/>
+          <t>(Schwein.) Murrill</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
           <t>Österbyggebo, Gstr</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>603857</v>
+        <v>603877</v>
       </c>
       <c r="R22" t="n">
-        <v>6692565</v>
+        <v>6692706</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2818,7 +2819,6 @@
       <c r="AE22" t="b">
         <v>0</v>
       </c>
-      <c r="AF22" t="inlineStr"/>
       <c r="AG22" t="b">
         <v>0</v>
       </c>
@@ -2830,39 +2830,39 @@
       </c>
       <c r="AX22" t="inlineStr">
         <is>
-          <t>Clara Lerbro, Beke Regelin</t>
+          <t>Beke Regelin, Clara Lerbro</t>
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>127290239</v>
+        <v>127290260</v>
       </c>
       <c r="B23" t="n">
-        <v>91306</v>
+        <v>98467</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>5447</v>
+        <v>220787</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -2872,10 +2872,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>603877</v>
+        <v>603977</v>
       </c>
       <c r="R23" t="n">
-        <v>6692706</v>
+        <v>6692392</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -2927,7 +2927,7 @@
       </c>
       <c r="AX23" t="inlineStr">
         <is>
-          <t>Clara Lerbro, Beke Regelin</t>
+          <t>Beke Regelin, Clara Lerbro</t>
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
@@ -2937,7 +2937,7 @@
         <v>127290244</v>
       </c>
       <c r="B24" t="n">
-        <v>98459</v>
+        <v>98467</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3041,7 +3041,7 @@
       </c>
       <c r="AX24" t="inlineStr">
         <is>
-          <t>Clara Lerbro, Beke Regelin</t>
+          <t>Beke Regelin, Clara Lerbro</t>
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
@@ -3051,7 +3051,7 @@
         <v>127290238</v>
       </c>
       <c r="B25" t="n">
-        <v>98459</v>
+        <v>98467</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3155,7 +3155,7 @@
       </c>
       <c r="AX25" t="inlineStr">
         <is>
-          <t>Clara Lerbro, Beke Regelin</t>
+          <t>Beke Regelin, Clara Lerbro</t>
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>
@@ -3165,7 +3165,7 @@
         <v>127290246</v>
       </c>
       <c r="B26" t="n">
-        <v>92631</v>
+        <v>92639</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3252,7 +3252,7 @@
       </c>
       <c r="AX26" t="inlineStr">
         <is>
-          <t>Clara Lerbro, Beke Regelin</t>
+          <t>Beke Regelin, Clara Lerbro</t>
         </is>
       </c>
       <c r="AY26" t="inlineStr"/>
@@ -3262,7 +3262,7 @@
         <v>127290225</v>
       </c>
       <c r="B27" t="n">
-        <v>98459</v>
+        <v>98467</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3373,10 +3373,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>127290232</v>
+        <v>127290242</v>
       </c>
       <c r="B28" t="n">
-        <v>98459</v>
+        <v>98467</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3403,12 +3403,12 @@
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>9</t>
         </is>
       </c>
       <c r="J28" t="inlineStr">
         <is>
-          <t>dm²</t>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="K28" t="inlineStr">
@@ -3416,16 +3416,18 @@
           <t>överblommad</t>
         </is>
       </c>
+      <c r="L28" t="inlineStr"/>
+      <c r="N28" t="inlineStr"/>
       <c r="P28" t="inlineStr">
         <is>
           <t>Österbyggebo, Gstr</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>603845</v>
+        <v>603879</v>
       </c>
       <c r="R28" t="n">
-        <v>6692678</v>
+        <v>6692700</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3466,6 +3468,7 @@
       <c r="AE28" t="b">
         <v>0</v>
       </c>
+      <c r="AF28" t="inlineStr"/>
       <c r="AG28" t="b">
         <v>0</v>
       </c>
@@ -3477,17 +3480,17 @@
       </c>
       <c r="AX28" t="inlineStr">
         <is>
-          <t>Clara Lerbro, Beke Regelin</t>
+          <t>Beke Regelin, Clara Lerbro</t>
         </is>
       </c>
       <c r="AY28" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>127290242</v>
+        <v>127290232</v>
       </c>
       <c r="B29" t="n">
-        <v>98459</v>
+        <v>98467</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3514,12 +3517,12 @@
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>4</t>
         </is>
       </c>
       <c r="J29" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
+          <t>dm²</t>
         </is>
       </c>
       <c r="K29" t="inlineStr">
@@ -3527,18 +3530,16 @@
           <t>överblommad</t>
         </is>
       </c>
-      <c r="L29" t="inlineStr"/>
-      <c r="N29" t="inlineStr"/>
       <c r="P29" t="inlineStr">
         <is>
           <t>Österbyggebo, Gstr</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>603879</v>
+        <v>603845</v>
       </c>
       <c r="R29" t="n">
-        <v>6692700</v>
+        <v>6692678</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3579,7 +3580,6 @@
       <c r="AE29" t="b">
         <v>0</v>
       </c>
-      <c r="AF29" t="inlineStr"/>
       <c r="AG29" t="b">
         <v>0</v>
       </c>
@@ -3591,7 +3591,7 @@
       </c>
       <c r="AX29" t="inlineStr">
         <is>
-          <t>Clara Lerbro, Beke Regelin</t>
+          <t>Beke Regelin, Clara Lerbro</t>
         </is>
       </c>
       <c r="AY29" t="inlineStr"/>
@@ -3601,7 +3601,7 @@
         <v>127290257</v>
       </c>
       <c r="B30" t="n">
-        <v>91306</v>
+        <v>91314</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3688,7 +3688,7 @@
       </c>
       <c r="AX30" t="inlineStr">
         <is>
-          <t>Clara Lerbro, Beke Regelin</t>
+          <t>Beke Regelin, Clara Lerbro</t>
         </is>
       </c>
       <c r="AY30" t="inlineStr"/>
@@ -3698,7 +3698,7 @@
         <v>127290234</v>
       </c>
       <c r="B31" t="n">
-        <v>91306</v>
+        <v>91314</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3785,7 +3785,7 @@
       </c>
       <c r="AX31" t="inlineStr">
         <is>
-          <t>Clara Lerbro, Beke Regelin</t>
+          <t>Beke Regelin, Clara Lerbro</t>
         </is>
       </c>
       <c r="AY31" t="inlineStr"/>
@@ -3795,7 +3795,7 @@
         <v>127290241</v>
       </c>
       <c r="B32" t="n">
-        <v>98459</v>
+        <v>98467</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3896,7 +3896,7 @@
       </c>
       <c r="AX32" t="inlineStr">
         <is>
-          <t>Clara Lerbro, Beke Regelin</t>
+          <t>Beke Regelin, Clara Lerbro</t>
         </is>
       </c>
       <c r="AY32" t="inlineStr"/>
@@ -3906,7 +3906,7 @@
         <v>127290230</v>
       </c>
       <c r="B33" t="n">
-        <v>91306</v>
+        <v>91314</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4003,7 +4003,7 @@
         <v>127290250</v>
       </c>
       <c r="B34" t="n">
-        <v>105497</v>
+        <v>105505</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4103,7 +4103,7 @@
       </c>
       <c r="AX34" t="inlineStr">
         <is>
-          <t>Clara Lerbro, Beke Regelin</t>
+          <t>Beke Regelin, Clara Lerbro</t>
         </is>
       </c>
       <c r="AY34" t="inlineStr"/>
@@ -4113,7 +4113,7 @@
         <v>127290235</v>
       </c>
       <c r="B35" t="n">
-        <v>105497</v>
+        <v>105505</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4213,7 +4213,7 @@
       </c>
       <c r="AX35" t="inlineStr">
         <is>
-          <t>Clara Lerbro, Beke Regelin</t>
+          <t>Beke Regelin, Clara Lerbro</t>
         </is>
       </c>
       <c r="AY35" t="inlineStr"/>

--- a/artfynd/A 31590-2025 artfynd.xlsx
+++ b/artfynd/A 31590-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>127264982</v>
       </c>
       <c r="B2" t="n">
-        <v>98467</v>
+        <v>98468</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -793,7 +793,7 @@
         <v>127283088</v>
       </c>
       <c r="B3" t="n">
-        <v>105505</v>
+        <v>105506</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -894,7 +894,7 @@
         <v>127264978</v>
       </c>
       <c r="B4" t="n">
-        <v>97344</v>
+        <v>97345</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -992,7 +992,7 @@
         <v>127283086</v>
       </c>
       <c r="B5" t="n">
-        <v>98467</v>
+        <v>98468</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1093,7 +1093,7 @@
         <v>127283078</v>
       </c>
       <c r="B6" t="n">
-        <v>91314</v>
+        <v>91315</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1194,7 +1194,7 @@
         <v>127264973</v>
       </c>
       <c r="B7" t="n">
-        <v>97344</v>
+        <v>97345</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1291,7 +1291,7 @@
         <v>127283087</v>
       </c>
       <c r="B8" t="n">
-        <v>105505</v>
+        <v>105506</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1392,7 +1392,7 @@
         <v>127283085</v>
       </c>
       <c r="B9" t="n">
-        <v>98467</v>
+        <v>98468</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1493,7 +1493,7 @@
         <v>127283083</v>
       </c>
       <c r="B10" t="n">
-        <v>92631</v>
+        <v>92632</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1696,7 +1696,7 @@
         <v>127283084</v>
       </c>
       <c r="B12" t="n">
-        <v>98467</v>
+        <v>98468</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1802,7 +1802,7 @@
         <v>127290259</v>
       </c>
       <c r="B13" t="n">
-        <v>98467</v>
+        <v>98468</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1906,52 +1906,56 @@
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>Beke Regelin, Clara Lerbro</t>
+          <t>Clara Lerbro, Beke Regelin</t>
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>127290233</v>
+        <v>127283080</v>
       </c>
       <c r="B14" t="n">
-        <v>91349</v>
+        <v>56864</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>1202</v>
+        <v>100138</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
+      <c r="K14" t="inlineStr"/>
+      <c r="L14" t="inlineStr"/>
+      <c r="M14" t="inlineStr"/>
+      <c r="N14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
-          <t>Österbyggebo, Gstr</t>
+          <t>Gråtängarna, Gstr</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>603850</v>
+        <v>603972</v>
       </c>
       <c r="R14" t="n">
-        <v>6692680</v>
+        <v>6692667</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -1986,6 +1990,11 @@
           <t>2025-08-06</t>
         </is>
       </c>
+      <c r="AC14" t="inlineStr">
+        <is>
+          <t>Fjäder efter en tjädertupp, 32 cm lång</t>
+        </is>
+      </c>
       <c r="AD14" t="b">
         <v>0</v>
       </c>
@@ -1998,7 +2007,7 @@
       <c r="AT14" t="inlineStr"/>
       <c r="AW14" t="inlineStr">
         <is>
-          <t>Clara Lerbro</t>
+          <t>Beke Regelin</t>
         </is>
       </c>
       <c r="AX14" t="inlineStr">
@@ -2010,10 +2019,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>127290255</v>
+        <v>127290233</v>
       </c>
       <c r="B15" t="n">
-        <v>91363</v>
+        <v>91350</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2021,21 +2030,21 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>1204</v>
+        <v>1202</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Gränsticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Phellopilus nigrolimitatus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2045,10 +2054,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>603980</v>
+        <v>603850</v>
       </c>
       <c r="R15" t="n">
-        <v>6692483</v>
+        <v>6692680</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2100,56 +2109,52 @@
       </c>
       <c r="AX15" t="inlineStr">
         <is>
-          <t>Beke Regelin, Clara Lerbro</t>
+          <t>Clara Lerbro, Beke Regelin</t>
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>127283080</v>
+        <v>127290255</v>
       </c>
       <c r="B16" t="n">
-        <v>56864</v>
+        <v>91364</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>100138</v>
+        <v>1204</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Gränsticka</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Phellopilus nigrolimitatus</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
-      <c r="K16" t="inlineStr"/>
-      <c r="L16" t="inlineStr"/>
-      <c r="M16" t="inlineStr"/>
-      <c r="N16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
-          <t>Gråtängarna, Gstr</t>
+          <t>Österbyggebo, Gstr</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>603972</v>
+        <v>603980</v>
       </c>
       <c r="R16" t="n">
-        <v>6692667</v>
+        <v>6692483</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2184,11 +2189,6 @@
           <t>2025-08-06</t>
         </is>
       </c>
-      <c r="AC16" t="inlineStr">
-        <is>
-          <t>Fjäder efter en tjädertupp, 32 cm lång</t>
-        </is>
-      </c>
       <c r="AD16" t="b">
         <v>0</v>
       </c>
@@ -2201,12 +2201,12 @@
       <c r="AT16" t="inlineStr"/>
       <c r="AW16" t="inlineStr">
         <is>
-          <t>Beke Regelin</t>
+          <t>Clara Lerbro</t>
         </is>
       </c>
       <c r="AX16" t="inlineStr">
         <is>
-          <t>Beke Regelin, Clara Lerbro</t>
+          <t>Clara Lerbro, Beke Regelin</t>
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
@@ -2216,7 +2216,7 @@
         <v>127290258</v>
       </c>
       <c r="B17" t="n">
-        <v>98467</v>
+        <v>98468</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2320,7 +2320,7 @@
       </c>
       <c r="AX17" t="inlineStr">
         <is>
-          <t>Beke Regelin, Clara Lerbro</t>
+          <t>Clara Lerbro, Beke Regelin</t>
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
@@ -2330,7 +2330,7 @@
         <v>127290240</v>
       </c>
       <c r="B18" t="n">
-        <v>98467</v>
+        <v>98468</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2430,7 +2430,7 @@
       </c>
       <c r="AX18" t="inlineStr">
         <is>
-          <t>Beke Regelin, Clara Lerbro</t>
+          <t>Clara Lerbro, Beke Regelin</t>
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
@@ -2440,7 +2440,7 @@
         <v>127290254</v>
       </c>
       <c r="B19" t="n">
-        <v>91314</v>
+        <v>91315</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2527,7 +2527,7 @@
       </c>
       <c r="AX19" t="inlineStr">
         <is>
-          <t>Beke Regelin, Clara Lerbro</t>
+          <t>Clara Lerbro, Beke Regelin</t>
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
@@ -2537,7 +2537,7 @@
         <v>127290227</v>
       </c>
       <c r="B20" t="n">
-        <v>91349</v>
+        <v>91350</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2631,56 +2631,45 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>127290226</v>
+        <v>127290260</v>
       </c>
       <c r="B21" t="n">
-        <v>92631</v>
+        <v>98468</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>4361</v>
+        <v>220787</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Orange taggsvamp</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Hydnellum aurantiacum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Batsch:Fr.) P.Karst.</t>
-        </is>
-      </c>
-      <c r="I21" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="J21" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
-      <c r="K21" t="inlineStr"/>
-      <c r="N21" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
           <t>Österbyggebo, Gstr</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>603857</v>
+        <v>603977</v>
       </c>
       <c r="R21" t="n">
-        <v>6692565</v>
+        <v>6692392</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2721,7 +2710,6 @@
       <c r="AE21" t="b">
         <v>0</v>
       </c>
-      <c r="AF21" t="inlineStr"/>
       <c r="AG21" t="b">
         <v>0</v>
       </c>
@@ -2740,45 +2728,56 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>127290239</v>
+        <v>127290226</v>
       </c>
       <c r="B22" t="n">
-        <v>91314</v>
+        <v>92632</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>5447</v>
+        <v>4361</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Orange taggsvamp</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Hydnellum aurantiacum</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
-        </is>
-      </c>
-      <c r="I22" t="inlineStr"/>
+          <t>(Batsch:Fr.) P.Karst.</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J22" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
+      <c r="K22" t="inlineStr"/>
+      <c r="N22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
           <t>Österbyggebo, Gstr</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>603877</v>
+        <v>603857</v>
       </c>
       <c r="R22" t="n">
-        <v>6692706</v>
+        <v>6692565</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2819,6 +2818,7 @@
       <c r="AE22" t="b">
         <v>0</v>
       </c>
+      <c r="AF22" t="inlineStr"/>
       <c r="AG22" t="b">
         <v>0</v>
       </c>
@@ -2830,39 +2830,39 @@
       </c>
       <c r="AX22" t="inlineStr">
         <is>
-          <t>Beke Regelin, Clara Lerbro</t>
+          <t>Clara Lerbro, Beke Regelin</t>
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>127290260</v>
+        <v>127290239</v>
       </c>
       <c r="B23" t="n">
-        <v>98467</v>
+        <v>91315</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>220787</v>
+        <v>5447</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -2872,10 +2872,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>603977</v>
+        <v>603877</v>
       </c>
       <c r="R23" t="n">
-        <v>6692392</v>
+        <v>6692706</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -2927,7 +2927,7 @@
       </c>
       <c r="AX23" t="inlineStr">
         <is>
-          <t>Beke Regelin, Clara Lerbro</t>
+          <t>Clara Lerbro, Beke Regelin</t>
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
@@ -2937,7 +2937,7 @@
         <v>127290244</v>
       </c>
       <c r="B24" t="n">
-        <v>98467</v>
+        <v>98468</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3041,7 +3041,7 @@
       </c>
       <c r="AX24" t="inlineStr">
         <is>
-          <t>Beke Regelin, Clara Lerbro</t>
+          <t>Clara Lerbro, Beke Regelin</t>
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
@@ -3051,7 +3051,7 @@
         <v>127290238</v>
       </c>
       <c r="B25" t="n">
-        <v>98467</v>
+        <v>98468</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3155,7 +3155,7 @@
       </c>
       <c r="AX25" t="inlineStr">
         <is>
-          <t>Beke Regelin, Clara Lerbro</t>
+          <t>Clara Lerbro, Beke Regelin</t>
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>
@@ -3165,7 +3165,7 @@
         <v>127290246</v>
       </c>
       <c r="B26" t="n">
-        <v>92639</v>
+        <v>92640</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3252,7 +3252,7 @@
       </c>
       <c r="AX26" t="inlineStr">
         <is>
-          <t>Beke Regelin, Clara Lerbro</t>
+          <t>Clara Lerbro, Beke Regelin</t>
         </is>
       </c>
       <c r="AY26" t="inlineStr"/>
@@ -3262,7 +3262,7 @@
         <v>127290225</v>
       </c>
       <c r="B27" t="n">
-        <v>98467</v>
+        <v>98468</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3376,7 +3376,7 @@
         <v>127290242</v>
       </c>
       <c r="B28" t="n">
-        <v>98467</v>
+        <v>98468</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3480,7 +3480,7 @@
       </c>
       <c r="AX28" t="inlineStr">
         <is>
-          <t>Beke Regelin, Clara Lerbro</t>
+          <t>Clara Lerbro, Beke Regelin</t>
         </is>
       </c>
       <c r="AY28" t="inlineStr"/>
@@ -3490,7 +3490,7 @@
         <v>127290232</v>
       </c>
       <c r="B29" t="n">
-        <v>98467</v>
+        <v>98468</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3591,7 +3591,7 @@
       </c>
       <c r="AX29" t="inlineStr">
         <is>
-          <t>Beke Regelin, Clara Lerbro</t>
+          <t>Clara Lerbro, Beke Regelin</t>
         </is>
       </c>
       <c r="AY29" t="inlineStr"/>
@@ -3601,7 +3601,7 @@
         <v>127290257</v>
       </c>
       <c r="B30" t="n">
-        <v>91314</v>
+        <v>91315</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3688,7 +3688,7 @@
       </c>
       <c r="AX30" t="inlineStr">
         <is>
-          <t>Beke Regelin, Clara Lerbro</t>
+          <t>Clara Lerbro, Beke Regelin</t>
         </is>
       </c>
       <c r="AY30" t="inlineStr"/>
@@ -3698,7 +3698,7 @@
         <v>127290234</v>
       </c>
       <c r="B31" t="n">
-        <v>91314</v>
+        <v>91315</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3785,7 +3785,7 @@
       </c>
       <c r="AX31" t="inlineStr">
         <is>
-          <t>Beke Regelin, Clara Lerbro</t>
+          <t>Clara Lerbro, Beke Regelin</t>
         </is>
       </c>
       <c r="AY31" t="inlineStr"/>
@@ -3795,7 +3795,7 @@
         <v>127290241</v>
       </c>
       <c r="B32" t="n">
-        <v>98467</v>
+        <v>98468</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3896,7 +3896,7 @@
       </c>
       <c r="AX32" t="inlineStr">
         <is>
-          <t>Beke Regelin, Clara Lerbro</t>
+          <t>Clara Lerbro, Beke Regelin</t>
         </is>
       </c>
       <c r="AY32" t="inlineStr"/>
@@ -3906,7 +3906,7 @@
         <v>127290230</v>
       </c>
       <c r="B33" t="n">
-        <v>91314</v>
+        <v>91315</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4003,7 +4003,7 @@
         <v>127290250</v>
       </c>
       <c r="B34" t="n">
-        <v>105505</v>
+        <v>105506</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4103,7 +4103,7 @@
       </c>
       <c r="AX34" t="inlineStr">
         <is>
-          <t>Beke Regelin, Clara Lerbro</t>
+          <t>Clara Lerbro, Beke Regelin</t>
         </is>
       </c>
       <c r="AY34" t="inlineStr"/>
@@ -4113,7 +4113,7 @@
         <v>127290235</v>
       </c>
       <c r="B35" t="n">
-        <v>105505</v>
+        <v>105506</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4213,7 +4213,7 @@
       </c>
       <c r="AX35" t="inlineStr">
         <is>
-          <t>Beke Regelin, Clara Lerbro</t>
+          <t>Clara Lerbro, Beke Regelin</t>
         </is>
       </c>
       <c r="AY35" t="inlineStr"/>

--- a/artfynd/A 31590-2025 artfynd.xlsx
+++ b/artfynd/A 31590-2025 artfynd.xlsx
@@ -1913,49 +1913,61 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>127283080</v>
+        <v>127290258</v>
       </c>
       <c r="B14" t="n">
-        <v>56864</v>
+        <v>98468</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>100138</v>
+        <v>220787</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
-        </is>
-      </c>
-      <c r="I14" t="inlineStr"/>
-      <c r="K14" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="J14" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K14" t="inlineStr">
+        <is>
+          <t>överblommad</t>
+        </is>
+      </c>
       <c r="L14" t="inlineStr"/>
-      <c r="M14" t="inlineStr"/>
       <c r="N14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
-          <t>Gråtängarna, Gstr</t>
+          <t>Österbyggebo, Gstr</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>603972</v>
+        <v>603981</v>
       </c>
       <c r="R14" t="n">
-        <v>6692667</v>
+        <v>6692427</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -1990,29 +2002,25 @@
           <t>2025-08-06</t>
         </is>
       </c>
-      <c r="AC14" t="inlineStr">
-        <is>
-          <t>Fjäder efter en tjädertupp, 32 cm lång</t>
-        </is>
-      </c>
       <c r="AD14" t="b">
         <v>0</v>
       </c>
       <c r="AE14" t="b">
         <v>0</v>
       </c>
+      <c r="AF14" t="inlineStr"/>
       <c r="AG14" t="b">
         <v>0</v>
       </c>
       <c r="AT14" t="inlineStr"/>
       <c r="AW14" t="inlineStr">
         <is>
-          <t>Beke Regelin</t>
+          <t>Clara Lerbro</t>
         </is>
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>Beke Regelin, Clara Lerbro</t>
+          <t>Clara Lerbro, Beke Regelin</t>
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
@@ -2213,61 +2221,49 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>127290258</v>
+        <v>127283080</v>
       </c>
       <c r="B17" t="n">
-        <v>98468</v>
+        <v>56864</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>220787</v>
+        <v>100138</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I17" t="inlineStr">
-        <is>
-          <t>15</t>
-        </is>
-      </c>
-      <c r="J17" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K17" t="inlineStr">
-        <is>
-          <t>överblommad</t>
-        </is>
-      </c>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr"/>
+      <c r="K17" t="inlineStr"/>
       <c r="L17" t="inlineStr"/>
+      <c r="M17" t="inlineStr"/>
       <c r="N17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
-          <t>Österbyggebo, Gstr</t>
+          <t>Gråtängarna, Gstr</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>603981</v>
+        <v>603972</v>
       </c>
       <c r="R17" t="n">
-        <v>6692427</v>
+        <v>6692667</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2302,25 +2298,29 @@
           <t>2025-08-06</t>
         </is>
       </c>
+      <c r="AC17" t="inlineStr">
+        <is>
+          <t>Fjäder efter en tjädertupp, 32 cm lång</t>
+        </is>
+      </c>
       <c r="AD17" t="b">
         <v>0</v>
       </c>
       <c r="AE17" t="b">
         <v>0</v>
       </c>
-      <c r="AF17" t="inlineStr"/>
       <c r="AG17" t="b">
         <v>0</v>
       </c>
       <c r="AT17" t="inlineStr"/>
       <c r="AW17" t="inlineStr">
         <is>
-          <t>Clara Lerbro</t>
+          <t>Beke Regelin</t>
         </is>
       </c>
       <c r="AX17" t="inlineStr">
         <is>
-          <t>Clara Lerbro, Beke Regelin</t>
+          <t>Beke Regelin, Clara Lerbro</t>
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
@@ -2631,45 +2631,56 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>127290260</v>
+        <v>127290226</v>
       </c>
       <c r="B21" t="n">
-        <v>98468</v>
+        <v>92632</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>220787</v>
+        <v>4361</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Orange taggsvamp</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hydnellum aurantiacum</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I21" t="inlineStr"/>
+          <t>(Batsch:Fr.) P.Karst.</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J21" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
+      <c r="K21" t="inlineStr"/>
+      <c r="N21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
           <t>Österbyggebo, Gstr</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>603977</v>
+        <v>603857</v>
       </c>
       <c r="R21" t="n">
-        <v>6692392</v>
+        <v>6692565</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2710,6 +2721,7 @@
       <c r="AE21" t="b">
         <v>0</v>
       </c>
+      <c r="AF21" t="inlineStr"/>
       <c r="AG21" t="b">
         <v>0</v>
       </c>
@@ -2728,56 +2740,45 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>127290226</v>
+        <v>127290239</v>
       </c>
       <c r="B22" t="n">
-        <v>92632</v>
+        <v>91315</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>4361</v>
+        <v>5447</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Orange taggsvamp</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Hydnellum aurantiacum</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Batsch:Fr.) P.Karst.</t>
-        </is>
-      </c>
-      <c r="I22" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="J22" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
-      <c r="K22" t="inlineStr"/>
-      <c r="N22" t="inlineStr"/>
+          <t>(Schwein.) Murrill</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
           <t>Österbyggebo, Gstr</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>603857</v>
+        <v>603877</v>
       </c>
       <c r="R22" t="n">
-        <v>6692565</v>
+        <v>6692706</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2818,7 +2819,6 @@
       <c r="AE22" t="b">
         <v>0</v>
       </c>
-      <c r="AF22" t="inlineStr"/>
       <c r="AG22" t="b">
         <v>0</v>
       </c>
@@ -2837,32 +2837,32 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>127290239</v>
+        <v>127290260</v>
       </c>
       <c r="B23" t="n">
-        <v>91315</v>
+        <v>98468</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>5447</v>
+        <v>220787</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -2872,10 +2872,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>603877</v>
+        <v>603977</v>
       </c>
       <c r="R23" t="n">
-        <v>6692706</v>
+        <v>6692392</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>

--- a/artfynd/A 31590-2025 artfynd.xlsx
+++ b/artfynd/A 31590-2025 artfynd.xlsx
@@ -1802,7 +1802,7 @@
         <v>127290259</v>
       </c>
       <c r="B13" t="n">
-        <v>98468</v>
+        <v>98469</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1913,61 +1913,45 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>127290258</v>
+        <v>127290233</v>
       </c>
       <c r="B14" t="n">
-        <v>98468</v>
+        <v>91351</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>220787</v>
+        <v>1202</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I14" t="inlineStr">
-        <is>
-          <t>15</t>
-        </is>
-      </c>
-      <c r="J14" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K14" t="inlineStr">
-        <is>
-          <t>överblommad</t>
-        </is>
-      </c>
-      <c r="L14" t="inlineStr"/>
-      <c r="N14" t="inlineStr"/>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
           <t>Österbyggebo, Gstr</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>603981</v>
+        <v>603850</v>
       </c>
       <c r="R14" t="n">
-        <v>6692427</v>
+        <v>6692680</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2008,7 +1992,6 @@
       <c r="AE14" t="b">
         <v>0</v>
       </c>
-      <c r="AF14" t="inlineStr"/>
       <c r="AG14" t="b">
         <v>0</v>
       </c>
@@ -2027,10 +2010,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>127290233</v>
+        <v>127290255</v>
       </c>
       <c r="B15" t="n">
-        <v>91350</v>
+        <v>91365</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2038,21 +2021,21 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>1202</v>
+        <v>1204</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Gränsticka</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Phellopilus nigrolimitatus</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2062,10 +2045,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>603850</v>
+        <v>603980</v>
       </c>
       <c r="R15" t="n">
-        <v>6692680</v>
+        <v>6692483</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2124,45 +2107,49 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>127290255</v>
+        <v>127283080</v>
       </c>
       <c r="B16" t="n">
-        <v>91364</v>
+        <v>56864</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>1204</v>
+        <v>100138</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Gränsticka</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Phellopilus nigrolimitatus</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
+      <c r="K16" t="inlineStr"/>
+      <c r="L16" t="inlineStr"/>
+      <c r="M16" t="inlineStr"/>
+      <c r="N16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
-          <t>Österbyggebo, Gstr</t>
+          <t>Gråtängarna, Gstr</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>603980</v>
+        <v>603972</v>
       </c>
       <c r="R16" t="n">
-        <v>6692483</v>
+        <v>6692667</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2197,6 +2184,11 @@
           <t>2025-08-06</t>
         </is>
       </c>
+      <c r="AC16" t="inlineStr">
+        <is>
+          <t>Fjäder efter en tjädertupp, 32 cm lång</t>
+        </is>
+      </c>
       <c r="AD16" t="b">
         <v>0</v>
       </c>
@@ -2209,61 +2201,73 @@
       <c r="AT16" t="inlineStr"/>
       <c r="AW16" t="inlineStr">
         <is>
-          <t>Clara Lerbro</t>
+          <t>Beke Regelin</t>
         </is>
       </c>
       <c r="AX16" t="inlineStr">
         <is>
-          <t>Clara Lerbro, Beke Regelin</t>
+          <t>Beke Regelin, Clara Lerbro</t>
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>127283080</v>
+        <v>127290258</v>
       </c>
       <c r="B17" t="n">
-        <v>56864</v>
+        <v>98469</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>100138</v>
+        <v>220787</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
-        </is>
-      </c>
-      <c r="I17" t="inlineStr"/>
-      <c r="K17" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="J17" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K17" t="inlineStr">
+        <is>
+          <t>överblommad</t>
+        </is>
+      </c>
       <c r="L17" t="inlineStr"/>
-      <c r="M17" t="inlineStr"/>
       <c r="N17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
-          <t>Gråtängarna, Gstr</t>
+          <t>Österbyggebo, Gstr</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>603972</v>
+        <v>603981</v>
       </c>
       <c r="R17" t="n">
-        <v>6692667</v>
+        <v>6692427</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2298,29 +2302,25 @@
           <t>2025-08-06</t>
         </is>
       </c>
-      <c r="AC17" t="inlineStr">
-        <is>
-          <t>Fjäder efter en tjädertupp, 32 cm lång</t>
-        </is>
-      </c>
       <c r="AD17" t="b">
         <v>0</v>
       </c>
       <c r="AE17" t="b">
         <v>0</v>
       </c>
+      <c r="AF17" t="inlineStr"/>
       <c r="AG17" t="b">
         <v>0</v>
       </c>
       <c r="AT17" t="inlineStr"/>
       <c r="AW17" t="inlineStr">
         <is>
-          <t>Beke Regelin</t>
+          <t>Clara Lerbro</t>
         </is>
       </c>
       <c r="AX17" t="inlineStr">
         <is>
-          <t>Beke Regelin, Clara Lerbro</t>
+          <t>Clara Lerbro, Beke Regelin</t>
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
@@ -2330,7 +2330,7 @@
         <v>127290240</v>
       </c>
       <c r="B18" t="n">
-        <v>98468</v>
+        <v>98469</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2440,7 +2440,7 @@
         <v>127290254</v>
       </c>
       <c r="B19" t="n">
-        <v>91315</v>
+        <v>91316</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2537,7 +2537,7 @@
         <v>127290227</v>
       </c>
       <c r="B20" t="n">
-        <v>91350</v>
+        <v>91351</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2634,7 +2634,7 @@
         <v>127290226</v>
       </c>
       <c r="B21" t="n">
-        <v>92632</v>
+        <v>92633</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2743,7 +2743,7 @@
         <v>127290239</v>
       </c>
       <c r="B22" t="n">
-        <v>91315</v>
+        <v>91316</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2840,7 +2840,7 @@
         <v>127290260</v>
       </c>
       <c r="B23" t="n">
-        <v>98468</v>
+        <v>98469</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2937,7 +2937,7 @@
         <v>127290244</v>
       </c>
       <c r="B24" t="n">
-        <v>98468</v>
+        <v>98469</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3051,7 +3051,7 @@
         <v>127290238</v>
       </c>
       <c r="B25" t="n">
-        <v>98468</v>
+        <v>98469</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3165,7 +3165,7 @@
         <v>127290246</v>
       </c>
       <c r="B26" t="n">
-        <v>92640</v>
+        <v>92641</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3262,7 +3262,7 @@
         <v>127290225</v>
       </c>
       <c r="B27" t="n">
-        <v>98468</v>
+        <v>98469</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3376,7 +3376,7 @@
         <v>127290242</v>
       </c>
       <c r="B28" t="n">
-        <v>98468</v>
+        <v>98469</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3490,7 +3490,7 @@
         <v>127290232</v>
       </c>
       <c r="B29" t="n">
-        <v>98468</v>
+        <v>98469</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3601,7 +3601,7 @@
         <v>127290257</v>
       </c>
       <c r="B30" t="n">
-        <v>91315</v>
+        <v>91316</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3695,45 +3695,59 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>127290234</v>
+        <v>127290241</v>
       </c>
       <c r="B31" t="n">
-        <v>91315</v>
+        <v>98469</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>5447</v>
+        <v>220787</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
-        </is>
-      </c>
-      <c r="I31" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="J31" t="inlineStr">
+        <is>
+          <t>dm²</t>
+        </is>
+      </c>
+      <c r="K31" t="inlineStr">
+        <is>
+          <t>överblommad</t>
+        </is>
+      </c>
       <c r="P31" t="inlineStr">
         <is>
           <t>Österbyggebo, Gstr</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>603860</v>
+        <v>603880</v>
       </c>
       <c r="R31" t="n">
-        <v>6692678</v>
+        <v>6692710</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3792,59 +3806,45 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>127290241</v>
+        <v>127290234</v>
       </c>
       <c r="B32" t="n">
-        <v>98468</v>
+        <v>91316</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>220787</v>
+        <v>5447</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I32" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="J32" t="inlineStr">
-        <is>
-          <t>dm²</t>
-        </is>
-      </c>
-      <c r="K32" t="inlineStr">
-        <is>
-          <t>överblommad</t>
-        </is>
-      </c>
+          <t>(Schwein.) Murrill</t>
+        </is>
+      </c>
+      <c r="I32" t="inlineStr"/>
       <c r="P32" t="inlineStr">
         <is>
           <t>Österbyggebo, Gstr</t>
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>603880</v>
+        <v>603860</v>
       </c>
       <c r="R32" t="n">
-        <v>6692710</v>
+        <v>6692678</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -3906,7 +3906,7 @@
         <v>127290230</v>
       </c>
       <c r="B33" t="n">
-        <v>91315</v>
+        <v>91316</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4003,7 +4003,7 @@
         <v>127290250</v>
       </c>
       <c r="B34" t="n">
-        <v>105506</v>
+        <v>105507</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4113,7 +4113,7 @@
         <v>127290235</v>
       </c>
       <c r="B35" t="n">
-        <v>105506</v>
+        <v>105507</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>

--- a/artfynd/A 31590-2025 artfynd.xlsx
+++ b/artfynd/A 31590-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY35"/>
+  <dimension ref="A1:AY40"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -4218,6 +4218,499 @@
       </c>
       <c r="AY35" t="inlineStr"/>
     </row>
+    <row r="36">
+      <c r="A36" t="n">
+        <v>128320327</v>
+      </c>
+      <c r="B36" t="n">
+        <v>97347</v>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E36" t="n">
+        <v>221945</v>
+      </c>
+      <c r="F36" t="inlineStr">
+        <is>
+          <t>Revlummer</t>
+        </is>
+      </c>
+      <c r="G36" t="inlineStr">
+        <is>
+          <t>Lycopodium annotinum</t>
+        </is>
+      </c>
+      <c r="H36" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I36" t="inlineStr"/>
+      <c r="P36" t="inlineStr">
+        <is>
+          <t>Gråtängarna, Gstr</t>
+        </is>
+      </c>
+      <c r="Q36" t="n">
+        <v>603804</v>
+      </c>
+      <c r="R36" t="n">
+        <v>6692572</v>
+      </c>
+      <c r="S36" t="n">
+        <v>10</v>
+      </c>
+      <c r="T36" t="inlineStr">
+        <is>
+          <t>Gävleborg</t>
+        </is>
+      </c>
+      <c r="U36" t="inlineStr">
+        <is>
+          <t>Gävle</t>
+        </is>
+      </c>
+      <c r="V36" t="inlineStr">
+        <is>
+          <t>Gästrikland</t>
+        </is>
+      </c>
+      <c r="W36" t="inlineStr">
+        <is>
+          <t>Hedesunda</t>
+        </is>
+      </c>
+      <c r="Y36" t="inlineStr">
+        <is>
+          <t>2025-09-06</t>
+        </is>
+      </c>
+      <c r="AA36" t="inlineStr">
+        <is>
+          <t>2025-09-06</t>
+        </is>
+      </c>
+      <c r="AD36" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE36" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG36" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT36" t="inlineStr"/>
+      <c r="AW36" t="inlineStr">
+        <is>
+          <t>Beke Regelin</t>
+        </is>
+      </c>
+      <c r="AX36" t="inlineStr">
+        <is>
+          <t>Beke Regelin</t>
+        </is>
+      </c>
+      <c r="AY36" t="inlineStr"/>
+    </row>
+    <row r="37">
+      <c r="A37" t="n">
+        <v>128320328</v>
+      </c>
+      <c r="B37" t="n">
+        <v>57832</v>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E37" t="n">
+        <v>103021</v>
+      </c>
+      <c r="F37" t="inlineStr">
+        <is>
+          <t>Talltita</t>
+        </is>
+      </c>
+      <c r="G37" t="inlineStr">
+        <is>
+          <t>Poecile montanus</t>
+        </is>
+      </c>
+      <c r="H37" t="inlineStr">
+        <is>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I37" t="inlineStr"/>
+      <c r="K37" t="inlineStr"/>
+      <c r="L37" t="inlineStr"/>
+      <c r="M37" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
+      <c r="N37" t="inlineStr"/>
+      <c r="P37" t="inlineStr">
+        <is>
+          <t>Gråtängarna, Gstr</t>
+        </is>
+      </c>
+      <c r="Q37" t="n">
+        <v>603812</v>
+      </c>
+      <c r="R37" t="n">
+        <v>6692518</v>
+      </c>
+      <c r="S37" t="n">
+        <v>10</v>
+      </c>
+      <c r="T37" t="inlineStr">
+        <is>
+          <t>Gävleborg</t>
+        </is>
+      </c>
+      <c r="U37" t="inlineStr">
+        <is>
+          <t>Gävle</t>
+        </is>
+      </c>
+      <c r="V37" t="inlineStr">
+        <is>
+          <t>Gästrikland</t>
+        </is>
+      </c>
+      <c r="W37" t="inlineStr">
+        <is>
+          <t>Hedesunda</t>
+        </is>
+      </c>
+      <c r="Y37" t="inlineStr">
+        <is>
+          <t>2025-09-06</t>
+        </is>
+      </c>
+      <c r="AA37" t="inlineStr">
+        <is>
+          <t>2025-09-06</t>
+        </is>
+      </c>
+      <c r="AD37" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE37" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG37" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT37" t="inlineStr"/>
+      <c r="AW37" t="inlineStr">
+        <is>
+          <t>Beke Regelin</t>
+        </is>
+      </c>
+      <c r="AX37" t="inlineStr">
+        <is>
+          <t>Beke Regelin</t>
+        </is>
+      </c>
+      <c r="AY37" t="inlineStr"/>
+    </row>
+    <row r="38">
+      <c r="A38" t="n">
+        <v>128320324</v>
+      </c>
+      <c r="B38" t="n">
+        <v>58042</v>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E38" t="n">
+        <v>103015</v>
+      </c>
+      <c r="F38" t="inlineStr">
+        <is>
+          <t>Kungsfågel</t>
+        </is>
+      </c>
+      <c r="G38" t="inlineStr">
+        <is>
+          <t>Regulus regulus</t>
+        </is>
+      </c>
+      <c r="H38" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I38" t="inlineStr"/>
+      <c r="P38" t="inlineStr">
+        <is>
+          <t>Gråtängarna, Gstr</t>
+        </is>
+      </c>
+      <c r="Q38" t="n">
+        <v>603808</v>
+      </c>
+      <c r="R38" t="n">
+        <v>6692504</v>
+      </c>
+      <c r="S38" t="n">
+        <v>10</v>
+      </c>
+      <c r="T38" t="inlineStr">
+        <is>
+          <t>Gävleborg</t>
+        </is>
+      </c>
+      <c r="U38" t="inlineStr">
+        <is>
+          <t>Gävle</t>
+        </is>
+      </c>
+      <c r="V38" t="inlineStr">
+        <is>
+          <t>Gästrikland</t>
+        </is>
+      </c>
+      <c r="W38" t="inlineStr">
+        <is>
+          <t>Hedesunda</t>
+        </is>
+      </c>
+      <c r="Y38" t="inlineStr">
+        <is>
+          <t>2025-09-06</t>
+        </is>
+      </c>
+      <c r="AA38" t="inlineStr">
+        <is>
+          <t>2025-09-06</t>
+        </is>
+      </c>
+      <c r="AD38" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE38" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG38" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT38" t="inlineStr"/>
+      <c r="AW38" t="inlineStr">
+        <is>
+          <t>Beke Regelin</t>
+        </is>
+      </c>
+      <c r="AX38" t="inlineStr">
+        <is>
+          <t>Beke Regelin</t>
+        </is>
+      </c>
+      <c r="AY38" t="inlineStr"/>
+    </row>
+    <row r="39">
+      <c r="A39" t="n">
+        <v>128320325</v>
+      </c>
+      <c r="B39" t="n">
+        <v>97347</v>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E39" t="n">
+        <v>221945</v>
+      </c>
+      <c r="F39" t="inlineStr">
+        <is>
+          <t>Revlummer</t>
+        </is>
+      </c>
+      <c r="G39" t="inlineStr">
+        <is>
+          <t>Lycopodium annotinum</t>
+        </is>
+      </c>
+      <c r="H39" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I39" t="inlineStr"/>
+      <c r="P39" t="inlineStr">
+        <is>
+          <t>Gråtängarna, Gstr</t>
+        </is>
+      </c>
+      <c r="Q39" t="n">
+        <v>603976</v>
+      </c>
+      <c r="R39" t="n">
+        <v>6692668</v>
+      </c>
+      <c r="S39" t="n">
+        <v>10</v>
+      </c>
+      <c r="T39" t="inlineStr">
+        <is>
+          <t>Gävleborg</t>
+        </is>
+      </c>
+      <c r="U39" t="inlineStr">
+        <is>
+          <t>Gävle</t>
+        </is>
+      </c>
+      <c r="V39" t="inlineStr">
+        <is>
+          <t>Gästrikland</t>
+        </is>
+      </c>
+      <c r="W39" t="inlineStr">
+        <is>
+          <t>Hedesunda</t>
+        </is>
+      </c>
+      <c r="Y39" t="inlineStr">
+        <is>
+          <t>2025-09-06</t>
+        </is>
+      </c>
+      <c r="AA39" t="inlineStr">
+        <is>
+          <t>2025-09-06</t>
+        </is>
+      </c>
+      <c r="AD39" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE39" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG39" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT39" t="inlineStr"/>
+      <c r="AW39" t="inlineStr">
+        <is>
+          <t>Beke Regelin</t>
+        </is>
+      </c>
+      <c r="AX39" t="inlineStr">
+        <is>
+          <t>Beke Regelin</t>
+        </is>
+      </c>
+      <c r="AY39" t="inlineStr"/>
+    </row>
+    <row r="40">
+      <c r="A40" t="n">
+        <v>128320323</v>
+      </c>
+      <c r="B40" t="n">
+        <v>105508</v>
+      </c>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E40" t="n">
+        <v>221144</v>
+      </c>
+      <c r="F40" t="inlineStr">
+        <is>
+          <t>Grönpyrola</t>
+        </is>
+      </c>
+      <c r="G40" t="inlineStr">
+        <is>
+          <t>Pyrola chlorantha</t>
+        </is>
+      </c>
+      <c r="H40" t="inlineStr">
+        <is>
+          <t>Sw.</t>
+        </is>
+      </c>
+      <c r="I40" t="inlineStr"/>
+      <c r="P40" t="inlineStr">
+        <is>
+          <t>Gråtängarna, Gstr</t>
+        </is>
+      </c>
+      <c r="Q40" t="n">
+        <v>603978</v>
+      </c>
+      <c r="R40" t="n">
+        <v>6692395</v>
+      </c>
+      <c r="S40" t="n">
+        <v>10</v>
+      </c>
+      <c r="T40" t="inlineStr">
+        <is>
+          <t>Gävleborg</t>
+        </is>
+      </c>
+      <c r="U40" t="inlineStr">
+        <is>
+          <t>Gävle</t>
+        </is>
+      </c>
+      <c r="V40" t="inlineStr">
+        <is>
+          <t>Gästrikland</t>
+        </is>
+      </c>
+      <c r="W40" t="inlineStr">
+        <is>
+          <t>Hedesunda</t>
+        </is>
+      </c>
+      <c r="Y40" t="inlineStr">
+        <is>
+          <t>2025-09-06</t>
+        </is>
+      </c>
+      <c r="AA40" t="inlineStr">
+        <is>
+          <t>2025-09-06</t>
+        </is>
+      </c>
+      <c r="AD40" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE40" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG40" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT40" t="inlineStr"/>
+      <c r="AW40" t="inlineStr">
+        <is>
+          <t>Beke Regelin</t>
+        </is>
+      </c>
+      <c r="AX40" t="inlineStr">
+        <is>
+          <t>Beke Regelin</t>
+        </is>
+      </c>
+      <c r="AY40" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 31590-2025 artfynd.xlsx
+++ b/artfynd/A 31590-2025 artfynd.xlsx
@@ -4223,7 +4223,7 @@
         <v>128320327</v>
       </c>
       <c r="B36" t="n">
-        <v>97347</v>
+        <v>97355</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4320,7 +4320,7 @@
         <v>128320328</v>
       </c>
       <c r="B37" t="n">
-        <v>57832</v>
+        <v>57833</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4425,7 +4425,7 @@
         <v>128320324</v>
       </c>
       <c r="B38" t="n">
-        <v>58042</v>
+        <v>58043</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4522,7 +4522,7 @@
         <v>128320325</v>
       </c>
       <c r="B39" t="n">
-        <v>97347</v>
+        <v>97355</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4619,7 +4619,7 @@
         <v>128320323</v>
       </c>
       <c r="B40" t="n">
-        <v>105508</v>
+        <v>105516</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>

--- a/artfynd/A 31590-2025 artfynd.xlsx
+++ b/artfynd/A 31590-2025 artfynd.xlsx
@@ -4223,7 +4223,7 @@
         <v>128320327</v>
       </c>
       <c r="B36" t="n">
-        <v>97355</v>
+        <v>97448</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4320,7 +4320,7 @@
         <v>128320328</v>
       </c>
       <c r="B37" t="n">
-        <v>57833</v>
+        <v>57845</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4425,7 +4425,7 @@
         <v>128320324</v>
       </c>
       <c r="B38" t="n">
-        <v>58043</v>
+        <v>58055</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4522,7 +4522,7 @@
         <v>128320325</v>
       </c>
       <c r="B39" t="n">
-        <v>97355</v>
+        <v>97448</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4619,7 +4619,7 @@
         <v>128320323</v>
       </c>
       <c r="B40" t="n">
-        <v>105516</v>
+        <v>105609</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>

--- a/artfynd/A 31590-2025 artfynd.xlsx
+++ b/artfynd/A 31590-2025 artfynd.xlsx
@@ -4223,7 +4223,7 @@
         <v>128320327</v>
       </c>
       <c r="B36" t="n">
-        <v>97448</v>
+        <v>97460</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4320,7 +4320,7 @@
         <v>128320328</v>
       </c>
       <c r="B37" t="n">
-        <v>57845</v>
+        <v>57849</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4425,7 +4425,7 @@
         <v>128320324</v>
       </c>
       <c r="B38" t="n">
-        <v>58055</v>
+        <v>58059</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4522,7 +4522,7 @@
         <v>128320325</v>
       </c>
       <c r="B39" t="n">
-        <v>97448</v>
+        <v>97460</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4619,7 +4619,7 @@
         <v>128320323</v>
       </c>
       <c r="B40" t="n">
-        <v>105609</v>
+        <v>105630</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>

--- a/artfynd/A 31590-2025 artfynd.xlsx
+++ b/artfynd/A 31590-2025 artfynd.xlsx
@@ -4223,7 +4223,7 @@
         <v>128320327</v>
       </c>
       <c r="B36" t="n">
-        <v>97460</v>
+        <v>97462</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4522,7 +4522,7 @@
         <v>128320325</v>
       </c>
       <c r="B39" t="n">
-        <v>97460</v>
+        <v>97462</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4619,7 +4619,7 @@
         <v>128320323</v>
       </c>
       <c r="B40" t="n">
-        <v>105630</v>
+        <v>105642</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>

--- a/artfynd/A 31590-2025 artfynd.xlsx
+++ b/artfynd/A 31590-2025 artfynd.xlsx
@@ -4619,7 +4619,7 @@
         <v>128320323</v>
       </c>
       <c r="B40" t="n">
-        <v>105642</v>
+        <v>105651</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>

--- a/artfynd/A 31590-2025 artfynd.xlsx
+++ b/artfynd/A 31590-2025 artfynd.xlsx
@@ -4223,7 +4223,7 @@
         <v>128320327</v>
       </c>
       <c r="B36" t="n">
-        <v>97462</v>
+        <v>97463</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4522,7 +4522,7 @@
         <v>128320325</v>
       </c>
       <c r="B39" t="n">
-        <v>97462</v>
+        <v>97463</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4619,7 +4619,7 @@
         <v>128320323</v>
       </c>
       <c r="B40" t="n">
-        <v>105651</v>
+        <v>105654</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>

--- a/artfynd/A 31590-2025 artfynd.xlsx
+++ b/artfynd/A 31590-2025 artfynd.xlsx
@@ -4223,7 +4223,7 @@
         <v>128320327</v>
       </c>
       <c r="B36" t="n">
-        <v>97463</v>
+        <v>97490</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4320,7 +4320,7 @@
         <v>128320328</v>
       </c>
       <c r="B37" t="n">
-        <v>57849</v>
+        <v>57876</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4425,7 +4425,7 @@
         <v>128320324</v>
       </c>
       <c r="B38" t="n">
-        <v>58059</v>
+        <v>58086</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4522,7 +4522,7 @@
         <v>128320325</v>
       </c>
       <c r="B39" t="n">
-        <v>97463</v>
+        <v>97490</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4619,7 +4619,7 @@
         <v>128320323</v>
       </c>
       <c r="B40" t="n">
-        <v>105654</v>
+        <v>105682</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>

--- a/artfynd/A 31590-2025 artfynd.xlsx
+++ b/artfynd/A 31590-2025 artfynd.xlsx
@@ -4223,7 +4223,7 @@
         <v>128320327</v>
       </c>
       <c r="B36" t="n">
-        <v>97490</v>
+        <v>97503</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4522,7 +4522,7 @@
         <v>128320325</v>
       </c>
       <c r="B39" t="n">
-        <v>97490</v>
+        <v>97503</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4619,7 +4619,7 @@
         <v>128320323</v>
       </c>
       <c r="B40" t="n">
-        <v>105682</v>
+        <v>105695</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>

--- a/artfynd/A 31590-2025 artfynd.xlsx
+++ b/artfynd/A 31590-2025 artfynd.xlsx
@@ -4223,7 +4223,7 @@
         <v>128320327</v>
       </c>
       <c r="B36" t="n">
-        <v>97503</v>
+        <v>97507</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4320,7 +4320,7 @@
         <v>128320328</v>
       </c>
       <c r="B37" t="n">
-        <v>57876</v>
+        <v>57880</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4425,7 +4425,7 @@
         <v>128320324</v>
       </c>
       <c r="B38" t="n">
-        <v>58086</v>
+        <v>58090</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4522,7 +4522,7 @@
         <v>128320325</v>
       </c>
       <c r="B39" t="n">
-        <v>97503</v>
+        <v>97507</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4619,7 +4619,7 @@
         <v>128320323</v>
       </c>
       <c r="B40" t="n">
-        <v>105695</v>
+        <v>105699</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
